--- a/my_response_spectrum.xlsx
+++ b/my_response_spectrum.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
         <v>0.31882</v>
       </c>
       <c r="C2" t="n">
-        <v>3.12762</v>
+        <v>3.12763</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +449,10 @@
         <v>0.01001</v>
       </c>
       <c r="B3" t="n">
-        <v>0.31916</v>
+        <v>0.32013</v>
       </c>
       <c r="C3" t="n">
-        <v>3.13091</v>
+        <v>3.14044</v>
       </c>
     </row>
     <row r="4">
@@ -460,10 +460,10 @@
         <v>0.02001</v>
       </c>
       <c r="B4" t="n">
-        <v>0.34431</v>
+        <v>0.34669</v>
       </c>
       <c r="C4" t="n">
-        <v>3.37767</v>
+        <v>3.40099</v>
       </c>
     </row>
     <row r="5">
@@ -471,10 +471,10 @@
         <v>0.03001</v>
       </c>
       <c r="B5" t="n">
-        <v>0.36318</v>
+        <v>0.35225</v>
       </c>
       <c r="C5" t="n">
-        <v>3.56279</v>
+        <v>3.45555</v>
       </c>
     </row>
     <row r="6">
@@ -482,10 +482,10 @@
         <v>0.04001</v>
       </c>
       <c r="B6" t="n">
-        <v>0.42089</v>
+        <v>0.35864</v>
       </c>
       <c r="C6" t="n">
-        <v>4.12895</v>
+        <v>3.51824</v>
       </c>
     </row>
     <row r="7">
@@ -493,10 +493,10 @@
         <v>0.05001</v>
       </c>
       <c r="B7" t="n">
-        <v>0.54061</v>
+        <v>0.47342</v>
       </c>
       <c r="C7" t="n">
-        <v>5.30334</v>
+        <v>4.64421</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +504,10 @@
         <v>0.06001</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6228399999999999</v>
+        <v>0.55565</v>
       </c>
       <c r="C8" t="n">
-        <v>6.11007</v>
+        <v>5.45093</v>
       </c>
     </row>
     <row r="9">
@@ -515,10 +515,10 @@
         <v>0.07001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.63065</v>
+        <v>0.56346</v>
       </c>
       <c r="C9" t="n">
-        <v>6.18664</v>
+        <v>5.5275</v>
       </c>
     </row>
     <row r="10">
@@ -526,10 +526,10 @@
         <v>0.08001</v>
       </c>
       <c r="B10" t="n">
-        <v>0.63973</v>
+        <v>0.57254</v>
       </c>
       <c r="C10" t="n">
-        <v>6.27571</v>
+        <v>5.61657</v>
       </c>
     </row>
     <row r="11">
@@ -537,10 +537,10 @@
         <v>0.09001000000000001</v>
       </c>
       <c r="B11" t="n">
-        <v>0.68682</v>
+        <v>0.61963</v>
       </c>
       <c r="C11" t="n">
-        <v>6.73773</v>
+        <v>6.0786</v>
       </c>
     </row>
     <row r="12">
@@ -548,10 +548,10 @@
         <v>0.10001</v>
       </c>
       <c r="B12" t="n">
-        <v>0.71613</v>
+        <v>0.64895</v>
       </c>
       <c r="C12" t="n">
-        <v>7.02527</v>
+        <v>6.36624</v>
       </c>
     </row>
     <row r="13">
@@ -559,10 +559,10 @@
         <v>0.11001</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7990699999999999</v>
+        <v>0.73189</v>
       </c>
       <c r="C13" t="n">
-        <v>7.83889</v>
+        <v>7.17986</v>
       </c>
     </row>
     <row r="14">
@@ -570,10 +570,10 @@
         <v>0.12001</v>
       </c>
       <c r="B14" t="n">
-        <v>0.68902</v>
+        <v>0.66816</v>
       </c>
       <c r="C14" t="n">
-        <v>6.75927</v>
+        <v>6.55469</v>
       </c>
     </row>
     <row r="15">
@@ -581,10 +581,10 @@
         <v>0.13001</v>
       </c>
       <c r="B15" t="n">
-        <v>0.66552</v>
+        <v>0.64705</v>
       </c>
       <c r="C15" t="n">
-        <v>6.52872</v>
+        <v>6.34753</v>
       </c>
     </row>
     <row r="16">
@@ -592,10 +592,10 @@
         <v>0.14001</v>
       </c>
       <c r="B16" t="n">
-        <v>0.76983</v>
+        <v>0.73324</v>
       </c>
       <c r="C16" t="n">
-        <v>7.55201</v>
+        <v>7.19304</v>
       </c>
     </row>
     <row r="17">
@@ -603,10 +603,10 @@
         <v>0.15001</v>
       </c>
       <c r="B17" t="n">
-        <v>0.81468</v>
+        <v>0.77133</v>
       </c>
       <c r="C17" t="n">
-        <v>7.99205</v>
+        <v>7.56671</v>
       </c>
     </row>
     <row r="18">
@@ -614,10 +614,10 @@
         <v>0.16001</v>
       </c>
       <c r="B18" t="n">
-        <v>0.77563</v>
+        <v>0.75715</v>
       </c>
       <c r="C18" t="n">
-        <v>7.60892</v>
+        <v>7.42763</v>
       </c>
     </row>
     <row r="19">
@@ -625,10 +625,10 @@
         <v>0.17001</v>
       </c>
       <c r="B19" t="n">
-        <v>0.92302</v>
+        <v>0.885</v>
       </c>
       <c r="C19" t="n">
-        <v>9.05486</v>
+        <v>8.68182</v>
       </c>
     </row>
     <row r="20">
@@ -636,10 +636,10 @@
         <v>0.18001</v>
       </c>
       <c r="B20" t="n">
-        <v>0.92435</v>
+        <v>0.88771</v>
       </c>
       <c r="C20" t="n">
-        <v>9.06784</v>
+        <v>8.708399999999999</v>
       </c>
     </row>
     <row r="21">
@@ -647,10 +647,10 @@
         <v>0.19001</v>
       </c>
       <c r="B21" t="n">
-        <v>0.91556</v>
+        <v>0.87893</v>
       </c>
       <c r="C21" t="n">
-        <v>8.98169</v>
+        <v>8.622350000000001</v>
       </c>
     </row>
     <row r="22">
@@ -658,10 +658,10 @@
         <v>0.20001</v>
       </c>
       <c r="B22" t="n">
-        <v>0.76035</v>
+        <v>0.7266899999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>7.45908</v>
+        <v>7.12887</v>
       </c>
     </row>
     <row r="23">
@@ -669,10 +669,10 @@
         <v>0.21001</v>
       </c>
       <c r="B23" t="n">
-        <v>0.66444</v>
+        <v>0.62516</v>
       </c>
       <c r="C23" t="n">
-        <v>6.51814</v>
+        <v>6.13283</v>
       </c>
     </row>
     <row r="24">
@@ -680,10 +680,10 @@
         <v>0.22001</v>
       </c>
       <c r="B24" t="n">
-        <v>0.62888</v>
+        <v>0.57073</v>
       </c>
       <c r="C24" t="n">
-        <v>6.16928</v>
+        <v>5.59891</v>
       </c>
     </row>
     <row r="25">
@@ -691,10 +691,10 @@
         <v>0.23001</v>
       </c>
       <c r="B25" t="n">
-        <v>0.68777</v>
+        <v>0.62058</v>
       </c>
       <c r="C25" t="n">
-        <v>6.74704</v>
+        <v>6.0879</v>
       </c>
     </row>
     <row r="26">
@@ -702,10 +702,10 @@
         <v>0.24001</v>
       </c>
       <c r="B26" t="n">
-        <v>0.83989</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>8.239369999999999</v>
+        <v>7.58023</v>
       </c>
     </row>
     <row r="27">
@@ -713,10 +713,10 @@
         <v>0.25001</v>
       </c>
       <c r="B27" t="n">
-        <v>0.93885</v>
+        <v>0.87166</v>
       </c>
       <c r="C27" t="n">
-        <v>9.21007</v>
+        <v>8.550940000000001</v>
       </c>
     </row>
     <row r="28">
@@ -724,10 +724,10 @@
         <v>0.26001</v>
       </c>
       <c r="B28" t="n">
-        <v>1.03663</v>
+        <v>0.90596</v>
       </c>
       <c r="C28" t="n">
-        <v>10.16937</v>
+        <v>8.887510000000001</v>
       </c>
     </row>
     <row r="29">
@@ -735,10 +735,10 @@
         <v>0.27001</v>
       </c>
       <c r="B29" t="n">
-        <v>1.03342</v>
+        <v>0.83943</v>
       </c>
       <c r="C29" t="n">
-        <v>10.13788</v>
+        <v>8.2348</v>
       </c>
     </row>
     <row r="30">
@@ -746,10 +746,10 @@
         <v>0.28001</v>
       </c>
       <c r="B30" t="n">
-        <v>0.98005</v>
+        <v>0.78296</v>
       </c>
       <c r="C30" t="n">
-        <v>9.61429</v>
+        <v>7.68087</v>
       </c>
     </row>
     <row r="31">
@@ -757,10 +757,10 @@
         <v>0.29001</v>
       </c>
       <c r="B31" t="n">
-        <v>0.95933</v>
+        <v>0.75412</v>
       </c>
       <c r="C31" t="n">
-        <v>9.41103</v>
+        <v>7.39788</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         <v>0.30001</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9859</v>
+        <v>0.75341</v>
       </c>
       <c r="C32" t="n">
-        <v>9.671670000000001</v>
+        <v>7.39092</v>
       </c>
     </row>
     <row r="33">
@@ -779,10 +779,10 @@
         <v>0.31001</v>
       </c>
       <c r="B33" t="n">
-        <v>1.03226</v>
+        <v>0.78613</v>
       </c>
       <c r="C33" t="n">
-        <v>10.12644</v>
+        <v>7.71193</v>
       </c>
     </row>
     <row r="34">
@@ -790,10 +790,10 @@
         <v>0.32001</v>
       </c>
       <c r="B34" t="n">
-        <v>1.07626</v>
+        <v>0.7839699999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>10.55813</v>
+        <v>7.69078</v>
       </c>
     </row>
     <row r="35">
@@ -801,10 +801,10 @@
         <v>0.33001</v>
       </c>
       <c r="B35" t="n">
-        <v>1.08101</v>
+        <v>0.78581</v>
       </c>
       <c r="C35" t="n">
-        <v>10.60469</v>
+        <v>7.70878</v>
       </c>
     </row>
     <row r="36">
@@ -812,10 +812,10 @@
         <v>0.34001</v>
       </c>
       <c r="B36" t="n">
-        <v>1.05128</v>
+        <v>0.7664299999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>10.31304</v>
+        <v>7.51866</v>
       </c>
     </row>
     <row r="37">
@@ -823,10 +823,10 @@
         <v>0.35001</v>
       </c>
       <c r="B37" t="n">
-        <v>1.00485</v>
+        <v>0.74581</v>
       </c>
       <c r="C37" t="n">
-        <v>9.857620000000001</v>
+        <v>7.31642</v>
       </c>
     </row>
     <row r="38">
@@ -834,10 +834,10 @@
         <v>0.36001</v>
       </c>
       <c r="B38" t="n">
-        <v>0.95785</v>
+        <v>0.73344</v>
       </c>
       <c r="C38" t="n">
-        <v>9.39653</v>
+        <v>7.19504</v>
       </c>
     </row>
     <row r="39">
@@ -845,10 +845,10 @@
         <v>0.37001</v>
       </c>
       <c r="B39" t="n">
-        <v>0.91789</v>
+        <v>0.7339</v>
       </c>
       <c r="C39" t="n">
-        <v>9.004519999999999</v>
+        <v>7.19955</v>
       </c>
     </row>
     <row r="40">
@@ -856,10 +856,10 @@
         <v>0.38001</v>
       </c>
       <c r="B40" t="n">
-        <v>0.88483</v>
+        <v>0.73262</v>
       </c>
       <c r="C40" t="n">
-        <v>8.68017</v>
+        <v>7.187</v>
       </c>
     </row>
     <row r="41">
@@ -867,10 +867,10 @@
         <v>0.39001</v>
       </c>
       <c r="B41" t="n">
-        <v>0.85468</v>
+        <v>0.75092</v>
       </c>
       <c r="C41" t="n">
-        <v>8.384449999999999</v>
+        <v>7.36649</v>
       </c>
     </row>
     <row r="42">
@@ -878,10 +878,10 @@
         <v>0.40001</v>
       </c>
       <c r="B42" t="n">
-        <v>0.823</v>
+        <v>0.75888</v>
       </c>
       <c r="C42" t="n">
-        <v>8.073589999999999</v>
+        <v>7.44466</v>
       </c>
     </row>
     <row r="43">
@@ -889,10 +889,10 @@
         <v>0.41001</v>
       </c>
       <c r="B43" t="n">
-        <v>0.81659</v>
+        <v>0.78293</v>
       </c>
       <c r="C43" t="n">
-        <v>8.0108</v>
+        <v>7.68059</v>
       </c>
     </row>
     <row r="44">
@@ -900,10 +900,10 @@
         <v>0.42001</v>
       </c>
       <c r="B44" t="n">
-        <v>0.8284</v>
+        <v>0.79474</v>
       </c>
       <c r="C44" t="n">
-        <v>8.12659</v>
+        <v>7.79639</v>
       </c>
     </row>
     <row r="45">
@@ -911,10 +911,10 @@
         <v>0.43001</v>
       </c>
       <c r="B45" t="n">
-        <v>0.84676</v>
+        <v>0.8131</v>
       </c>
       <c r="C45" t="n">
-        <v>8.30674</v>
+        <v>7.97653</v>
       </c>
     </row>
     <row r="46">
@@ -922,10 +922,10 @@
         <v>0.44001</v>
       </c>
       <c r="B46" t="n">
-        <v>0.85741</v>
+        <v>0.82375</v>
       </c>
       <c r="C46" t="n">
-        <v>8.41122</v>
+        <v>8.081020000000001</v>
       </c>
     </row>
     <row r="47">
@@ -933,10 +933,10 @@
         <v>0.45001</v>
       </c>
       <c r="B47" t="n">
-        <v>0.8777</v>
+        <v>0.82586</v>
       </c>
       <c r="C47" t="n">
-        <v>8.61022</v>
+        <v>8.10168</v>
       </c>
     </row>
     <row r="48">
@@ -944,10 +944,10 @@
         <v>0.46001</v>
       </c>
       <c r="B48" t="n">
-        <v>0.91232</v>
+        <v>0.8459</v>
       </c>
       <c r="C48" t="n">
-        <v>8.94988</v>
+        <v>8.298299999999999</v>
       </c>
     </row>
     <row r="49">
@@ -955,10 +955,10 @@
         <v>0.47001</v>
       </c>
       <c r="B49" t="n">
-        <v>0.9371</v>
+        <v>0.87068</v>
       </c>
       <c r="C49" t="n">
-        <v>9.19295</v>
+        <v>8.541370000000001</v>
       </c>
     </row>
     <row r="50">
@@ -966,10 +966,10 @@
         <v>0.48001</v>
       </c>
       <c r="B50" t="n">
-        <v>0.96065</v>
+        <v>0.89423</v>
       </c>
       <c r="C50" t="n">
-        <v>9.42394</v>
+        <v>8.772360000000001</v>
       </c>
     </row>
     <row r="51">
@@ -977,10 +977,10 @@
         <v>0.49001</v>
       </c>
       <c r="B51" t="n">
-        <v>0.98056</v>
+        <v>0.91414</v>
       </c>
       <c r="C51" t="n">
-        <v>9.619249999999999</v>
+        <v>8.96767</v>
       </c>
     </row>
     <row r="52">
@@ -988,10 +988,10 @@
         <v>0.50001</v>
       </c>
       <c r="B52" t="n">
-        <v>0.98356</v>
+        <v>0.91714</v>
       </c>
       <c r="C52" t="n">
-        <v>9.648720000000001</v>
+        <v>8.99714</v>
       </c>
     </row>
     <row r="53">
@@ -999,10 +999,10 @@
         <v>0.51001</v>
       </c>
       <c r="B53" t="n">
-        <v>0.98912</v>
+        <v>0.9227</v>
       </c>
       <c r="C53" t="n">
-        <v>9.703239999999999</v>
+        <v>9.05166</v>
       </c>
     </row>
     <row r="54">
@@ -1010,10 +1010,10 @@
         <v>0.52001</v>
       </c>
       <c r="B54" t="n">
-        <v>0.98163</v>
+        <v>0.91521</v>
       </c>
       <c r="C54" t="n">
-        <v>9.62979</v>
+        <v>8.978210000000001</v>
       </c>
     </row>
     <row r="55">
@@ -1021,10 +1021,10 @@
         <v>0.53001</v>
       </c>
       <c r="B55" t="n">
-        <v>0.96297</v>
+        <v>0.89654</v>
       </c>
       <c r="C55" t="n">
-        <v>9.44669</v>
+        <v>8.795019999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1032,10 +1032,10 @@
         <v>0.54001</v>
       </c>
       <c r="B56" t="n">
-        <v>0.9454900000000001</v>
+        <v>0.87906</v>
       </c>
       <c r="C56" t="n">
-        <v>9.275259999999999</v>
+        <v>8.62358</v>
       </c>
     </row>
     <row r="57">
@@ -1043,10 +1043,10 @@
         <v>0.55001</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9119</v>
+        <v>0.8454700000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>8.945790000000001</v>
+        <v>8.29411</v>
       </c>
     </row>
     <row r="58">
@@ -1054,10 +1054,10 @@
         <v>0.56001</v>
       </c>
       <c r="B58" t="n">
-        <v>0.88489</v>
+        <v>0.81631</v>
       </c>
       <c r="C58" t="n">
-        <v>8.680730000000001</v>
+        <v>8.007960000000001</v>
       </c>
     </row>
     <row r="59">
@@ -1065,10 +1065,10 @@
         <v>0.57001</v>
       </c>
       <c r="B59" t="n">
-        <v>0.87697</v>
+        <v>0.8083900000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>8.60308</v>
+        <v>7.93031</v>
       </c>
     </row>
     <row r="60">
@@ -1076,10 +1076,10 @@
         <v>0.58001</v>
       </c>
       <c r="B60" t="n">
-        <v>0.86648</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>8.500220000000001</v>
+        <v>7.82745</v>
       </c>
     </row>
     <row r="61">
@@ -1087,10 +1087,10 @@
         <v>0.59001</v>
       </c>
       <c r="B61" t="n">
-        <v>0.84879</v>
+        <v>0.78021</v>
       </c>
       <c r="C61" t="n">
-        <v>8.326610000000001</v>
+        <v>7.65384</v>
       </c>
     </row>
     <row r="62">
@@ -1098,10 +1098,10 @@
         <v>0.60001</v>
       </c>
       <c r="B62" t="n">
-        <v>0.8298</v>
+        <v>0.76122</v>
       </c>
       <c r="C62" t="n">
-        <v>8.1403</v>
+        <v>7.46753</v>
       </c>
     </row>
     <row r="63">
@@ -1109,10 +1109,10 @@
         <v>0.6100100000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>0.81233</v>
+        <v>0.74375</v>
       </c>
       <c r="C63" t="n">
-        <v>7.96899</v>
+        <v>7.29622</v>
       </c>
     </row>
     <row r="64">
@@ -1120,10 +1120,10 @@
         <v>0.62001</v>
       </c>
       <c r="B64" t="n">
-        <v>0.78998</v>
+        <v>0.7214</v>
       </c>
       <c r="C64" t="n">
-        <v>7.7497</v>
+        <v>7.07693</v>
       </c>
     </row>
     <row r="65">
@@ -1131,10 +1131,10 @@
         <v>0.63001</v>
       </c>
       <c r="B65" t="n">
-        <v>0.76385</v>
+        <v>0.6952700000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>7.49336</v>
+        <v>6.82059</v>
       </c>
     </row>
     <row r="66">
@@ -1142,10 +1142,10 @@
         <v>0.64001</v>
       </c>
       <c r="B66" t="n">
-        <v>0.74131</v>
+        <v>0.6727300000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>7.27222</v>
+        <v>6.59945</v>
       </c>
     </row>
     <row r="67">
@@ -1153,10 +1153,10 @@
         <v>0.65001</v>
       </c>
       <c r="B67" t="n">
-        <v>0.71812</v>
+        <v>0.64954</v>
       </c>
       <c r="C67" t="n">
-        <v>7.04477</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="68">
@@ -1164,10 +1164,10 @@
         <v>0.66001</v>
       </c>
       <c r="B68" t="n">
-        <v>0.69272</v>
+        <v>0.62414</v>
       </c>
       <c r="C68" t="n">
-        <v>6.79558</v>
+        <v>6.12281</v>
       </c>
     </row>
     <row r="69">
@@ -1175,10 +1175,10 @@
         <v>0.67001</v>
       </c>
       <c r="B69" t="n">
-        <v>0.6658500000000001</v>
+        <v>0.59727</v>
       </c>
       <c r="C69" t="n">
-        <v>6.53198</v>
+        <v>5.85921</v>
       </c>
     </row>
     <row r="70">
@@ -1186,10 +1186,10 @@
         <v>0.68001</v>
       </c>
       <c r="B70" t="n">
-        <v>0.63966</v>
+        <v>0.57108</v>
       </c>
       <c r="C70" t="n">
-        <v>6.2751</v>
+        <v>5.60233</v>
       </c>
     </row>
     <row r="71">
@@ -1197,10 +1197,10 @@
         <v>0.69001</v>
       </c>
       <c r="B71" t="n">
-        <v>0.61689</v>
+        <v>0.54831</v>
       </c>
       <c r="C71" t="n">
-        <v>6.05165</v>
+        <v>5.37888</v>
       </c>
     </row>
     <row r="72">
@@ -1208,10 +1208,10 @@
         <v>0.70001</v>
       </c>
       <c r="B72" t="n">
-        <v>0.59343</v>
+        <v>0.52485</v>
       </c>
       <c r="C72" t="n">
-        <v>5.82158</v>
+        <v>5.14881</v>
       </c>
     </row>
     <row r="73">
@@ -1219,10 +1219,10 @@
         <v>0.71001</v>
       </c>
       <c r="B73" t="n">
-        <v>0.56974</v>
+        <v>0.50116</v>
       </c>
       <c r="C73" t="n">
-        <v>5.5892</v>
+        <v>4.91643</v>
       </c>
     </row>
     <row r="74">
@@ -1230,10 +1230,10 @@
         <v>0.72001</v>
       </c>
       <c r="B74" t="n">
-        <v>0.54618</v>
+        <v>0.47879</v>
       </c>
       <c r="C74" t="n">
-        <v>5.358</v>
+        <v>4.69693</v>
       </c>
     </row>
     <row r="75">
@@ -1241,10 +1241,10 @@
         <v>0.73001</v>
       </c>
       <c r="B75" t="n">
-        <v>0.52302</v>
+        <v>0.4629</v>
       </c>
       <c r="C75" t="n">
-        <v>5.13078</v>
+        <v>4.54107</v>
       </c>
     </row>
     <row r="76">
@@ -1252,10 +1252,10 @@
         <v>0.7400099999999999</v>
       </c>
       <c r="B76" t="n">
-        <v>0.50048</v>
+        <v>0.45533</v>
       </c>
       <c r="C76" t="n">
-        <v>4.9097</v>
+        <v>4.46681</v>
       </c>
     </row>
     <row r="77">
@@ -1263,10 +1263,10 @@
         <v>0.75001</v>
       </c>
       <c r="B77" t="n">
-        <v>0.48234</v>
+        <v>0.44783</v>
       </c>
       <c r="C77" t="n">
-        <v>4.73172</v>
+        <v>4.39319</v>
       </c>
     </row>
     <row r="78">
@@ -1274,10 +1274,10 @@
         <v>0.76001</v>
       </c>
       <c r="B78" t="n">
-        <v>0.47905</v>
+        <v>0.43218</v>
       </c>
       <c r="C78" t="n">
-        <v>4.69948</v>
+        <v>4.23968</v>
       </c>
     </row>
     <row r="79">
@@ -1285,10 +1285,10 @@
         <v>0.77001</v>
       </c>
       <c r="B79" t="n">
-        <v>0.48538</v>
+        <v>0.43982</v>
       </c>
       <c r="C79" t="n">
-        <v>4.76161</v>
+        <v>4.31465</v>
       </c>
     </row>
     <row r="80">
@@ -1296,10 +1296,10 @@
         <v>0.78001</v>
       </c>
       <c r="B80" t="n">
-        <v>0.49955</v>
+        <v>0.45596</v>
       </c>
       <c r="C80" t="n">
-        <v>4.90056</v>
+        <v>4.47301</v>
       </c>
     </row>
     <row r="81">
@@ -1307,10 +1307,10 @@
         <v>0.79001</v>
       </c>
       <c r="B81" t="n">
-        <v>0.51785</v>
+        <v>0.47754</v>
       </c>
       <c r="C81" t="n">
-        <v>5.08012</v>
+        <v>4.68469</v>
       </c>
     </row>
     <row r="82">
@@ -1318,10 +1318,10 @@
         <v>0.80001</v>
       </c>
       <c r="B82" t="n">
-        <v>0.53565</v>
+        <v>0.50142</v>
       </c>
       <c r="C82" t="n">
-        <v>5.25477</v>
+        <v>4.91894</v>
       </c>
     </row>
     <row r="83">
@@ -1329,10 +1329,10 @@
         <v>0.81001</v>
       </c>
       <c r="B83" t="n">
-        <v>0.54827</v>
+        <v>0.52663</v>
       </c>
       <c r="C83" t="n">
-        <v>5.37853</v>
+        <v>5.16625</v>
       </c>
     </row>
     <row r="84">
@@ -1340,10 +1340,10 @@
         <v>0.82001</v>
       </c>
       <c r="B84" t="n">
-        <v>0.55169</v>
+        <v>0.54855</v>
       </c>
       <c r="C84" t="n">
-        <v>5.41209</v>
+        <v>5.38131</v>
       </c>
     </row>
     <row r="85">
@@ -1351,10 +1351,10 @@
         <v>0.83001</v>
       </c>
       <c r="B85" t="n">
-        <v>0.57628</v>
+        <v>0.5656099999999999</v>
       </c>
       <c r="C85" t="n">
-        <v>5.65328</v>
+        <v>5.54867</v>
       </c>
     </row>
     <row r="86">
@@ -1362,10 +1362,10 @@
         <v>0.84001</v>
       </c>
       <c r="B86" t="n">
-        <v>0.5906</v>
+        <v>0.57983</v>
       </c>
       <c r="C86" t="n">
-        <v>5.79375</v>
+        <v>5.6881</v>
       </c>
     </row>
     <row r="87">
@@ -1373,10 +1373,10 @@
         <v>0.85001</v>
       </c>
       <c r="B87" t="n">
-        <v>0.59841</v>
+        <v>0.58765</v>
       </c>
       <c r="C87" t="n">
-        <v>5.87044</v>
+        <v>5.76488</v>
       </c>
     </row>
     <row r="88">
@@ -1384,10 +1384,10 @@
         <v>0.8600100000000001</v>
       </c>
       <c r="B88" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.58911</v>
       </c>
       <c r="C88" t="n">
-        <v>6.03709</v>
+        <v>5.77917</v>
       </c>
     </row>
     <row r="89">
@@ -1395,10 +1395,10 @@
         <v>0.87001</v>
       </c>
       <c r="B89" t="n">
-        <v>0.62807</v>
+        <v>0.58445</v>
       </c>
       <c r="C89" t="n">
-        <v>6.16138</v>
+        <v>5.73345</v>
       </c>
     </row>
     <row r="90">
@@ -1406,10 +1406,10 @@
         <v>0.88001</v>
       </c>
       <c r="B90" t="n">
-        <v>0.62556</v>
+        <v>0.57342</v>
       </c>
       <c r="C90" t="n">
-        <v>6.13671</v>
+        <v>5.62522</v>
       </c>
     </row>
     <row r="91">
@@ -1417,10 +1417,10 @@
         <v>0.89001</v>
       </c>
       <c r="B91" t="n">
-        <v>0.60811</v>
+        <v>0.55611</v>
       </c>
       <c r="C91" t="n">
-        <v>5.96558</v>
+        <v>5.45547</v>
       </c>
     </row>
     <row r="92">
@@ -1428,10 +1428,10 @@
         <v>0.90001</v>
       </c>
       <c r="B92" t="n">
-        <v>0.57979</v>
+        <v>0.53449</v>
       </c>
       <c r="C92" t="n">
-        <v>5.68771</v>
+        <v>5.24336</v>
       </c>
     </row>
     <row r="93">
@@ -1439,10 +1439,10 @@
         <v>0.91001</v>
       </c>
       <c r="B93" t="n">
-        <v>0.58292</v>
+        <v>0.50788</v>
       </c>
       <c r="C93" t="n">
-        <v>5.71842</v>
+        <v>4.98232</v>
       </c>
     </row>
     <row r="94">
@@ -1450,10 +1450,10 @@
         <v>0.92001</v>
       </c>
       <c r="B94" t="n">
-        <v>0.5786</v>
+        <v>0.50286</v>
       </c>
       <c r="C94" t="n">
-        <v>5.67611</v>
+        <v>4.93304</v>
       </c>
     </row>
     <row r="95">
@@ -1461,10 +1461,10 @@
         <v>0.93001</v>
       </c>
       <c r="B95" t="n">
-        <v>0.56723</v>
+        <v>0.50627</v>
       </c>
       <c r="C95" t="n">
-        <v>5.5645</v>
+        <v>4.96647</v>
       </c>
     </row>
     <row r="96">
@@ -1472,10 +1472,10 @@
         <v>0.94001</v>
       </c>
       <c r="B96" t="n">
-        <v>0.55489</v>
+        <v>0.50681</v>
       </c>
       <c r="C96" t="n">
-        <v>5.44351</v>
+        <v>4.97184</v>
       </c>
     </row>
     <row r="97">
@@ -1483,10 +1483,10 @@
         <v>0.95001</v>
       </c>
       <c r="B97" t="n">
-        <v>0.55393</v>
+        <v>0.50585</v>
       </c>
       <c r="C97" t="n">
-        <v>5.43408</v>
+        <v>4.96241</v>
       </c>
     </row>
     <row r="98">
@@ -1494,10 +1494,10 @@
         <v>0.96001</v>
       </c>
       <c r="B98" t="n">
-        <v>0.5488</v>
+        <v>0.5007200000000001</v>
       </c>
       <c r="C98" t="n">
-        <v>5.38372</v>
+        <v>4.91206</v>
       </c>
     </row>
     <row r="99">
@@ -1505,10 +1505,10 @@
         <v>0.97001</v>
       </c>
       <c r="B99" t="n">
-        <v>0.54166</v>
+        <v>0.49358</v>
       </c>
       <c r="C99" t="n">
-        <v>5.31364</v>
+        <v>4.84198</v>
       </c>
     </row>
     <row r="100">
@@ -1516,10 +1516,10 @@
         <v>0.98001</v>
       </c>
       <c r="B100" t="n">
-        <v>0.53172</v>
+        <v>0.48364</v>
       </c>
       <c r="C100" t="n">
-        <v>5.21621</v>
+        <v>4.74454</v>
       </c>
     </row>
     <row r="101">
@@ -1527,10 +1527,10 @@
         <v>0.9900099999999999</v>
       </c>
       <c r="B101" t="n">
-        <v>0.51854</v>
+        <v>0.47046</v>
       </c>
       <c r="C101" t="n">
-        <v>5.08691</v>
+        <v>4.61525</v>
       </c>
     </row>
     <row r="102">
@@ -1538,10 +1538,10 @@
         <v>1.00001</v>
       </c>
       <c r="B102" t="n">
-        <v>0.50392</v>
+        <v>0.45584</v>
       </c>
       <c r="C102" t="n">
-        <v>4.94347</v>
+        <v>4.47181</v>
       </c>
     </row>
     <row r="103">
@@ -1549,10 +1549,10 @@
         <v>1.01001</v>
       </c>
       <c r="B103" t="n">
-        <v>0.48592</v>
+        <v>0.43784</v>
       </c>
       <c r="C103" t="n">
-        <v>4.76684</v>
+        <v>4.29517</v>
       </c>
     </row>
     <row r="104">
@@ -1560,10 +1560,10 @@
         <v>1.02001</v>
       </c>
       <c r="B104" t="n">
-        <v>0.47701</v>
+        <v>0.43009</v>
       </c>
       <c r="C104" t="n">
-        <v>4.67948</v>
+        <v>4.2192</v>
       </c>
     </row>
     <row r="105">
@@ -1571,10 +1571,10 @@
         <v>1.03001</v>
       </c>
       <c r="B105" t="n">
-        <v>0.46961</v>
+        <v>0.42269</v>
       </c>
       <c r="C105" t="n">
-        <v>4.60689</v>
+        <v>4.1466</v>
       </c>
     </row>
     <row r="106">
@@ -1582,10 +1582,10 @@
         <v>1.04001</v>
       </c>
       <c r="B106" t="n">
-        <v>0.45878</v>
+        <v>0.41186</v>
       </c>
       <c r="C106" t="n">
-        <v>4.50061</v>
+        <v>4.04032</v>
       </c>
     </row>
     <row r="107">
@@ -1593,10 +1593,10 @@
         <v>1.05001</v>
       </c>
       <c r="B107" t="n">
-        <v>0.45681</v>
+        <v>0.4011</v>
       </c>
       <c r="C107" t="n">
-        <v>4.48132</v>
+        <v>3.93479</v>
       </c>
     </row>
     <row r="108">
@@ -1604,10 +1604,10 @@
         <v>1.06001</v>
       </c>
       <c r="B108" t="n">
-        <v>0.45524</v>
+        <v>0.38789</v>
       </c>
       <c r="C108" t="n">
-        <v>4.46587</v>
+        <v>3.80523</v>
       </c>
     </row>
     <row r="109">
@@ -1615,10 +1615,10 @@
         <v>1.07001</v>
       </c>
       <c r="B109" t="n">
-        <v>0.45338</v>
+        <v>0.37445</v>
       </c>
       <c r="C109" t="n">
-        <v>4.44761</v>
+        <v>3.67336</v>
       </c>
     </row>
     <row r="110">
@@ -1626,10 +1626,10 @@
         <v>1.08001</v>
       </c>
       <c r="B110" t="n">
-        <v>0.45124</v>
+        <v>0.35955</v>
       </c>
       <c r="C110" t="n">
-        <v>4.42662</v>
+        <v>3.52714</v>
       </c>
     </row>
     <row r="111">
@@ -1637,10 +1637,10 @@
         <v>1.09001</v>
       </c>
       <c r="B111" t="n">
-        <v>0.44883</v>
+        <v>0.34481</v>
       </c>
       <c r="C111" t="n">
-        <v>4.40297</v>
+        <v>3.38256</v>
       </c>
     </row>
     <row r="112">
@@ -1648,10 +1648,10 @@
         <v>1.10001</v>
       </c>
       <c r="B112" t="n">
-        <v>0.44615</v>
+        <v>0.32893</v>
       </c>
       <c r="C112" t="n">
-        <v>4.37676</v>
+        <v>3.22683</v>
       </c>
     </row>
     <row r="113">
@@ -1659,10 +1659,10 @@
         <v>1.11001</v>
       </c>
       <c r="B113" t="n">
-        <v>0.44323</v>
+        <v>0.31383</v>
       </c>
       <c r="C113" t="n">
-        <v>4.34807</v>
+        <v>3.07863</v>
       </c>
     </row>
     <row r="114">
@@ -1670,10 +1670,10 @@
         <v>1.12001</v>
       </c>
       <c r="B114" t="n">
-        <v>0.44006</v>
+        <v>0.29763</v>
       </c>
       <c r="C114" t="n">
-        <v>4.31704</v>
+        <v>2.91976</v>
       </c>
     </row>
     <row r="115">
@@ -1681,10 +1681,10 @@
         <v>1.13001</v>
       </c>
       <c r="B115" t="n">
-        <v>0.43667</v>
+        <v>0.28209</v>
       </c>
       <c r="C115" t="n">
-        <v>4.28377</v>
+        <v>2.76734</v>
       </c>
     </row>
     <row r="116">
@@ -1692,10 +1692,10 @@
         <v>1.14001</v>
       </c>
       <c r="B116" t="n">
-        <v>0.43307</v>
+        <v>0.27249</v>
       </c>
       <c r="C116" t="n">
-        <v>4.24839</v>
+        <v>2.67312</v>
       </c>
     </row>
     <row r="117">
@@ -1703,10 +1703,10 @@
         <v>1.15001</v>
       </c>
       <c r="B117" t="n">
-        <v>0.42926</v>
+        <v>0.26417</v>
       </c>
       <c r="C117" t="n">
-        <v>4.21104</v>
+        <v>2.59154</v>
       </c>
     </row>
     <row r="118">
@@ -1714,10 +1714,10 @@
         <v>1.16001</v>
       </c>
       <c r="B118" t="n">
-        <v>0.42527</v>
+        <v>0.25651</v>
       </c>
       <c r="C118" t="n">
-        <v>4.17187</v>
+        <v>2.51635</v>
       </c>
     </row>
     <row r="119">
@@ -1725,10 +1725,10 @@
         <v>1.17001</v>
       </c>
       <c r="B119" t="n">
-        <v>0.4211</v>
+        <v>0.2534</v>
       </c>
       <c r="C119" t="n">
-        <v>4.13102</v>
+        <v>2.4859</v>
       </c>
     </row>
     <row r="120">
@@ -1736,10 +1736,10 @@
         <v>1.18001</v>
       </c>
       <c r="B120" t="n">
-        <v>0.41678</v>
+        <v>0.25703</v>
       </c>
       <c r="C120" t="n">
-        <v>4.08864</v>
+        <v>2.52145</v>
       </c>
     </row>
     <row r="121">
@@ -1747,10 +1747,10 @@
         <v>1.19001</v>
       </c>
       <c r="B121" t="n">
-        <v>0.41232</v>
+        <v>0.25869</v>
       </c>
       <c r="C121" t="n">
-        <v>4.04488</v>
+        <v>2.53774</v>
       </c>
     </row>
     <row r="122">
@@ -1758,10 +1758,10 @@
         <v>1.20001</v>
       </c>
       <c r="B122" t="n">
-        <v>0.40774</v>
+        <v>0.259</v>
       </c>
       <c r="C122" t="n">
-        <v>3.99989</v>
+        <v>2.54082</v>
       </c>
     </row>
     <row r="123">
@@ -1769,10 +1769,10 @@
         <v>1.21001</v>
       </c>
       <c r="B123" t="n">
-        <v>0.40304</v>
+        <v>0.2573</v>
       </c>
       <c r="C123" t="n">
-        <v>3.95382</v>
+        <v>2.52411</v>
       </c>
     </row>
     <row r="124">
@@ -1780,10 +1780,10 @@
         <v>1.22001</v>
       </c>
       <c r="B124" t="n">
-        <v>0.39825</v>
+        <v>0.25495</v>
       </c>
       <c r="C124" t="n">
-        <v>3.90683</v>
+        <v>2.50111</v>
       </c>
     </row>
     <row r="125">
@@ -1791,10 +1791,10 @@
         <v>1.23001</v>
       </c>
       <c r="B125" t="n">
-        <v>0.39338</v>
+        <v>0.25096</v>
       </c>
       <c r="C125" t="n">
-        <v>3.85906</v>
+        <v>2.46191</v>
       </c>
     </row>
     <row r="126">
@@ -1802,10 +1802,10 @@
         <v>1.24001</v>
       </c>
       <c r="B126" t="n">
-        <v>0.38845</v>
+        <v>0.24671</v>
       </c>
       <c r="C126" t="n">
-        <v>3.81066</v>
+        <v>2.42023</v>
       </c>
     </row>
     <row r="127">
@@ -1813,10 +1813,10 @@
         <v>1.25001</v>
       </c>
       <c r="B127" t="n">
-        <v>0.38346</v>
+        <v>0.24147</v>
       </c>
       <c r="C127" t="n">
-        <v>3.76176</v>
+        <v>2.36882</v>
       </c>
     </row>
     <row r="128">
@@ -1824,10 +1824,10 @@
         <v>1.26001</v>
       </c>
       <c r="B128" t="n">
-        <v>0.37844</v>
+        <v>0.2361</v>
       </c>
       <c r="C128" t="n">
-        <v>3.71252</v>
+        <v>2.31619</v>
       </c>
     </row>
     <row r="129">
@@ -1835,10 +1835,10 @@
         <v>1.27001</v>
       </c>
       <c r="B129" t="n">
-        <v>0.3734</v>
+        <v>0.23037</v>
       </c>
       <c r="C129" t="n">
-        <v>3.66305</v>
+        <v>2.25993</v>
       </c>
     </row>
     <row r="130">
@@ -1846,10 +1846,10 @@
         <v>1.28001</v>
       </c>
       <c r="B130" t="n">
-        <v>0.36835</v>
+        <v>0.22467</v>
       </c>
       <c r="C130" t="n">
-        <v>3.61348</v>
+        <v>2.20399</v>
       </c>
     </row>
     <row r="131">
@@ -1857,10 +1857,10 @@
         <v>1.29001</v>
       </c>
       <c r="B131" t="n">
-        <v>0.3633</v>
+        <v>0.21906</v>
       </c>
       <c r="C131" t="n">
-        <v>3.56394</v>
+        <v>2.14896</v>
       </c>
     </row>
     <row r="132">
@@ -1868,10 +1868,10 @@
         <v>1.30001</v>
       </c>
       <c r="B132" t="n">
-        <v>0.35826</v>
+        <v>0.21364</v>
       </c>
       <c r="C132" t="n">
-        <v>3.51455</v>
+        <v>2.09585</v>
       </c>
     </row>
     <row r="133">
@@ -1879,10 +1879,10 @@
         <v>1.31001</v>
       </c>
       <c r="B133" t="n">
-        <v>0.35325</v>
+        <v>0.20829</v>
       </c>
       <c r="C133" t="n">
-        <v>3.4654</v>
+        <v>2.0433</v>
       </c>
     </row>
     <row r="134">
@@ -1890,10 +1890,10 @@
         <v>1.32001</v>
       </c>
       <c r="B134" t="n">
-        <v>0.34828</v>
+        <v>0.20355</v>
       </c>
       <c r="C134" t="n">
-        <v>3.41661</v>
+        <v>1.99683</v>
       </c>
     </row>
     <row r="135">
@@ -1901,10 +1901,10 @@
         <v>1.33001</v>
       </c>
       <c r="B135" t="n">
-        <v>0.34335</v>
+        <v>0.19919</v>
       </c>
       <c r="C135" t="n">
-        <v>3.36827</v>
+        <v>1.95406</v>
       </c>
     </row>
     <row r="136">
@@ -1912,10 +1912,10 @@
         <v>1.34001</v>
       </c>
       <c r="B136" t="n">
-        <v>0.33848</v>
+        <v>0.19526</v>
       </c>
       <c r="C136" t="n">
-        <v>3.32047</v>
+        <v>1.91547</v>
       </c>
     </row>
     <row r="137">
@@ -1923,10 +1923,10 @@
         <v>1.35001</v>
       </c>
       <c r="B137" t="n">
-        <v>0.33367</v>
+        <v>0.19184</v>
       </c>
       <c r="C137" t="n">
-        <v>3.27329</v>
+        <v>1.88194</v>
       </c>
     </row>
     <row r="138">
@@ -1934,10 +1934,10 @@
         <v>1.36001</v>
       </c>
       <c r="B138" t="n">
-        <v>0.32893</v>
+        <v>0.18899</v>
       </c>
       <c r="C138" t="n">
-        <v>3.22681</v>
+        <v>1.85398</v>
       </c>
     </row>
     <row r="139">
@@ -1945,10 +1945,10 @@
         <v>1.37001</v>
       </c>
       <c r="B139" t="n">
-        <v>0.32427</v>
+        <v>0.18673</v>
       </c>
       <c r="C139" t="n">
-        <v>3.1811</v>
+        <v>1.83178</v>
       </c>
     </row>
     <row r="140">
@@ -1956,10 +1956,10 @@
         <v>1.38001</v>
       </c>
       <c r="B140" t="n">
-        <v>0.3197</v>
+        <v>0.18504</v>
       </c>
       <c r="C140" t="n">
-        <v>3.13622</v>
+        <v>1.81526</v>
       </c>
     </row>
     <row r="141">
@@ -1967,10 +1967,10 @@
         <v>1.39001</v>
       </c>
       <c r="B141" t="n">
-        <v>0.31521</v>
+        <v>0.18398</v>
       </c>
       <c r="C141" t="n">
-        <v>3.09224</v>
+        <v>1.80484</v>
       </c>
     </row>
     <row r="142">
@@ -1978,10 +1978,10 @@
         <v>1.40001</v>
       </c>
       <c r="B142" t="n">
-        <v>0.31083</v>
+        <v>0.18348</v>
       </c>
       <c r="C142" t="n">
-        <v>3.0492</v>
+        <v>1.79989</v>
       </c>
     </row>
     <row r="143">
@@ -1989,10 +1989,10 @@
         <v>1.41001</v>
       </c>
       <c r="B143" t="n">
-        <v>0.30654</v>
+        <v>0.1834</v>
       </c>
       <c r="C143" t="n">
-        <v>3.00715</v>
+        <v>1.79918</v>
       </c>
     </row>
     <row r="144">
@@ -2000,10 +2000,10 @@
         <v>1.42001</v>
       </c>
       <c r="B144" t="n">
-        <v>0.30236</v>
+        <v>0.18369</v>
       </c>
       <c r="C144" t="n">
-        <v>2.96614</v>
+        <v>1.802</v>
       </c>
     </row>
     <row r="145">
@@ -2011,10 +2011,10 @@
         <v>1.43001</v>
       </c>
       <c r="B145" t="n">
-        <v>0.29829</v>
+        <v>0.18426</v>
       </c>
       <c r="C145" t="n">
-        <v>2.9262</v>
+        <v>1.80755</v>
       </c>
     </row>
     <row r="146">
@@ -2022,10 +2022,10 @@
         <v>1.44001</v>
       </c>
       <c r="B146" t="n">
-        <v>0.29433</v>
+        <v>0.18501</v>
       </c>
       <c r="C146" t="n">
-        <v>2.88736</v>
+        <v>1.81498</v>
       </c>
     </row>
     <row r="147">
@@ -2033,10 +2033,10 @@
         <v>1.45001</v>
       </c>
       <c r="B147" t="n">
-        <v>0.29048</v>
+        <v>0.18588</v>
       </c>
       <c r="C147" t="n">
-        <v>2.84964</v>
+        <v>1.82343</v>
       </c>
     </row>
     <row r="148">
@@ -2044,10 +2044,10 @@
         <v>1.46001</v>
       </c>
       <c r="B148" t="n">
-        <v>0.28676</v>
+        <v>0.18675</v>
       </c>
       <c r="C148" t="n">
-        <v>2.81307</v>
+        <v>1.83206</v>
       </c>
     </row>
     <row r="149">
@@ -2055,10 +2055,10 @@
         <v>1.47001</v>
       </c>
       <c r="B149" t="n">
-        <v>0.28315</v>
+        <v>0.18757</v>
       </c>
       <c r="C149" t="n">
-        <v>2.77767</v>
+        <v>1.84007</v>
       </c>
     </row>
     <row r="150">
@@ -2066,10 +2066,10 @@
         <v>1.48001</v>
       </c>
       <c r="B150" t="n">
-        <v>0.27966</v>
+        <v>0.18856</v>
       </c>
       <c r="C150" t="n">
-        <v>2.74344</v>
+        <v>1.84979</v>
       </c>
     </row>
     <row r="151">
@@ -2077,10 +2077,10 @@
         <v>1.49001</v>
       </c>
       <c r="B151" t="n">
-        <v>0.27629</v>
+        <v>0.1894</v>
       </c>
       <c r="C151" t="n">
-        <v>2.71041</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="152">
@@ -2088,10 +2088,10 @@
         <v>1.50001</v>
       </c>
       <c r="B152" t="n">
-        <v>0.27304</v>
+        <v>0.18999</v>
       </c>
       <c r="C152" t="n">
-        <v>2.67856</v>
+        <v>1.86382</v>
       </c>
     </row>
     <row r="153">
@@ -2099,10 +2099,10 @@
         <v>1.51001</v>
       </c>
       <c r="B153" t="n">
-        <v>0.26992</v>
+        <v>0.19029</v>
       </c>
       <c r="C153" t="n">
-        <v>2.64792</v>
+        <v>1.86674</v>
       </c>
     </row>
     <row r="154">
@@ -2110,10 +2110,10 @@
         <v>1.52001</v>
       </c>
       <c r="B154" t="n">
-        <v>0.26692</v>
+        <v>0.19052</v>
       </c>
       <c r="C154" t="n">
-        <v>2.61847</v>
+        <v>1.869</v>
       </c>
     </row>
     <row r="155">
@@ -2121,10 +2121,10 @@
         <v>1.53001</v>
       </c>
       <c r="B155" t="n">
-        <v>0.26404</v>
+        <v>0.19055</v>
       </c>
       <c r="C155" t="n">
-        <v>2.59021</v>
+        <v>1.86929</v>
       </c>
     </row>
     <row r="156">
@@ -2132,10 +2132,10 @@
         <v>1.54001</v>
       </c>
       <c r="B156" t="n">
-        <v>0.26128</v>
+        <v>0.1902</v>
       </c>
       <c r="C156" t="n">
-        <v>2.56314</v>
+        <v>1.86582</v>
       </c>
     </row>
     <row r="157">
@@ -2143,10 +2143,10 @@
         <v>1.55001</v>
       </c>
       <c r="B157" t="n">
-        <v>0.25864</v>
+        <v>0.18984</v>
       </c>
       <c r="C157" t="n">
-        <v>2.53724</v>
+        <v>1.86233</v>
       </c>
     </row>
     <row r="158">
@@ -2154,10 +2154,10 @@
         <v>1.56001</v>
       </c>
       <c r="B158" t="n">
-        <v>0.25612</v>
+        <v>0.18913</v>
       </c>
       <c r="C158" t="n">
-        <v>2.51252</v>
+        <v>1.85539</v>
       </c>
     </row>
     <row r="159">
@@ -2165,10 +2165,10 @@
         <v>1.57001</v>
       </c>
       <c r="B159" t="n">
-        <v>0.25683</v>
+        <v>0.18836</v>
       </c>
       <c r="C159" t="n">
-        <v>2.51946</v>
+        <v>1.84778</v>
       </c>
     </row>
     <row r="160">
@@ -2176,10 +2176,10 @@
         <v>1.58001</v>
       </c>
       <c r="B160" t="n">
-        <v>0.2589</v>
+        <v>0.18729</v>
       </c>
       <c r="C160" t="n">
-        <v>2.53978</v>
+        <v>1.83732</v>
       </c>
     </row>
     <row r="161">
@@ -2187,10 +2187,10 @@
         <v>1.59001</v>
       </c>
       <c r="B161" t="n">
-        <v>0.25959</v>
+        <v>0.186</v>
       </c>
       <c r="C161" t="n">
-        <v>2.54657</v>
+        <v>1.8247</v>
       </c>
     </row>
     <row r="162">
@@ -2198,10 +2198,10 @@
         <v>1.60001</v>
       </c>
       <c r="B162" t="n">
-        <v>0.25892</v>
+        <v>0.1846</v>
       </c>
       <c r="C162" t="n">
-        <v>2.53999</v>
+        <v>1.81089</v>
       </c>
     </row>
     <row r="163">
@@ -2209,10 +2209,10 @@
         <v>1.61001</v>
       </c>
       <c r="B163" t="n">
-        <v>0.25693</v>
+        <v>0.18282</v>
       </c>
       <c r="C163" t="n">
-        <v>2.52053</v>
+        <v>1.79342</v>
       </c>
     </row>
     <row r="164">
@@ -2220,10 +2220,10 @@
         <v>1.62001</v>
       </c>
       <c r="B164" t="n">
-        <v>0.25371</v>
+        <v>0.18084</v>
       </c>
       <c r="C164" t="n">
-        <v>2.48894</v>
+        <v>1.77401</v>
       </c>
     </row>
     <row r="165">
@@ -2231,10 +2231,10 @@
         <v>1.63001</v>
       </c>
       <c r="B165" t="n">
-        <v>0.24936</v>
+        <v>0.1788</v>
       </c>
       <c r="C165" t="n">
-        <v>2.44619</v>
+        <v>1.75399</v>
       </c>
     </row>
     <row r="166">
@@ -2242,10 +2242,10 @@
         <v>1.64001</v>
       </c>
       <c r="B166" t="n">
-        <v>0.24398</v>
+        <v>0.17645</v>
       </c>
       <c r="C166" t="n">
-        <v>2.39343</v>
+        <v>1.731</v>
       </c>
     </row>
     <row r="167">
@@ -2253,10 +2253,10 @@
         <v>1.65001</v>
       </c>
       <c r="B167" t="n">
-        <v>0.23852</v>
+        <v>0.17398</v>
       </c>
       <c r="C167" t="n">
-        <v>2.3399</v>
+        <v>1.7067</v>
       </c>
     </row>
     <row r="168">
@@ -2264,10 +2264,10 @@
         <v>1.66001</v>
       </c>
       <c r="B168" t="n">
-        <v>0.23709</v>
+        <v>0.17149</v>
       </c>
       <c r="C168" t="n">
-        <v>2.3259</v>
+        <v>1.68229</v>
       </c>
     </row>
     <row r="169">
@@ -2275,10 +2275,10 @@
         <v>1.67001</v>
       </c>
       <c r="B169" t="n">
-        <v>0.23577</v>
+        <v>0.16879</v>
       </c>
       <c r="C169" t="n">
-        <v>2.31286</v>
+        <v>1.65582</v>
       </c>
     </row>
     <row r="170">
@@ -2286,10 +2286,10 @@
         <v>1.68001</v>
       </c>
       <c r="B170" t="n">
-        <v>0.23453</v>
+        <v>0.16614</v>
       </c>
       <c r="C170" t="n">
-        <v>2.30074</v>
+        <v>1.62985</v>
       </c>
     </row>
     <row r="171">
@@ -2297,10 +2297,10 @@
         <v>1.69001</v>
       </c>
       <c r="B171" t="n">
-        <v>0.23489</v>
+        <v>0.16439</v>
       </c>
       <c r="C171" t="n">
-        <v>2.30428</v>
+        <v>1.61265</v>
       </c>
     </row>
     <row r="172">
@@ -2308,10 +2308,10 @@
         <v>1.70001</v>
       </c>
       <c r="B172" t="n">
-        <v>0.2409</v>
+        <v>0.16267</v>
       </c>
       <c r="C172" t="n">
-        <v>2.36323</v>
+        <v>1.59584</v>
       </c>
     </row>
     <row r="173">
@@ -2319,10 +2319,10 @@
         <v>1.71001</v>
       </c>
       <c r="B173" t="n">
-        <v>0.24612</v>
+        <v>0.16092</v>
       </c>
       <c r="C173" t="n">
-        <v>2.41445</v>
+        <v>1.57866</v>
       </c>
     </row>
     <row r="174">
@@ -2330,10 +2330,10 @@
         <v>1.72001</v>
       </c>
       <c r="B174" t="n">
-        <v>0.25058</v>
+        <v>0.15864</v>
       </c>
       <c r="C174" t="n">
-        <v>2.45818</v>
+        <v>1.55627</v>
       </c>
     </row>
     <row r="175">
@@ -2341,10 +2341,10 @@
         <v>1.73001</v>
       </c>
       <c r="B175" t="n">
-        <v>0.25431</v>
+        <v>0.15588</v>
       </c>
       <c r="C175" t="n">
-        <v>2.49479</v>
+        <v>1.52921</v>
       </c>
     </row>
     <row r="176">
@@ -2352,10 +2352,10 @@
         <v>1.74001</v>
       </c>
       <c r="B176" t="n">
-        <v>0.25737</v>
+        <v>0.153</v>
       </c>
       <c r="C176" t="n">
-        <v>2.52476</v>
+        <v>1.50093</v>
       </c>
     </row>
     <row r="177">
@@ -2363,10 +2363,10 @@
         <v>1.75001</v>
       </c>
       <c r="B177" t="n">
-        <v>0.2598</v>
+        <v>0.15038</v>
       </c>
       <c r="C177" t="n">
-        <v>2.54862</v>
+        <v>1.47521</v>
       </c>
     </row>
     <row r="178">
@@ -2374,10 +2374,10 @@
         <v>1.76001</v>
       </c>
       <c r="B178" t="n">
-        <v>0.26167</v>
+        <v>0.14991</v>
       </c>
       <c r="C178" t="n">
-        <v>2.56696</v>
+        <v>1.47066</v>
       </c>
     </row>
     <row r="179">
@@ -2385,10 +2385,10 @@
         <v>1.77001</v>
       </c>
       <c r="B179" t="n">
-        <v>0.26304</v>
+        <v>0.15107</v>
       </c>
       <c r="C179" t="n">
-        <v>2.58038</v>
+        <v>1.48197</v>
       </c>
     </row>
     <row r="180">
@@ -2396,10 +2396,10 @@
         <v>1.78001</v>
       </c>
       <c r="B180" t="n">
-        <v>0.26397</v>
+        <v>0.15206</v>
       </c>
       <c r="C180" t="n">
-        <v>2.5895</v>
+        <v>1.49169</v>
       </c>
     </row>
     <row r="181">
@@ -2407,10 +2407,10 @@
         <v>1.79001</v>
       </c>
       <c r="B181" t="n">
-        <v>0.26452</v>
+        <v>0.15265</v>
       </c>
       <c r="C181" t="n">
-        <v>2.59491</v>
+        <v>1.49746</v>
       </c>
     </row>
     <row r="182">
@@ -2418,10 +2418,10 @@
         <v>1.80001</v>
       </c>
       <c r="B182" t="n">
-        <v>0.26475</v>
+        <v>0.15297</v>
       </c>
       <c r="C182" t="n">
-        <v>2.59718</v>
+        <v>1.50065</v>
       </c>
     </row>
     <row r="183">
@@ -2429,10 +2429,10 @@
         <v>1.81001</v>
       </c>
       <c r="B183" t="n">
-        <v>0.26471</v>
+        <v>0.15486</v>
       </c>
       <c r="C183" t="n">
-        <v>2.59681</v>
+        <v>1.51917</v>
       </c>
     </row>
     <row r="184">
@@ -2440,10 +2440,10 @@
         <v>1.82001</v>
       </c>
       <c r="B184" t="n">
-        <v>0.26445</v>
+        <v>0.1563</v>
       </c>
       <c r="C184" t="n">
-        <v>2.59426</v>
+        <v>1.53329</v>
       </c>
     </row>
     <row r="185">
@@ -2451,10 +2451,10 @@
         <v>1.83001</v>
       </c>
       <c r="B185" t="n">
-        <v>0.26401</v>
+        <v>0.15726</v>
       </c>
       <c r="C185" t="n">
-        <v>2.58993</v>
+        <v>1.54269</v>
       </c>
     </row>
     <row r="186">
@@ -2462,10 +2462,10 @@
         <v>1.84001</v>
       </c>
       <c r="B186" t="n">
-        <v>0.26342</v>
+        <v>0.15763</v>
       </c>
       <c r="C186" t="n">
-        <v>2.58415</v>
+        <v>1.54631</v>
       </c>
     </row>
     <row r="187">
@@ -2473,10 +2473,10 @@
         <v>1.85001</v>
       </c>
       <c r="B187" t="n">
-        <v>0.26271</v>
+        <v>0.1578</v>
       </c>
       <c r="C187" t="n">
-        <v>2.57717</v>
+        <v>1.54806</v>
       </c>
     </row>
     <row r="188">
@@ -2484,10 +2484,10 @@
         <v>1.86001</v>
       </c>
       <c r="B188" t="n">
-        <v>0.26189</v>
+        <v>0.1574</v>
       </c>
       <c r="C188" t="n">
-        <v>2.56918</v>
+        <v>1.54412</v>
       </c>
     </row>
     <row r="189">
@@ -2495,10 +2495,10 @@
         <v>1.87001</v>
       </c>
       <c r="B189" t="n">
-        <v>0.26099</v>
+        <v>0.15691</v>
       </c>
       <c r="C189" t="n">
-        <v>2.56029</v>
+        <v>1.53926</v>
       </c>
     </row>
     <row r="190">
@@ -2506,10 +2506,10 @@
         <v>1.88001</v>
       </c>
       <c r="B190" t="n">
-        <v>0.25999</v>
+        <v>0.1559</v>
       </c>
       <c r="C190" t="n">
-        <v>2.55055</v>
+        <v>1.52935</v>
       </c>
     </row>
     <row r="191">
@@ -2517,10 +2517,10 @@
         <v>1.89001</v>
       </c>
       <c r="B191" t="n">
-        <v>0.25891</v>
+        <v>0.15479</v>
       </c>
       <c r="C191" t="n">
-        <v>2.53995</v>
+        <v>1.51846</v>
       </c>
     </row>
     <row r="192">
@@ -2528,10 +2528,10 @@
         <v>1.90001</v>
       </c>
       <c r="B192" t="n">
-        <v>0.25774</v>
+        <v>0.15329</v>
       </c>
       <c r="C192" t="n">
-        <v>2.52844</v>
+        <v>1.50373</v>
       </c>
     </row>
     <row r="193">
@@ -2539,10 +2539,10 @@
         <v>1.91001</v>
       </c>
       <c r="B193" t="n">
-        <v>0.2566</v>
+        <v>0.15158</v>
       </c>
       <c r="C193" t="n">
-        <v>2.5172</v>
+        <v>1.487</v>
       </c>
     </row>
     <row r="194">
@@ -2550,10 +2550,10 @@
         <v>1.92001</v>
       </c>
       <c r="B194" t="n">
-        <v>0.2555</v>
+        <v>0.14958</v>
       </c>
       <c r="C194" t="n">
-        <v>2.50647</v>
+        <v>1.46737</v>
       </c>
     </row>
     <row r="195">
@@ -2561,10 +2561,10 @@
         <v>1.93001</v>
       </c>
       <c r="B195" t="n">
-        <v>0.25427</v>
+        <v>0.14727</v>
       </c>
       <c r="C195" t="n">
-        <v>2.49438</v>
+        <v>1.44471</v>
       </c>
     </row>
     <row r="196">
@@ -2572,10 +2572,10 @@
         <v>1.94001</v>
       </c>
       <c r="B196" t="n">
-        <v>0.25288</v>
+        <v>0.1447</v>
       </c>
       <c r="C196" t="n">
-        <v>2.48075</v>
+        <v>1.41947</v>
       </c>
     </row>
     <row r="197">
@@ -2583,10 +2583,10 @@
         <v>1.95001</v>
       </c>
       <c r="B197" t="n">
-        <v>0.25131</v>
+        <v>0.14176</v>
       </c>
       <c r="C197" t="n">
-        <v>2.46539</v>
+        <v>1.39064</v>
       </c>
     </row>
     <row r="198">
@@ -2594,10 +2594,10 @@
         <v>1.96001</v>
       </c>
       <c r="B198" t="n">
-        <v>0.24955</v>
+        <v>0.13966</v>
       </c>
       <c r="C198" t="n">
-        <v>2.44809</v>
+        <v>1.37006</v>
       </c>
     </row>
     <row r="199">
@@ -2605,10 +2605,10 @@
         <v>1.97001</v>
       </c>
       <c r="B199" t="n">
-        <v>0.24757</v>
+        <v>0.13858</v>
       </c>
       <c r="C199" t="n">
-        <v>2.42865</v>
+        <v>1.35951</v>
       </c>
     </row>
     <row r="200">
@@ -2616,10 +2616,10 @@
         <v>1.98001</v>
       </c>
       <c r="B200" t="n">
-        <v>0.24535</v>
+        <v>0.13782</v>
       </c>
       <c r="C200" t="n">
-        <v>2.40687</v>
+        <v>1.35198</v>
       </c>
     </row>
     <row r="201">
@@ -2627,10 +2627,10 @@
         <v>1.99001</v>
       </c>
       <c r="B201" t="n">
-        <v>0.24287</v>
+        <v>0.13703</v>
       </c>
       <c r="C201" t="n">
-        <v>2.38258</v>
+        <v>1.3443</v>
       </c>
     </row>
     <row r="202">
@@ -2638,10 +2638,10 @@
         <v>2.00001</v>
       </c>
       <c r="B202" t="n">
-        <v>0.24013</v>
+        <v>0.13827</v>
       </c>
       <c r="C202" t="n">
-        <v>2.35563</v>
+        <v>1.35646</v>
       </c>
     </row>
     <row r="203">
@@ -2649,10 +2649,10 @@
         <v>2.01001</v>
       </c>
       <c r="B203" t="n">
-        <v>0.23709</v>
+        <v>0.13974</v>
       </c>
       <c r="C203" t="n">
-        <v>2.32588</v>
+        <v>1.37087</v>
       </c>
     </row>
     <row r="204">
@@ -2660,10 +2660,10 @@
         <v>2.02001</v>
       </c>
       <c r="B204" t="n">
-        <v>0.23376</v>
+        <v>0.14124</v>
       </c>
       <c r="C204" t="n">
-        <v>2.29323</v>
+        <v>1.38555</v>
       </c>
     </row>
     <row r="205">
@@ -2671,10 +2671,10 @@
         <v>2.03001</v>
       </c>
       <c r="B205" t="n">
-        <v>0.23212</v>
+        <v>0.14275</v>
       </c>
       <c r="C205" t="n">
-        <v>2.2771</v>
+        <v>1.40033</v>
       </c>
     </row>
     <row r="206">
@@ -2682,10 +2682,10 @@
         <v>2.04001</v>
       </c>
       <c r="B206" t="n">
-        <v>0.23283</v>
+        <v>0.14429</v>
       </c>
       <c r="C206" t="n">
-        <v>2.28402</v>
+        <v>1.41553</v>
       </c>
     </row>
     <row r="207">
@@ -2693,10 +2693,10 @@
         <v>2.05001</v>
       </c>
       <c r="B207" t="n">
-        <v>0.23355</v>
+        <v>0.14591</v>
       </c>
       <c r="C207" t="n">
-        <v>2.2911</v>
+        <v>1.43134</v>
       </c>
     </row>
     <row r="208">
@@ -2704,10 +2704,10 @@
         <v>2.06001</v>
       </c>
       <c r="B208" t="n">
-        <v>0.23428</v>
+        <v>0.14749</v>
       </c>
       <c r="C208" t="n">
-        <v>2.29831</v>
+        <v>1.44683</v>
       </c>
     </row>
     <row r="209">
@@ -2715,10 +2715,10 @@
         <v>2.07001</v>
       </c>
       <c r="B209" t="n">
-        <v>0.23503</v>
+        <v>0.14903</v>
       </c>
       <c r="C209" t="n">
-        <v>2.30564</v>
+        <v>1.46202</v>
       </c>
     </row>
     <row r="210">
@@ -2726,10 +2726,10 @@
         <v>2.08001</v>
       </c>
       <c r="B210" t="n">
-        <v>0.23579</v>
+        <v>0.15067</v>
       </c>
       <c r="C210" t="n">
-        <v>2.31309</v>
+        <v>1.47803</v>
       </c>
     </row>
     <row r="211">
@@ -2737,10 +2737,10 @@
         <v>2.09001</v>
       </c>
       <c r="B211" t="n">
-        <v>0.23656</v>
+        <v>0.15223</v>
       </c>
       <c r="C211" t="n">
-        <v>2.32065</v>
+        <v>1.49336</v>
       </c>
     </row>
     <row r="212">
@@ -2748,10 +2748,10 @@
         <v>2.10001</v>
       </c>
       <c r="B212" t="n">
-        <v>0.23734</v>
+        <v>0.15372</v>
       </c>
       <c r="C212" t="n">
-        <v>2.3283</v>
+        <v>1.508</v>
       </c>
     </row>
     <row r="213">
@@ -2759,10 +2759,10 @@
         <v>2.11001</v>
       </c>
       <c r="B213" t="n">
-        <v>0.23813</v>
+        <v>0.15529</v>
       </c>
       <c r="C213" t="n">
-        <v>2.33604</v>
+        <v>1.52338</v>
       </c>
     </row>
     <row r="214">
@@ -2770,10 +2770,10 @@
         <v>2.12001</v>
       </c>
       <c r="B214" t="n">
-        <v>0.23893</v>
+        <v>0.15675</v>
       </c>
       <c r="C214" t="n">
-        <v>2.34386</v>
+        <v>1.53776</v>
       </c>
     </row>
     <row r="215">
@@ -2781,10 +2781,10 @@
         <v>2.13001</v>
       </c>
       <c r="B215" t="n">
-        <v>0.23973</v>
+        <v>0.15811</v>
       </c>
       <c r="C215" t="n">
-        <v>2.35174</v>
+        <v>1.55101</v>
       </c>
     </row>
     <row r="216">
@@ -2792,10 +2792,10 @@
         <v>2.14001</v>
       </c>
       <c r="B216" t="n">
-        <v>0.24054</v>
+        <v>0.15953</v>
       </c>
       <c r="C216" t="n">
-        <v>2.35969</v>
+        <v>1.56498</v>
       </c>
     </row>
     <row r="217">
@@ -2803,10 +2803,10 @@
         <v>2.15001</v>
       </c>
       <c r="B217" t="n">
-        <v>0.24136</v>
+        <v>0.16083</v>
       </c>
       <c r="C217" t="n">
-        <v>2.3677</v>
+        <v>1.57773</v>
       </c>
     </row>
     <row r="218">
@@ -2814,10 +2814,10 @@
         <v>2.16001</v>
       </c>
       <c r="B218" t="n">
-        <v>0.24218</v>
+        <v>0.16203</v>
       </c>
       <c r="C218" t="n">
-        <v>2.37574</v>
+        <v>1.58955</v>
       </c>
     </row>
     <row r="219">
@@ -2825,10 +2825,10 @@
         <v>2.17001</v>
       </c>
       <c r="B219" t="n">
-        <v>0.243</v>
+        <v>0.16327</v>
       </c>
       <c r="C219" t="n">
-        <v>2.38383</v>
+        <v>1.60164</v>
       </c>
     </row>
     <row r="220">
@@ -2836,10 +2836,10 @@
         <v>2.18001</v>
       </c>
       <c r="B220" t="n">
-        <v>0.24383</v>
+        <v>0.16434</v>
       </c>
       <c r="C220" t="n">
-        <v>2.39195</v>
+        <v>1.61222</v>
       </c>
     </row>
     <row r="221">
@@ -2847,10 +2847,10 @@
         <v>2.19001</v>
       </c>
       <c r="B221" t="n">
-        <v>0.24466</v>
+        <v>0.16544</v>
       </c>
       <c r="C221" t="n">
-        <v>2.4001</v>
+        <v>1.62297</v>
       </c>
     </row>
     <row r="222">
@@ -2858,10 +2858,10 @@
         <v>2.20001</v>
       </c>
       <c r="B222" t="n">
-        <v>0.24549</v>
+        <v>0.16642</v>
       </c>
       <c r="C222" t="n">
-        <v>2.40827</v>
+        <v>1.63263</v>
       </c>
     </row>
     <row r="223">
@@ -2869,10 +2869,10 @@
         <v>2.21001</v>
       </c>
       <c r="B223" t="n">
-        <v>0.24632</v>
+        <v>0.16736</v>
       </c>
       <c r="C223" t="n">
-        <v>2.41645</v>
+        <v>1.64176</v>
       </c>
     </row>
     <row r="224">
@@ -2880,10 +2880,10 @@
         <v>2.22001</v>
       </c>
       <c r="B224" t="n">
-        <v>0.24716</v>
+        <v>0.16823</v>
       </c>
       <c r="C224" t="n">
-        <v>2.42464</v>
+        <v>1.65038</v>
       </c>
     </row>
     <row r="225">
@@ -2891,10 +2891,10 @@
         <v>2.23001</v>
       </c>
       <c r="B225" t="n">
-        <v>0.24799</v>
+        <v>0.16903</v>
       </c>
       <c r="C225" t="n">
-        <v>2.43283</v>
+        <v>1.65819</v>
       </c>
     </row>
     <row r="226">
@@ -2902,10 +2902,10 @@
         <v>2.24001</v>
       </c>
       <c r="B226" t="n">
-        <v>0.24883</v>
+        <v>0.16979</v>
       </c>
       <c r="C226" t="n">
-        <v>2.44102</v>
+        <v>1.66568</v>
       </c>
     </row>
     <row r="227">
@@ -2913,10 +2913,10 @@
         <v>2.25001</v>
       </c>
       <c r="B227" t="n">
-        <v>0.24966</v>
+        <v>0.17049</v>
       </c>
       <c r="C227" t="n">
-        <v>2.44921</v>
+        <v>1.67251</v>
       </c>
     </row>
     <row r="228">
@@ -2924,10 +2924,10 @@
         <v>2.26001</v>
       </c>
       <c r="B228" t="n">
-        <v>0.2505</v>
+        <v>0.17113</v>
       </c>
       <c r="C228" t="n">
-        <v>2.45738</v>
+        <v>1.67879</v>
       </c>
     </row>
     <row r="229">
@@ -2935,10 +2935,10 @@
         <v>2.27001</v>
       </c>
       <c r="B229" t="n">
-        <v>0.25133</v>
+        <v>0.17168</v>
       </c>
       <c r="C229" t="n">
-        <v>2.46553</v>
+        <v>1.68416</v>
       </c>
     </row>
     <row r="230">
@@ -2946,10 +2946,10 @@
         <v>2.28001</v>
       </c>
       <c r="B230" t="n">
-        <v>0.25216</v>
+        <v>0.17219</v>
       </c>
       <c r="C230" t="n">
-        <v>2.47367</v>
+        <v>1.68918</v>
       </c>
     </row>
     <row r="231">
@@ -2957,10 +2957,10 @@
         <v>2.29001</v>
       </c>
       <c r="B231" t="n">
-        <v>0.25299</v>
+        <v>0.17251</v>
       </c>
       <c r="C231" t="n">
-        <v>2.48179</v>
+        <v>1.69231</v>
       </c>
     </row>
     <row r="232">
@@ -2968,10 +2968,10 @@
         <v>2.30001</v>
       </c>
       <c r="B232" t="n">
-        <v>0.25381</v>
+        <v>0.17289</v>
       </c>
       <c r="C232" t="n">
-        <v>2.48987</v>
+        <v>1.69602</v>
       </c>
     </row>
     <row r="233">
@@ -2979,10 +2979,10 @@
         <v>2.31001</v>
       </c>
       <c r="B233" t="n">
-        <v>0.25463</v>
+        <v>0.17306</v>
       </c>
       <c r="C233" t="n">
-        <v>2.49793</v>
+        <v>1.69776</v>
       </c>
     </row>
     <row r="234">
@@ -2990,10 +2990,10 @@
         <v>2.32001</v>
       </c>
       <c r="B234" t="n">
-        <v>0.25545</v>
+        <v>0.17319</v>
       </c>
       <c r="C234" t="n">
-        <v>2.50595</v>
+        <v>1.69898</v>
       </c>
     </row>
     <row r="235">
@@ -3001,10 +3001,10 @@
         <v>2.33001</v>
       </c>
       <c r="B235" t="n">
-        <v>0.25626</v>
+        <v>0.17323</v>
       </c>
       <c r="C235" t="n">
-        <v>2.51393</v>
+        <v>1.69938</v>
       </c>
     </row>
     <row r="236">
@@ -3012,10 +3012,10 @@
         <v>2.34001</v>
       </c>
       <c r="B236" t="n">
-        <v>0.25707</v>
+        <v>0.17307</v>
       </c>
       <c r="C236" t="n">
-        <v>2.52188</v>
+        <v>1.69779</v>
       </c>
     </row>
     <row r="237">
@@ -3023,10 +3023,10 @@
         <v>2.35001</v>
       </c>
       <c r="B237" t="n">
-        <v>0.25788</v>
+        <v>0.17297</v>
       </c>
       <c r="C237" t="n">
-        <v>2.52978</v>
+        <v>1.69681</v>
       </c>
     </row>
     <row r="238">
@@ -3034,10 +3034,10 @@
         <v>2.36001</v>
       </c>
       <c r="B238" t="n">
-        <v>0.25868</v>
+        <v>0.17281</v>
       </c>
       <c r="C238" t="n">
-        <v>2.53763</v>
+        <v>1.69527</v>
       </c>
     </row>
     <row r="239">
@@ -3045,10 +3045,10 @@
         <v>2.37001</v>
       </c>
       <c r="B239" t="n">
-        <v>0.25947</v>
+        <v>0.17387</v>
       </c>
       <c r="C239" t="n">
-        <v>2.54544</v>
+        <v>1.70564</v>
       </c>
     </row>
     <row r="240">
@@ -3056,10 +3056,10 @@
         <v>2.38001</v>
       </c>
       <c r="B240" t="n">
-        <v>0.26026</v>
+        <v>0.17481</v>
       </c>
       <c r="C240" t="n">
-        <v>2.55319</v>
+        <v>1.71487</v>
       </c>
     </row>
     <row r="241">
@@ -3067,10 +3067,10 @@
         <v>2.39001</v>
       </c>
       <c r="B241" t="n">
-        <v>0.26105</v>
+        <v>0.17563</v>
       </c>
       <c r="C241" t="n">
-        <v>2.5609</v>
+        <v>1.72295</v>
       </c>
     </row>
     <row r="242">
@@ -3078,10 +3078,10 @@
         <v>2.40001</v>
       </c>
       <c r="B242" t="n">
-        <v>0.26183</v>
+        <v>0.1764</v>
       </c>
       <c r="C242" t="n">
-        <v>2.56855</v>
+        <v>1.73052</v>
       </c>
     </row>
     <row r="243">
@@ -3089,10 +3089,10 @@
         <v>2.41001</v>
       </c>
       <c r="B243" t="n">
-        <v>0.2626</v>
+        <v>0.17716</v>
       </c>
       <c r="C243" t="n">
-        <v>2.57614</v>
+        <v>1.73794</v>
       </c>
     </row>
     <row r="244">
@@ -3100,10 +3100,10 @@
         <v>2.42001</v>
       </c>
       <c r="B244" t="n">
-        <v>0.26337</v>
+        <v>0.1778</v>
       </c>
       <c r="C244" t="n">
-        <v>2.58368</v>
+        <v>1.74421</v>
       </c>
     </row>
     <row r="245">
@@ -3111,10 +3111,10 @@
         <v>2.43001</v>
       </c>
       <c r="B245" t="n">
-        <v>0.26413</v>
+        <v>0.17832</v>
       </c>
       <c r="C245" t="n">
-        <v>2.59115</v>
+        <v>1.74933</v>
       </c>
     </row>
     <row r="246">
@@ -3122,10 +3122,10 @@
         <v>2.44001</v>
       </c>
       <c r="B246" t="n">
-        <v>0.26489</v>
+        <v>0.17873</v>
       </c>
       <c r="C246" t="n">
-        <v>2.59856</v>
+        <v>1.75331</v>
       </c>
     </row>
     <row r="247">
@@ -3133,10 +3133,10 @@
         <v>2.45001</v>
       </c>
       <c r="B247" t="n">
-        <v>0.26564</v>
+        <v>0.17912</v>
       </c>
       <c r="C247" t="n">
-        <v>2.60591</v>
+        <v>1.75714</v>
       </c>
     </row>
     <row r="248">
@@ -3144,10 +3144,10 @@
         <v>2.46001</v>
       </c>
       <c r="B248" t="n">
-        <v>0.26638</v>
+        <v>0.17946</v>
       </c>
       <c r="C248" t="n">
-        <v>2.6132</v>
+        <v>1.76051</v>
       </c>
     </row>
     <row r="249">
@@ -3155,10 +3155,10 @@
         <v>2.47001</v>
       </c>
       <c r="B249" t="n">
-        <v>0.26712</v>
+        <v>0.17969</v>
       </c>
       <c r="C249" t="n">
-        <v>2.62042</v>
+        <v>1.76275</v>
       </c>
     </row>
     <row r="250">
@@ -3166,10 +3166,10 @@
         <v>2.48001</v>
       </c>
       <c r="B250" t="n">
-        <v>0.26785</v>
+        <v>0.1798</v>
       </c>
       <c r="C250" t="n">
-        <v>2.62758</v>
+        <v>1.76387</v>
       </c>
     </row>
     <row r="251">
@@ -3177,10 +3177,10 @@
         <v>2.49001</v>
       </c>
       <c r="B251" t="n">
-        <v>0.26857</v>
+        <v>0.1798</v>
       </c>
       <c r="C251" t="n">
-        <v>2.63466</v>
+        <v>1.76388</v>
       </c>
     </row>
     <row r="252">
@@ -3188,10 +3188,10 @@
         <v>2.50001</v>
       </c>
       <c r="B252" t="n">
-        <v>0.26928</v>
+        <v>0.17977</v>
       </c>
       <c r="C252" t="n">
-        <v>2.64168</v>
+        <v>1.76359</v>
       </c>
     </row>
     <row r="253">
@@ -3199,10 +3199,10 @@
         <v>2.51001</v>
       </c>
       <c r="B253" t="n">
-        <v>0.26999</v>
+        <v>0.17972</v>
       </c>
       <c r="C253" t="n">
-        <v>2.64863</v>
+        <v>1.76309</v>
       </c>
     </row>
     <row r="254">
@@ -3210,10 +3210,10 @@
         <v>2.52001</v>
       </c>
       <c r="B254" t="n">
-        <v>0.27069</v>
+        <v>0.17956</v>
       </c>
       <c r="C254" t="n">
-        <v>2.65552</v>
+        <v>1.76151</v>
       </c>
     </row>
     <row r="255">
@@ -3221,10 +3221,10 @@
         <v>2.53001</v>
       </c>
       <c r="B255" t="n">
-        <v>0.27139</v>
+        <v>0.17929</v>
       </c>
       <c r="C255" t="n">
-        <v>2.66233</v>
+        <v>1.75887</v>
       </c>
     </row>
     <row r="256">
@@ -3232,10 +3232,10 @@
         <v>2.54001</v>
       </c>
       <c r="B256" t="n">
-        <v>0.27208</v>
+        <v>0.17892</v>
       </c>
       <c r="C256" t="n">
-        <v>2.66906</v>
+        <v>1.75519</v>
       </c>
     </row>
     <row r="257">
@@ -3243,10 +3243,10 @@
         <v>2.55001</v>
       </c>
       <c r="B257" t="n">
-        <v>0.27276</v>
+        <v>0.17844</v>
       </c>
       <c r="C257" t="n">
-        <v>2.67573</v>
+        <v>1.75049</v>
       </c>
     </row>
     <row r="258">
@@ -3254,10 +3254,10 @@
         <v>2.56001</v>
       </c>
       <c r="B258" t="n">
-        <v>0.27343</v>
+        <v>0.17802</v>
       </c>
       <c r="C258" t="n">
-        <v>2.68233</v>
+        <v>1.74638</v>
       </c>
     </row>
     <row r="259">
@@ -3265,10 +3265,10 @@
         <v>2.57001</v>
       </c>
       <c r="B259" t="n">
-        <v>0.27409</v>
+        <v>0.1775</v>
       </c>
       <c r="C259" t="n">
-        <v>2.68885</v>
+        <v>1.7413</v>
       </c>
     </row>
     <row r="260">
@@ -3276,10 +3276,10 @@
         <v>2.58001</v>
       </c>
       <c r="B260" t="n">
-        <v>0.27475</v>
+        <v>0.17689</v>
       </c>
       <c r="C260" t="n">
-        <v>2.6953</v>
+        <v>1.73524</v>
       </c>
     </row>
     <row r="261">
@@ -3287,10 +3287,10 @@
         <v>2.59001</v>
       </c>
       <c r="B261" t="n">
-        <v>0.2754</v>
+        <v>0.17617</v>
       </c>
       <c r="C261" t="n">
-        <v>2.70168</v>
+        <v>1.72823</v>
       </c>
     </row>
     <row r="262">
@@ -3298,10 +3298,10 @@
         <v>2.60001</v>
       </c>
       <c r="B262" t="n">
-        <v>0.27604</v>
+        <v>0.17536</v>
       </c>
       <c r="C262" t="n">
-        <v>2.70799</v>
+        <v>1.72028</v>
       </c>
     </row>
     <row r="263">
@@ -3309,10 +3309,10 @@
         <v>2.61001</v>
       </c>
       <c r="B263" t="n">
-        <v>0.27668</v>
+        <v>0.17446</v>
       </c>
       <c r="C263" t="n">
-        <v>2.71422</v>
+        <v>1.71148</v>
       </c>
     </row>
     <row r="264">
@@ -3320,10 +3320,10 @@
         <v>2.62001</v>
       </c>
       <c r="B264" t="n">
-        <v>0.27731</v>
+        <v>0.17363</v>
       </c>
       <c r="C264" t="n">
-        <v>2.72038</v>
+        <v>1.70328</v>
       </c>
     </row>
     <row r="265">
@@ -3331,10 +3331,10 @@
         <v>2.63001</v>
       </c>
       <c r="B265" t="n">
-        <v>0.27793</v>
+        <v>0.1727</v>
       </c>
       <c r="C265" t="n">
-        <v>2.72646</v>
+        <v>1.6942</v>
       </c>
     </row>
     <row r="266">
@@ -3342,10 +3342,10 @@
         <v>2.64001</v>
       </c>
       <c r="B266" t="n">
-        <v>0.27854</v>
+        <v>0.17169</v>
       </c>
       <c r="C266" t="n">
-        <v>2.73247</v>
+        <v>1.68426</v>
       </c>
     </row>
     <row r="267">
@@ -3353,10 +3353,10 @@
         <v>2.65001</v>
       </c>
       <c r="B267" t="n">
-        <v>0.27915</v>
+        <v>0.17059</v>
       </c>
       <c r="C267" t="n">
-        <v>2.73841</v>
+        <v>1.67348</v>
       </c>
     </row>
     <row r="268">
@@ -3364,10 +3364,10 @@
         <v>2.66001</v>
       </c>
       <c r="B268" t="n">
-        <v>0.27974</v>
+        <v>0.16943</v>
       </c>
       <c r="C268" t="n">
-        <v>2.74428</v>
+        <v>1.66213</v>
       </c>
     </row>
     <row r="269">
@@ -3375,10 +3375,10 @@
         <v>2.67001</v>
       </c>
       <c r="B269" t="n">
-        <v>0.28033</v>
+        <v>0.16832</v>
       </c>
       <c r="C269" t="n">
-        <v>2.75007</v>
+        <v>1.65123</v>
       </c>
     </row>
     <row r="270">
@@ -3386,10 +3386,10 @@
         <v>2.68001</v>
       </c>
       <c r="B270" t="n">
-        <v>0.28092</v>
+        <v>0.16713</v>
       </c>
       <c r="C270" t="n">
-        <v>2.75579</v>
+        <v>1.63954</v>
       </c>
     </row>
     <row r="271">
@@ -3397,10 +3397,10 @@
         <v>2.69001</v>
       </c>
       <c r="B271" t="n">
-        <v>0.28149</v>
+        <v>0.16586</v>
       </c>
       <c r="C271" t="n">
-        <v>2.76144</v>
+        <v>1.62711</v>
       </c>
     </row>
     <row r="272">
@@ -3408,10 +3408,10 @@
         <v>2.70001</v>
       </c>
       <c r="B272" t="n">
-        <v>0.28206</v>
+        <v>0.16466</v>
       </c>
       <c r="C272" t="n">
-        <v>2.76701</v>
+        <v>1.61536</v>
       </c>
     </row>
     <row r="273">
@@ -3419,10 +3419,10 @@
         <v>2.71001</v>
       </c>
       <c r="B273" t="n">
-        <v>0.28262</v>
+        <v>0.16339</v>
       </c>
       <c r="C273" t="n">
-        <v>2.77251</v>
+        <v>1.60287</v>
       </c>
     </row>
     <row r="274">
@@ -3430,10 +3430,10 @@
         <v>2.72001</v>
       </c>
       <c r="B274" t="n">
-        <v>0.28317</v>
+        <v>0.16214</v>
       </c>
       <c r="C274" t="n">
-        <v>2.77794</v>
+        <v>1.59057</v>
       </c>
     </row>
     <row r="275">
@@ -3441,10 +3441,10 @@
         <v>2.73001</v>
       </c>
       <c r="B275" t="n">
-        <v>0.28372</v>
+        <v>0.16087</v>
       </c>
       <c r="C275" t="n">
-        <v>2.7833</v>
+        <v>1.57812</v>
       </c>
     </row>
     <row r="276">
@@ -3452,10 +3452,10 @@
         <v>2.74001</v>
       </c>
       <c r="B276" t="n">
-        <v>0.28426</v>
+        <v>0.15967</v>
       </c>
       <c r="C276" t="n">
-        <v>2.78859</v>
+        <v>1.56632</v>
       </c>
     </row>
     <row r="277">
@@ -3463,10 +3463,10 @@
         <v>2.75001</v>
       </c>
       <c r="B277" t="n">
-        <v>0.28479</v>
+        <v>0.15839</v>
       </c>
       <c r="C277" t="n">
-        <v>2.79381</v>
+        <v>1.55382</v>
       </c>
     </row>
     <row r="278">
@@ -3474,10 +3474,10 @@
         <v>2.76001</v>
       </c>
       <c r="B278" t="n">
-        <v>0.28532</v>
+        <v>0.15717</v>
       </c>
       <c r="C278" t="n">
-        <v>2.79895</v>
+        <v>1.54188</v>
       </c>
     </row>
     <row r="279">
@@ -3485,10 +3485,10 @@
         <v>2.77001</v>
       </c>
       <c r="B279" t="n">
-        <v>0.28583</v>
+        <v>0.15626</v>
       </c>
       <c r="C279" t="n">
-        <v>2.80403</v>
+        <v>1.53291</v>
       </c>
     </row>
     <row r="280">
@@ -3496,10 +3496,10 @@
         <v>2.78001</v>
       </c>
       <c r="B280" t="n">
-        <v>0.28634</v>
+        <v>0.1562</v>
       </c>
       <c r="C280" t="n">
-        <v>2.80904</v>
+        <v>1.53228</v>
       </c>
     </row>
     <row r="281">
@@ -3507,10 +3507,10 @@
         <v>2.79001</v>
       </c>
       <c r="B281" t="n">
-        <v>0.28685</v>
+        <v>0.15602</v>
       </c>
       <c r="C281" t="n">
-        <v>2.81397</v>
+        <v>1.53053</v>
       </c>
     </row>
     <row r="282">
@@ -3518,10 +3518,10 @@
         <v>2.80001</v>
       </c>
       <c r="B282" t="n">
-        <v>0.28734</v>
+        <v>0.15547</v>
       </c>
       <c r="C282" t="n">
-        <v>2.81884</v>
+        <v>1.52517</v>
       </c>
     </row>
     <row r="283">
@@ -3529,10 +3529,10 @@
         <v>2.81001</v>
       </c>
       <c r="B283" t="n">
-        <v>0.28783</v>
+        <v>0.1548</v>
       </c>
       <c r="C283" t="n">
-        <v>2.82364</v>
+        <v>1.51856</v>
       </c>
     </row>
     <row r="284">
@@ -3540,10 +3540,10 @@
         <v>2.82001</v>
       </c>
       <c r="B284" t="n">
-        <v>0.28832</v>
+        <v>0.15381</v>
       </c>
       <c r="C284" t="n">
-        <v>2.82838</v>
+        <v>1.50885</v>
       </c>
     </row>
     <row r="285">
@@ -3551,10 +3551,10 @@
         <v>2.83001</v>
       </c>
       <c r="B285" t="n">
-        <v>0.28879</v>
+        <v>0.15268</v>
       </c>
       <c r="C285" t="n">
-        <v>2.83304</v>
+        <v>1.49778</v>
       </c>
     </row>
     <row r="286">
@@ -3562,10 +3562,10 @@
         <v>2.84001</v>
       </c>
       <c r="B286" t="n">
-        <v>0.28926</v>
+        <v>0.15127</v>
       </c>
       <c r="C286" t="n">
-        <v>2.83764</v>
+        <v>1.48399</v>
       </c>
     </row>
     <row r="287">
@@ -3573,10 +3573,10 @@
         <v>2.85001</v>
       </c>
       <c r="B287" t="n">
-        <v>0.28972</v>
+        <v>0.14971</v>
       </c>
       <c r="C287" t="n">
-        <v>2.84217</v>
+        <v>1.46868</v>
       </c>
     </row>
     <row r="288">
@@ -3584,10 +3584,10 @@
         <v>2.86001</v>
       </c>
       <c r="B288" t="n">
-        <v>0.29018</v>
+        <v>0.14792</v>
       </c>
       <c r="C288" t="n">
-        <v>2.84664</v>
+        <v>1.45113</v>
       </c>
     </row>
     <row r="289">
@@ -3595,10 +3595,10 @@
         <v>2.87001</v>
       </c>
       <c r="B289" t="n">
-        <v>0.29063</v>
+        <v>0.14595</v>
       </c>
       <c r="C289" t="n">
-        <v>2.85104</v>
+        <v>1.4318</v>
       </c>
     </row>
     <row r="290">
@@ -3606,10 +3606,10 @@
         <v>2.88001</v>
       </c>
       <c r="B290" t="n">
-        <v>0.29107</v>
+        <v>0.14381</v>
       </c>
       <c r="C290" t="n">
-        <v>2.85538</v>
+        <v>1.4108</v>
       </c>
     </row>
     <row r="291">
@@ -3617,10 +3617,10 @@
         <v>2.89001</v>
       </c>
       <c r="B291" t="n">
-        <v>0.2915</v>
+        <v>0.14139</v>
       </c>
       <c r="C291" t="n">
-        <v>2.85966</v>
+        <v>1.38706</v>
       </c>
     </row>
     <row r="292">
@@ -3628,10 +3628,10 @@
         <v>2.90001</v>
       </c>
       <c r="B292" t="n">
-        <v>0.29193</v>
+        <v>0.1389</v>
       </c>
       <c r="C292" t="n">
-        <v>2.86387</v>
+        <v>1.36263</v>
       </c>
     </row>
     <row r="293">
@@ -3639,10 +3639,10 @@
         <v>2.91001</v>
       </c>
       <c r="B293" t="n">
-        <v>0.29236</v>
+        <v>0.13619</v>
       </c>
       <c r="C293" t="n">
-        <v>2.86801</v>
+        <v>1.33601</v>
       </c>
     </row>
     <row r="294">
@@ -3650,10 +3650,10 @@
         <v>2.92001</v>
       </c>
       <c r="B294" t="n">
-        <v>0.29277</v>
+        <v>0.13452</v>
       </c>
       <c r="C294" t="n">
-        <v>2.8721</v>
+        <v>1.31961</v>
       </c>
     </row>
     <row r="295">
@@ -3661,10 +3661,10 @@
         <v>2.93001</v>
       </c>
       <c r="B295" t="n">
-        <v>0.29318</v>
+        <v>0.13302</v>
       </c>
       <c r="C295" t="n">
-        <v>2.87612</v>
+        <v>1.30489</v>
       </c>
     </row>
     <row r="296">
@@ -3672,10 +3672,10 @@
         <v>2.94001</v>
       </c>
       <c r="B296" t="n">
-        <v>0.29359</v>
+        <v>0.13154</v>
       </c>
       <c r="C296" t="n">
-        <v>2.88009</v>
+        <v>1.29042</v>
       </c>
     </row>
     <row r="297">
@@ -3683,10 +3683,10 @@
         <v>2.95001</v>
       </c>
       <c r="B297" t="n">
-        <v>0.29398</v>
+        <v>0.13012</v>
       </c>
       <c r="C297" t="n">
-        <v>2.88399</v>
+        <v>1.27652</v>
       </c>
     </row>
     <row r="298">
@@ -3694,10 +3694,10 @@
         <v>2.96001</v>
       </c>
       <c r="B298" t="n">
-        <v>0.29438</v>
+        <v>0.12876</v>
       </c>
       <c r="C298" t="n">
-        <v>2.88784</v>
+        <v>1.2631</v>
       </c>
     </row>
     <row r="299">
@@ -3705,10 +3705,10 @@
         <v>2.97001</v>
       </c>
       <c r="B299" t="n">
-        <v>0.29476</v>
+        <v>0.12736</v>
       </c>
       <c r="C299" t="n">
-        <v>2.89162</v>
+        <v>1.24945</v>
       </c>
     </row>
     <row r="300">
@@ -3716,10 +3716,10 @@
         <v>2.98001</v>
       </c>
       <c r="B300" t="n">
-        <v>0.29514</v>
+        <v>0.12603</v>
       </c>
       <c r="C300" t="n">
-        <v>2.89535</v>
+        <v>1.23633</v>
       </c>
     </row>
     <row r="301">
@@ -3727,10 +3727,1110 @@
         <v>2.99001</v>
       </c>
       <c r="B301" t="n">
-        <v>0.29552</v>
+        <v>0.12469</v>
       </c>
       <c r="C301" t="n">
-        <v>2.89902</v>
+        <v>1.22322</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>3.00001</v>
+      </c>
+      <c r="B302" t="n">
+        <v>0.12338</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1.21034</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>3.01001</v>
+      </c>
+      <c r="B303" t="n">
+        <v>0.12205</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1.19727</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>3.02001</v>
+      </c>
+      <c r="B304" t="n">
+        <v>0.12075</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1.18456</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>3.03001</v>
+      </c>
+      <c r="B305" t="n">
+        <v>0.11941</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1.17145</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>3.04001</v>
+      </c>
+      <c r="B306" t="n">
+        <v>0.11806</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1.15819</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>3.05001</v>
+      </c>
+      <c r="B307" t="n">
+        <v>0.11675</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1.14527</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>3.06001</v>
+      </c>
+      <c r="B308" t="n">
+        <v>0.11543</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1.1324</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>3.07001</v>
+      </c>
+      <c r="B309" t="n">
+        <v>0.11425</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1.12074</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>3.08001</v>
+      </c>
+      <c r="B310" t="n">
+        <v>0.11294</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1.10795</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>3.09001</v>
+      </c>
+      <c r="B311" t="n">
+        <v>0.11165</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1.0953</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>3.10001</v>
+      </c>
+      <c r="B312" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1.08403</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>3.11001</v>
+      </c>
+      <c r="B313" t="n">
+        <v>0.11049</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1.08392</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>3.12001</v>
+      </c>
+      <c r="B314" t="n">
+        <v>0.11045</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1.0835</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>3.13001</v>
+      </c>
+      <c r="B315" t="n">
+        <v>0.11038</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1.08279</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>3.14001</v>
+      </c>
+      <c r="B316" t="n">
+        <v>0.11028</v>
+      </c>
+      <c r="C316" t="n">
+        <v>1.08181</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>3.15001</v>
+      </c>
+      <c r="B317" t="n">
+        <v>0.11021</v>
+      </c>
+      <c r="C317" t="n">
+        <v>1.08112</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>3.16001</v>
+      </c>
+      <c r="B318" t="n">
+        <v>0.11011</v>
+      </c>
+      <c r="C318" t="n">
+        <v>1.08016</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>3.17001</v>
+      </c>
+      <c r="B319" t="n">
+        <v>0.10998</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1.07892</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>3.18001</v>
+      </c>
+      <c r="B320" t="n">
+        <v>0.10983</v>
+      </c>
+      <c r="C320" t="n">
+        <v>1.07742</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>3.19001</v>
+      </c>
+      <c r="B321" t="n">
+        <v>0.10965</v>
+      </c>
+      <c r="C321" t="n">
+        <v>1.07566</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>3.20001</v>
+      </c>
+      <c r="B322" t="n">
+        <v>0.10944</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1.07365</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>3.21001</v>
+      </c>
+      <c r="B323" t="n">
+        <v>0.10921</v>
+      </c>
+      <c r="C323" t="n">
+        <v>1.07139</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>3.22001</v>
+      </c>
+      <c r="B324" t="n">
+        <v>0.10896</v>
+      </c>
+      <c r="C324" t="n">
+        <v>1.0689</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>3.23001</v>
+      </c>
+      <c r="B325" t="n">
+        <v>0.10868</v>
+      </c>
+      <c r="C325" t="n">
+        <v>1.06617</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>3.24001</v>
+      </c>
+      <c r="B326" t="n">
+        <v>0.10838</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1.06322</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>3.25001</v>
+      </c>
+      <c r="B327" t="n">
+        <v>0.10806</v>
+      </c>
+      <c r="C327" t="n">
+        <v>1.06005</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>3.26001</v>
+      </c>
+      <c r="B328" t="n">
+        <v>0.10771</v>
+      </c>
+      <c r="C328" t="n">
+        <v>1.05668</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>3.27001</v>
+      </c>
+      <c r="B329" t="n">
+        <v>0.10736</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1.05322</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>3.28001</v>
+      </c>
+      <c r="B330" t="n">
+        <v>0.10703</v>
+      </c>
+      <c r="C330" t="n">
+        <v>1.04994</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>3.29001</v>
+      </c>
+      <c r="B331" t="n">
+        <v>0.10667</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1.04646</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>3.30001</v>
+      </c>
+      <c r="B332" t="n">
+        <v>0.1063</v>
+      </c>
+      <c r="C332" t="n">
+        <v>1.04278</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>3.31001</v>
+      </c>
+      <c r="B333" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1.03892</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>3.32001</v>
+      </c>
+      <c r="B334" t="n">
+        <v>0.10549</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1.03487</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>3.33001</v>
+      </c>
+      <c r="B335" t="n">
+        <v>0.10506</v>
+      </c>
+      <c r="C335" t="n">
+        <v>1.03064</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>3.34001</v>
+      </c>
+      <c r="B336" t="n">
+        <v>0.10461</v>
+      </c>
+      <c r="C336" t="n">
+        <v>1.02625</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>3.35001</v>
+      </c>
+      <c r="B337" t="n">
+        <v>0.10415</v>
+      </c>
+      <c r="C337" t="n">
+        <v>1.02169</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>3.36001</v>
+      </c>
+      <c r="B338" t="n">
+        <v>0.10367</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1.01697</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>3.37001</v>
+      </c>
+      <c r="B339" t="n">
+        <v>0.10317</v>
+      </c>
+      <c r="C339" t="n">
+        <v>1.01209</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>3.38001</v>
+      </c>
+      <c r="B340" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1.00744</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>3.39001</v>
+      </c>
+      <c r="B341" t="n">
+        <v>0.10221</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1.0027</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>3.40001</v>
+      </c>
+      <c r="B342" t="n">
+        <v>0.10171</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.99782</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>3.41001</v>
+      </c>
+      <c r="B343" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.9928</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3.42001</v>
+      </c>
+      <c r="B344" t="n">
+        <v>0.10069</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.98773</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3.43001</v>
+      </c>
+      <c r="B345" t="n">
+        <v>0.10019</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.98286</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3.44001</v>
+      </c>
+      <c r="B346" t="n">
+        <v>0.09968</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.97785</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3.45001</v>
+      </c>
+      <c r="B347" t="n">
+        <v>0.09916</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.97271</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3.46001</v>
+      </c>
+      <c r="B348" t="n">
+        <v>0.09865</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.96777</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3.47001</v>
+      </c>
+      <c r="B349" t="n">
+        <v>0.09814000000000001</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.96278</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3.48001</v>
+      </c>
+      <c r="B350" t="n">
+        <v>0.09765</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.9579</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3.49001</v>
+      </c>
+      <c r="B351" t="n">
+        <v>0.09715</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.95307</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3.50001</v>
+      </c>
+      <c r="B352" t="n">
+        <v>0.09665</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.94812</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>3.51001</v>
+      </c>
+      <c r="B353" t="n">
+        <v>0.09612999999999999</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.9430500000000001</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>3.52001</v>
+      </c>
+      <c r="B354" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.93787</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>3.53001</v>
+      </c>
+      <c r="B355" t="n">
+        <v>0.09506000000000001</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.93258</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>3.54001</v>
+      </c>
+      <c r="B356" t="n">
+        <v>0.09453</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.9273</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>3.55001</v>
+      </c>
+      <c r="B357" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.92217</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>3.56001</v>
+      </c>
+      <c r="B358" t="n">
+        <v>0.09347</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.91694</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>3.57001</v>
+      </c>
+      <c r="B359" t="n">
+        <v>0.09293</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.91161</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>3.58001</v>
+      </c>
+      <c r="B360" t="n">
+        <v>0.09236999999999999</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.9061900000000001</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3.59001</v>
+      </c>
+      <c r="B361" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.90067</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>3.60001</v>
+      </c>
+      <c r="B362" t="n">
+        <v>0.09124</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.89507</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3.61001</v>
+      </c>
+      <c r="B363" t="n">
+        <v>0.09066</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.88939</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>3.62001</v>
+      </c>
+      <c r="B364" t="n">
+        <v>0.09007</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.88363</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>3.63001</v>
+      </c>
+      <c r="B365" t="n">
+        <v>0.08948</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.8778</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3.64001</v>
+      </c>
+      <c r="B366" t="n">
+        <v>0.08888</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.8718900000000001</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>3.65001</v>
+      </c>
+      <c r="B367" t="n">
+        <v>0.08827</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.86592</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>3.66001</v>
+      </c>
+      <c r="B368" t="n">
+        <v>0.08765000000000001</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.85988</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>3.67001</v>
+      </c>
+      <c r="B369" t="n">
+        <v>0.08704000000000001</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.85382</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3.68001</v>
+      </c>
+      <c r="B370" t="n">
+        <v>0.08644</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.84795</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>3.69001</v>
+      </c>
+      <c r="B371" t="n">
+        <v>0.08583</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.8420299999999999</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>3.70001</v>
+      </c>
+      <c r="B372" t="n">
+        <v>0.08522</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.83605</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>3.71001</v>
+      </c>
+      <c r="B373" t="n">
+        <v>0.08461</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.83001</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>3.72001</v>
+      </c>
+      <c r="B374" t="n">
+        <v>0.08399</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.82392</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>3.73001</v>
+      </c>
+      <c r="B375" t="n">
+        <v>0.08336</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.81779</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>3.74001</v>
+      </c>
+      <c r="B376" t="n">
+        <v>0.08273</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.8116100000000001</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>3.75001</v>
+      </c>
+      <c r="B377" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.8053900000000001</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>3.76001</v>
+      </c>
+      <c r="B378" t="n">
+        <v>0.08146</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.7991200000000001</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>3.77001</v>
+      </c>
+      <c r="B379" t="n">
+        <v>0.08082</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.79283</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>3.78001</v>
+      </c>
+      <c r="B380" t="n">
+        <v>0.08017000000000001</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.78649</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>3.79001</v>
+      </c>
+      <c r="B381" t="n">
+        <v>0.07951999999999999</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.78013</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>3.80001</v>
+      </c>
+      <c r="B382" t="n">
+        <v>0.07887</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.77374</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>3.81001</v>
+      </c>
+      <c r="B383" t="n">
+        <v>0.07822</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.76732</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>3.82001</v>
+      </c>
+      <c r="B384" t="n">
+        <v>0.07756</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.76088</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>3.83001</v>
+      </c>
+      <c r="B385" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.75442</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>3.84001</v>
+      </c>
+      <c r="B386" t="n">
+        <v>0.07624</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.74794</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>3.85001</v>
+      </c>
+      <c r="B387" t="n">
+        <v>0.07557999999999999</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.74144</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>3.86001</v>
+      </c>
+      <c r="B388" t="n">
+        <v>0.07492</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.73498</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>3.87001</v>
+      </c>
+      <c r="B389" t="n">
+        <v>0.07428</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.72865</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>3.88001</v>
+      </c>
+      <c r="B390" t="n">
+        <v>0.07363</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.72231</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>3.89001</v>
+      </c>
+      <c r="B391" t="n">
+        <v>0.07298</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.71596</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>3.90001</v>
+      </c>
+      <c r="B392" t="n">
+        <v>0.07233000000000001</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.7095900000000001</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>3.91001</v>
+      </c>
+      <c r="B393" t="n">
+        <v>0.07167999999999999</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.70322</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>3.92001</v>
+      </c>
+      <c r="B394" t="n">
+        <v>0.07103</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.6968299999999999</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>3.93001</v>
+      </c>
+      <c r="B395" t="n">
+        <v>0.07038</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.6904400000000001</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>3.94001</v>
+      </c>
+      <c r="B396" t="n">
+        <v>0.06973</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.68405</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>3.95001</v>
+      </c>
+      <c r="B397" t="n">
+        <v>0.06908</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.67766</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>3.96001</v>
+      </c>
+      <c r="B398" t="n">
+        <v>0.06843</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.67126</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>3.97001</v>
+      </c>
+      <c r="B399" t="n">
+        <v>0.06777</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.66487</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>3.98001</v>
+      </c>
+      <c r="B400" t="n">
+        <v>0.06712</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.65847</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>3.99001</v>
+      </c>
+      <c r="B401" t="n">
+        <v>0.06647</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.6520899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/my_response_spectrum.xlsx
+++ b/my_response_spectrum.xlsx
@@ -441,7 +441,7 @@
         <v>0.31882</v>
       </c>
       <c r="C2" t="n">
-        <v>3.12763</v>
+        <v>3.12762</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +449,10 @@
         <v>0.01001</v>
       </c>
       <c r="B3" t="n">
-        <v>0.32013</v>
+        <v>0.31916</v>
       </c>
       <c r="C3" t="n">
-        <v>3.14044</v>
+        <v>3.13091</v>
       </c>
     </row>
     <row r="4">
@@ -460,10 +460,10 @@
         <v>0.02001</v>
       </c>
       <c r="B4" t="n">
-        <v>0.34669</v>
+        <v>0.34431</v>
       </c>
       <c r="C4" t="n">
-        <v>3.40099</v>
+        <v>3.37767</v>
       </c>
     </row>
     <row r="5">
@@ -471,10 +471,10 @@
         <v>0.03001</v>
       </c>
       <c r="B5" t="n">
-        <v>0.35225</v>
+        <v>0.36318</v>
       </c>
       <c r="C5" t="n">
-        <v>3.45555</v>
+        <v>3.56279</v>
       </c>
     </row>
     <row r="6">
@@ -482,10 +482,10 @@
         <v>0.04001</v>
       </c>
       <c r="B6" t="n">
-        <v>0.35864</v>
+        <v>0.42089</v>
       </c>
       <c r="C6" t="n">
-        <v>3.51824</v>
+        <v>4.12895</v>
       </c>
     </row>
     <row r="7">
@@ -493,10 +493,10 @@
         <v>0.05001</v>
       </c>
       <c r="B7" t="n">
-        <v>0.47342</v>
+        <v>0.54061</v>
       </c>
       <c r="C7" t="n">
-        <v>4.64421</v>
+        <v>5.30334</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +504,10 @@
         <v>0.06001</v>
       </c>
       <c r="B8" t="n">
-        <v>0.55565</v>
+        <v>0.6228399999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>5.45093</v>
+        <v>6.11007</v>
       </c>
     </row>
     <row r="9">
@@ -515,10 +515,10 @@
         <v>0.07001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.56346</v>
+        <v>0.63065</v>
       </c>
       <c r="C9" t="n">
-        <v>5.5275</v>
+        <v>6.18664</v>
       </c>
     </row>
     <row r="10">
@@ -526,10 +526,10 @@
         <v>0.08001</v>
       </c>
       <c r="B10" t="n">
-        <v>0.57254</v>
+        <v>0.63973</v>
       </c>
       <c r="C10" t="n">
-        <v>5.61657</v>
+        <v>6.27571</v>
       </c>
     </row>
     <row r="11">
@@ -537,10 +537,10 @@
         <v>0.09001000000000001</v>
       </c>
       <c r="B11" t="n">
-        <v>0.61963</v>
+        <v>0.68682</v>
       </c>
       <c r="C11" t="n">
-        <v>6.0786</v>
+        <v>6.73773</v>
       </c>
     </row>
     <row r="12">
@@ -548,10 +548,10 @@
         <v>0.10001</v>
       </c>
       <c r="B12" t="n">
-        <v>0.64895</v>
+        <v>0.71613</v>
       </c>
       <c r="C12" t="n">
-        <v>6.36624</v>
+        <v>7.02527</v>
       </c>
     </row>
     <row r="13">
@@ -559,10 +559,10 @@
         <v>0.11001</v>
       </c>
       <c r="B13" t="n">
-        <v>0.73189</v>
+        <v>0.7990699999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>7.17986</v>
+        <v>7.83889</v>
       </c>
     </row>
     <row r="14">
@@ -570,10 +570,10 @@
         <v>0.12001</v>
       </c>
       <c r="B14" t="n">
-        <v>0.66816</v>
+        <v>0.68902</v>
       </c>
       <c r="C14" t="n">
-        <v>6.55469</v>
+        <v>6.75927</v>
       </c>
     </row>
     <row r="15">
@@ -581,10 +581,10 @@
         <v>0.13001</v>
       </c>
       <c r="B15" t="n">
-        <v>0.64705</v>
+        <v>0.66552</v>
       </c>
       <c r="C15" t="n">
-        <v>6.34753</v>
+        <v>6.52872</v>
       </c>
     </row>
     <row r="16">
@@ -592,10 +592,10 @@
         <v>0.14001</v>
       </c>
       <c r="B16" t="n">
-        <v>0.73324</v>
+        <v>0.76983</v>
       </c>
       <c r="C16" t="n">
-        <v>7.19304</v>
+        <v>7.55201</v>
       </c>
     </row>
     <row r="17">
@@ -603,10 +603,10 @@
         <v>0.15001</v>
       </c>
       <c r="B17" t="n">
-        <v>0.77133</v>
+        <v>0.81468</v>
       </c>
       <c r="C17" t="n">
-        <v>7.56671</v>
+        <v>7.99205</v>
       </c>
     </row>
     <row r="18">
@@ -614,10 +614,10 @@
         <v>0.16001</v>
       </c>
       <c r="B18" t="n">
-        <v>0.75715</v>
+        <v>0.77563</v>
       </c>
       <c r="C18" t="n">
-        <v>7.42763</v>
+        <v>7.60892</v>
       </c>
     </row>
     <row r="19">
@@ -625,10 +625,10 @@
         <v>0.17001</v>
       </c>
       <c r="B19" t="n">
-        <v>0.885</v>
+        <v>0.92302</v>
       </c>
       <c r="C19" t="n">
-        <v>8.68182</v>
+        <v>9.05486</v>
       </c>
     </row>
     <row r="20">
@@ -636,10 +636,10 @@
         <v>0.18001</v>
       </c>
       <c r="B20" t="n">
-        <v>0.88771</v>
+        <v>0.92435</v>
       </c>
       <c r="C20" t="n">
-        <v>8.708399999999999</v>
+        <v>9.06784</v>
       </c>
     </row>
     <row r="21">
@@ -647,10 +647,10 @@
         <v>0.19001</v>
       </c>
       <c r="B21" t="n">
-        <v>0.87893</v>
+        <v>0.91556</v>
       </c>
       <c r="C21" t="n">
-        <v>8.622350000000001</v>
+        <v>8.98169</v>
       </c>
     </row>
     <row r="22">
@@ -658,10 +658,10 @@
         <v>0.20001</v>
       </c>
       <c r="B22" t="n">
-        <v>0.7266899999999999</v>
+        <v>0.76035</v>
       </c>
       <c r="C22" t="n">
-        <v>7.12887</v>
+        <v>7.45908</v>
       </c>
     </row>
     <row r="23">
@@ -669,10 +669,10 @@
         <v>0.21001</v>
       </c>
       <c r="B23" t="n">
-        <v>0.62516</v>
+        <v>0.66444</v>
       </c>
       <c r="C23" t="n">
-        <v>6.13283</v>
+        <v>6.51814</v>
       </c>
     </row>
     <row r="24">
@@ -680,10 +680,10 @@
         <v>0.22001</v>
       </c>
       <c r="B24" t="n">
-        <v>0.57073</v>
+        <v>0.62888</v>
       </c>
       <c r="C24" t="n">
-        <v>5.59891</v>
+        <v>6.16928</v>
       </c>
     </row>
     <row r="25">
@@ -691,10 +691,10 @@
         <v>0.23001</v>
       </c>
       <c r="B25" t="n">
-        <v>0.62058</v>
+        <v>0.68777</v>
       </c>
       <c r="C25" t="n">
-        <v>6.0879</v>
+        <v>6.74704</v>
       </c>
     </row>
     <row r="26">
@@ -702,10 +702,10 @@
         <v>0.24001</v>
       </c>
       <c r="B26" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.83989</v>
       </c>
       <c r="C26" t="n">
-        <v>7.58023</v>
+        <v>8.239369999999999</v>
       </c>
     </row>
     <row r="27">
@@ -713,10 +713,10 @@
         <v>0.25001</v>
       </c>
       <c r="B27" t="n">
-        <v>0.87166</v>
+        <v>0.93885</v>
       </c>
       <c r="C27" t="n">
-        <v>8.550940000000001</v>
+        <v>9.21007</v>
       </c>
     </row>
     <row r="28">
@@ -724,10 +724,10 @@
         <v>0.26001</v>
       </c>
       <c r="B28" t="n">
-        <v>0.90596</v>
+        <v>1.03663</v>
       </c>
       <c r="C28" t="n">
-        <v>8.887510000000001</v>
+        <v>10.16937</v>
       </c>
     </row>
     <row r="29">
@@ -735,10 +735,10 @@
         <v>0.27001</v>
       </c>
       <c r="B29" t="n">
-        <v>0.83943</v>
+        <v>1.03342</v>
       </c>
       <c r="C29" t="n">
-        <v>8.2348</v>
+        <v>10.13788</v>
       </c>
     </row>
     <row r="30">
@@ -746,10 +746,10 @@
         <v>0.28001</v>
       </c>
       <c r="B30" t="n">
-        <v>0.78296</v>
+        <v>0.98005</v>
       </c>
       <c r="C30" t="n">
-        <v>7.68087</v>
+        <v>9.61429</v>
       </c>
     </row>
     <row r="31">
@@ -757,10 +757,10 @@
         <v>0.29001</v>
       </c>
       <c r="B31" t="n">
-        <v>0.75412</v>
+        <v>0.95933</v>
       </c>
       <c r="C31" t="n">
-        <v>7.39788</v>
+        <v>9.41103</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         <v>0.30001</v>
       </c>
       <c r="B32" t="n">
-        <v>0.75341</v>
+        <v>0.9859</v>
       </c>
       <c r="C32" t="n">
-        <v>7.39092</v>
+        <v>9.671670000000001</v>
       </c>
     </row>
     <row r="33">
@@ -779,10 +779,10 @@
         <v>0.31001</v>
       </c>
       <c r="B33" t="n">
-        <v>0.78613</v>
+        <v>1.03226</v>
       </c>
       <c r="C33" t="n">
-        <v>7.71193</v>
+        <v>10.12644</v>
       </c>
     </row>
     <row r="34">
@@ -790,10 +790,10 @@
         <v>0.32001</v>
       </c>
       <c r="B34" t="n">
-        <v>0.7839699999999999</v>
+        <v>1.07626</v>
       </c>
       <c r="C34" t="n">
-        <v>7.69078</v>
+        <v>10.55813</v>
       </c>
     </row>
     <row r="35">
@@ -801,10 +801,10 @@
         <v>0.33001</v>
       </c>
       <c r="B35" t="n">
-        <v>0.78581</v>
+        <v>1.08101</v>
       </c>
       <c r="C35" t="n">
-        <v>7.70878</v>
+        <v>10.60469</v>
       </c>
     </row>
     <row r="36">
@@ -812,10 +812,10 @@
         <v>0.34001</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7664299999999999</v>
+        <v>1.05128</v>
       </c>
       <c r="C36" t="n">
-        <v>7.51866</v>
+        <v>10.31304</v>
       </c>
     </row>
     <row r="37">
@@ -823,10 +823,10 @@
         <v>0.35001</v>
       </c>
       <c r="B37" t="n">
-        <v>0.74581</v>
+        <v>1.00485</v>
       </c>
       <c r="C37" t="n">
-        <v>7.31642</v>
+        <v>9.857620000000001</v>
       </c>
     </row>
     <row r="38">
@@ -834,10 +834,10 @@
         <v>0.36001</v>
       </c>
       <c r="B38" t="n">
-        <v>0.73344</v>
+        <v>0.95785</v>
       </c>
       <c r="C38" t="n">
-        <v>7.19504</v>
+        <v>9.39653</v>
       </c>
     </row>
     <row r="39">
@@ -845,10 +845,10 @@
         <v>0.37001</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7339</v>
+        <v>0.91789</v>
       </c>
       <c r="C39" t="n">
-        <v>7.19955</v>
+        <v>9.004519999999999</v>
       </c>
     </row>
     <row r="40">
@@ -856,10 +856,10 @@
         <v>0.38001</v>
       </c>
       <c r="B40" t="n">
-        <v>0.73262</v>
+        <v>0.88483</v>
       </c>
       <c r="C40" t="n">
-        <v>7.187</v>
+        <v>8.68017</v>
       </c>
     </row>
     <row r="41">
@@ -867,10 +867,10 @@
         <v>0.39001</v>
       </c>
       <c r="B41" t="n">
-        <v>0.75092</v>
+        <v>0.85468</v>
       </c>
       <c r="C41" t="n">
-        <v>7.36649</v>
+        <v>8.384449999999999</v>
       </c>
     </row>
     <row r="42">
@@ -878,10 +878,10 @@
         <v>0.40001</v>
       </c>
       <c r="B42" t="n">
-        <v>0.75888</v>
+        <v>0.823</v>
       </c>
       <c r="C42" t="n">
-        <v>7.44466</v>
+        <v>8.073589999999999</v>
       </c>
     </row>
     <row r="43">
@@ -889,10 +889,10 @@
         <v>0.41001</v>
       </c>
       <c r="B43" t="n">
-        <v>0.78293</v>
+        <v>0.81659</v>
       </c>
       <c r="C43" t="n">
-        <v>7.68059</v>
+        <v>8.0108</v>
       </c>
     </row>
     <row r="44">
@@ -900,10 +900,10 @@
         <v>0.42001</v>
       </c>
       <c r="B44" t="n">
-        <v>0.79474</v>
+        <v>0.8284</v>
       </c>
       <c r="C44" t="n">
-        <v>7.79639</v>
+        <v>8.12659</v>
       </c>
     </row>
     <row r="45">
@@ -911,10 +911,10 @@
         <v>0.43001</v>
       </c>
       <c r="B45" t="n">
-        <v>0.8131</v>
+        <v>0.84676</v>
       </c>
       <c r="C45" t="n">
-        <v>7.97653</v>
+        <v>8.30674</v>
       </c>
     </row>
     <row r="46">
@@ -922,10 +922,10 @@
         <v>0.44001</v>
       </c>
       <c r="B46" t="n">
-        <v>0.82375</v>
+        <v>0.85741</v>
       </c>
       <c r="C46" t="n">
-        <v>8.081020000000001</v>
+        <v>8.41122</v>
       </c>
     </row>
     <row r="47">
@@ -933,10 +933,10 @@
         <v>0.45001</v>
       </c>
       <c r="B47" t="n">
-        <v>0.82586</v>
+        <v>0.8777</v>
       </c>
       <c r="C47" t="n">
-        <v>8.10168</v>
+        <v>8.61022</v>
       </c>
     </row>
     <row r="48">
@@ -944,10 +944,10 @@
         <v>0.46001</v>
       </c>
       <c r="B48" t="n">
-        <v>0.8459</v>
+        <v>0.91232</v>
       </c>
       <c r="C48" t="n">
-        <v>8.298299999999999</v>
+        <v>8.94988</v>
       </c>
     </row>
     <row r="49">
@@ -955,10 +955,10 @@
         <v>0.47001</v>
       </c>
       <c r="B49" t="n">
-        <v>0.87068</v>
+        <v>0.9371</v>
       </c>
       <c r="C49" t="n">
-        <v>8.541370000000001</v>
+        <v>9.19295</v>
       </c>
     </row>
     <row r="50">
@@ -966,10 +966,10 @@
         <v>0.48001</v>
       </c>
       <c r="B50" t="n">
-        <v>0.89423</v>
+        <v>0.96065</v>
       </c>
       <c r="C50" t="n">
-        <v>8.772360000000001</v>
+        <v>9.42394</v>
       </c>
     </row>
     <row r="51">
@@ -977,10 +977,10 @@
         <v>0.49001</v>
       </c>
       <c r="B51" t="n">
-        <v>0.91414</v>
+        <v>0.98056</v>
       </c>
       <c r="C51" t="n">
-        <v>8.96767</v>
+        <v>9.619249999999999</v>
       </c>
     </row>
     <row r="52">
@@ -988,10 +988,10 @@
         <v>0.50001</v>
       </c>
       <c r="B52" t="n">
-        <v>0.91714</v>
+        <v>0.98356</v>
       </c>
       <c r="C52" t="n">
-        <v>8.99714</v>
+        <v>9.648720000000001</v>
       </c>
     </row>
     <row r="53">
@@ -999,10 +999,10 @@
         <v>0.51001</v>
       </c>
       <c r="B53" t="n">
-        <v>0.9227</v>
+        <v>0.98912</v>
       </c>
       <c r="C53" t="n">
-        <v>9.05166</v>
+        <v>9.703239999999999</v>
       </c>
     </row>
     <row r="54">
@@ -1010,10 +1010,10 @@
         <v>0.52001</v>
       </c>
       <c r="B54" t="n">
-        <v>0.91521</v>
+        <v>0.98163</v>
       </c>
       <c r="C54" t="n">
-        <v>8.978210000000001</v>
+        <v>9.62979</v>
       </c>
     </row>
     <row r="55">
@@ -1021,10 +1021,10 @@
         <v>0.53001</v>
       </c>
       <c r="B55" t="n">
-        <v>0.89654</v>
+        <v>0.96297</v>
       </c>
       <c r="C55" t="n">
-        <v>8.795019999999999</v>
+        <v>9.44669</v>
       </c>
     </row>
     <row r="56">
@@ -1032,10 +1032,10 @@
         <v>0.54001</v>
       </c>
       <c r="B56" t="n">
-        <v>0.87906</v>
+        <v>0.9454900000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>8.62358</v>
+        <v>9.275259999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1043,10 +1043,10 @@
         <v>0.55001</v>
       </c>
       <c r="B57" t="n">
-        <v>0.8454700000000001</v>
+        <v>0.9119</v>
       </c>
       <c r="C57" t="n">
-        <v>8.29411</v>
+        <v>8.945790000000001</v>
       </c>
     </row>
     <row r="58">
@@ -1054,10 +1054,10 @@
         <v>0.56001</v>
       </c>
       <c r="B58" t="n">
-        <v>0.81631</v>
+        <v>0.88489</v>
       </c>
       <c r="C58" t="n">
-        <v>8.007960000000001</v>
+        <v>8.680730000000001</v>
       </c>
     </row>
     <row r="59">
@@ -1065,10 +1065,10 @@
         <v>0.57001</v>
       </c>
       <c r="B59" t="n">
-        <v>0.8083900000000001</v>
+        <v>0.87697</v>
       </c>
       <c r="C59" t="n">
-        <v>7.93031</v>
+        <v>8.60308</v>
       </c>
     </row>
     <row r="60">
@@ -1076,10 +1076,10 @@
         <v>0.58001</v>
       </c>
       <c r="B60" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.86648</v>
       </c>
       <c r="C60" t="n">
-        <v>7.82745</v>
+        <v>8.500220000000001</v>
       </c>
     </row>
     <row r="61">
@@ -1087,10 +1087,10 @@
         <v>0.59001</v>
       </c>
       <c r="B61" t="n">
-        <v>0.78021</v>
+        <v>0.84879</v>
       </c>
       <c r="C61" t="n">
-        <v>7.65384</v>
+        <v>8.326610000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1098,10 +1098,10 @@
         <v>0.60001</v>
       </c>
       <c r="B62" t="n">
-        <v>0.76122</v>
+        <v>0.8298</v>
       </c>
       <c r="C62" t="n">
-        <v>7.46753</v>
+        <v>8.1403</v>
       </c>
     </row>
     <row r="63">
@@ -1109,10 +1109,10 @@
         <v>0.6100100000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>0.74375</v>
+        <v>0.81233</v>
       </c>
       <c r="C63" t="n">
-        <v>7.29622</v>
+        <v>7.96899</v>
       </c>
     </row>
     <row r="64">
@@ -1120,10 +1120,10 @@
         <v>0.62001</v>
       </c>
       <c r="B64" t="n">
-        <v>0.7214</v>
+        <v>0.78998</v>
       </c>
       <c r="C64" t="n">
-        <v>7.07693</v>
+        <v>7.7497</v>
       </c>
     </row>
     <row r="65">
@@ -1131,10 +1131,10 @@
         <v>0.63001</v>
       </c>
       <c r="B65" t="n">
-        <v>0.6952700000000001</v>
+        <v>0.76385</v>
       </c>
       <c r="C65" t="n">
-        <v>6.82059</v>
+        <v>7.49336</v>
       </c>
     </row>
     <row r="66">
@@ -1142,10 +1142,10 @@
         <v>0.64001</v>
       </c>
       <c r="B66" t="n">
-        <v>0.6727300000000001</v>
+        <v>0.74131</v>
       </c>
       <c r="C66" t="n">
-        <v>6.59945</v>
+        <v>7.27222</v>
       </c>
     </row>
     <row r="67">
@@ -1153,10 +1153,10 @@
         <v>0.65001</v>
       </c>
       <c r="B67" t="n">
-        <v>0.64954</v>
+        <v>0.71812</v>
       </c>
       <c r="C67" t="n">
-        <v>6.372</v>
+        <v>7.04477</v>
       </c>
     </row>
     <row r="68">
@@ -1164,10 +1164,10 @@
         <v>0.66001</v>
       </c>
       <c r="B68" t="n">
-        <v>0.62414</v>
+        <v>0.69272</v>
       </c>
       <c r="C68" t="n">
-        <v>6.12281</v>
+        <v>6.79558</v>
       </c>
     </row>
     <row r="69">
@@ -1175,10 +1175,10 @@
         <v>0.67001</v>
       </c>
       <c r="B69" t="n">
-        <v>0.59727</v>
+        <v>0.6658500000000001</v>
       </c>
       <c r="C69" t="n">
-        <v>5.85921</v>
+        <v>6.53198</v>
       </c>
     </row>
     <row r="70">
@@ -1186,10 +1186,10 @@
         <v>0.68001</v>
       </c>
       <c r="B70" t="n">
-        <v>0.57108</v>
+        <v>0.63966</v>
       </c>
       <c r="C70" t="n">
-        <v>5.60233</v>
+        <v>6.2751</v>
       </c>
     </row>
     <row r="71">
@@ -1197,10 +1197,10 @@
         <v>0.69001</v>
       </c>
       <c r="B71" t="n">
-        <v>0.54831</v>
+        <v>0.61689</v>
       </c>
       <c r="C71" t="n">
-        <v>5.37888</v>
+        <v>6.05165</v>
       </c>
     </row>
     <row r="72">
@@ -1208,10 +1208,10 @@
         <v>0.70001</v>
       </c>
       <c r="B72" t="n">
-        <v>0.52485</v>
+        <v>0.59343</v>
       </c>
       <c r="C72" t="n">
-        <v>5.14881</v>
+        <v>5.82158</v>
       </c>
     </row>
     <row r="73">
@@ -1219,10 +1219,10 @@
         <v>0.71001</v>
       </c>
       <c r="B73" t="n">
-        <v>0.50116</v>
+        <v>0.56974</v>
       </c>
       <c r="C73" t="n">
-        <v>4.91643</v>
+        <v>5.5892</v>
       </c>
     </row>
     <row r="74">
@@ -1230,10 +1230,10 @@
         <v>0.72001</v>
       </c>
       <c r="B74" t="n">
-        <v>0.47879</v>
+        <v>0.54618</v>
       </c>
       <c r="C74" t="n">
-        <v>4.69693</v>
+        <v>5.358</v>
       </c>
     </row>
     <row r="75">
@@ -1241,10 +1241,10 @@
         <v>0.73001</v>
       </c>
       <c r="B75" t="n">
-        <v>0.4629</v>
+        <v>0.52302</v>
       </c>
       <c r="C75" t="n">
-        <v>4.54107</v>
+        <v>5.13078</v>
       </c>
     </row>
     <row r="76">
@@ -1252,10 +1252,10 @@
         <v>0.7400099999999999</v>
       </c>
       <c r="B76" t="n">
-        <v>0.45533</v>
+        <v>0.50048</v>
       </c>
       <c r="C76" t="n">
-        <v>4.46681</v>
+        <v>4.9097</v>
       </c>
     </row>
     <row r="77">
@@ -1263,10 +1263,10 @@
         <v>0.75001</v>
       </c>
       <c r="B77" t="n">
-        <v>0.44783</v>
+        <v>0.48234</v>
       </c>
       <c r="C77" t="n">
-        <v>4.39319</v>
+        <v>4.73172</v>
       </c>
     </row>
     <row r="78">
@@ -1274,10 +1274,10 @@
         <v>0.76001</v>
       </c>
       <c r="B78" t="n">
-        <v>0.43218</v>
+        <v>0.47905</v>
       </c>
       <c r="C78" t="n">
-        <v>4.23968</v>
+        <v>4.69948</v>
       </c>
     </row>
     <row r="79">
@@ -1285,10 +1285,10 @@
         <v>0.77001</v>
       </c>
       <c r="B79" t="n">
-        <v>0.43982</v>
+        <v>0.48538</v>
       </c>
       <c r="C79" t="n">
-        <v>4.31465</v>
+        <v>4.76161</v>
       </c>
     </row>
     <row r="80">
@@ -1296,10 +1296,10 @@
         <v>0.78001</v>
       </c>
       <c r="B80" t="n">
-        <v>0.45596</v>
+        <v>0.49955</v>
       </c>
       <c r="C80" t="n">
-        <v>4.47301</v>
+        <v>4.90056</v>
       </c>
     </row>
     <row r="81">
@@ -1307,10 +1307,10 @@
         <v>0.79001</v>
       </c>
       <c r="B81" t="n">
-        <v>0.47754</v>
+        <v>0.51785</v>
       </c>
       <c r="C81" t="n">
-        <v>4.68469</v>
+        <v>5.08012</v>
       </c>
     </row>
     <row r="82">
@@ -1318,10 +1318,10 @@
         <v>0.80001</v>
       </c>
       <c r="B82" t="n">
-        <v>0.50142</v>
+        <v>0.53565</v>
       </c>
       <c r="C82" t="n">
-        <v>4.91894</v>
+        <v>5.25477</v>
       </c>
     </row>
     <row r="83">
@@ -1329,10 +1329,10 @@
         <v>0.81001</v>
       </c>
       <c r="B83" t="n">
-        <v>0.52663</v>
+        <v>0.54827</v>
       </c>
       <c r="C83" t="n">
-        <v>5.16625</v>
+        <v>5.37853</v>
       </c>
     </row>
     <row r="84">
@@ -1340,10 +1340,10 @@
         <v>0.82001</v>
       </c>
       <c r="B84" t="n">
-        <v>0.54855</v>
+        <v>0.55169</v>
       </c>
       <c r="C84" t="n">
-        <v>5.38131</v>
+        <v>5.41209</v>
       </c>
     </row>
     <row r="85">
@@ -1351,10 +1351,10 @@
         <v>0.83001</v>
       </c>
       <c r="B85" t="n">
-        <v>0.5656099999999999</v>
+        <v>0.57628</v>
       </c>
       <c r="C85" t="n">
-        <v>5.54867</v>
+        <v>5.65328</v>
       </c>
     </row>
     <row r="86">
@@ -1362,10 +1362,10 @@
         <v>0.84001</v>
       </c>
       <c r="B86" t="n">
-        <v>0.57983</v>
+        <v>0.5906</v>
       </c>
       <c r="C86" t="n">
-        <v>5.6881</v>
+        <v>5.79375</v>
       </c>
     </row>
     <row r="87">
@@ -1373,10 +1373,10 @@
         <v>0.85001</v>
       </c>
       <c r="B87" t="n">
-        <v>0.58765</v>
+        <v>0.59841</v>
       </c>
       <c r="C87" t="n">
-        <v>5.76488</v>
+        <v>5.87044</v>
       </c>
     </row>
     <row r="88">
@@ -1384,10 +1384,10 @@
         <v>0.8600100000000001</v>
       </c>
       <c r="B88" t="n">
-        <v>0.58911</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="C88" t="n">
-        <v>5.77917</v>
+        <v>6.03709</v>
       </c>
     </row>
     <row r="89">
@@ -1395,10 +1395,10 @@
         <v>0.87001</v>
       </c>
       <c r="B89" t="n">
-        <v>0.58445</v>
+        <v>0.62807</v>
       </c>
       <c r="C89" t="n">
-        <v>5.73345</v>
+        <v>6.16138</v>
       </c>
     </row>
     <row r="90">
@@ -1406,10 +1406,10 @@
         <v>0.88001</v>
       </c>
       <c r="B90" t="n">
-        <v>0.57342</v>
+        <v>0.62556</v>
       </c>
       <c r="C90" t="n">
-        <v>5.62522</v>
+        <v>6.13671</v>
       </c>
     </row>
     <row r="91">
@@ -1417,10 +1417,10 @@
         <v>0.89001</v>
       </c>
       <c r="B91" t="n">
-        <v>0.55611</v>
+        <v>0.60811</v>
       </c>
       <c r="C91" t="n">
-        <v>5.45547</v>
+        <v>5.96558</v>
       </c>
     </row>
     <row r="92">
@@ -1428,10 +1428,10 @@
         <v>0.90001</v>
       </c>
       <c r="B92" t="n">
-        <v>0.53449</v>
+        <v>0.57979</v>
       </c>
       <c r="C92" t="n">
-        <v>5.24336</v>
+        <v>5.68771</v>
       </c>
     </row>
     <row r="93">
@@ -1439,10 +1439,10 @@
         <v>0.91001</v>
       </c>
       <c r="B93" t="n">
-        <v>0.50788</v>
+        <v>0.58292</v>
       </c>
       <c r="C93" t="n">
-        <v>4.98232</v>
+        <v>5.71842</v>
       </c>
     </row>
     <row r="94">
@@ -1450,10 +1450,10 @@
         <v>0.92001</v>
       </c>
       <c r="B94" t="n">
-        <v>0.50286</v>
+        <v>0.5786</v>
       </c>
       <c r="C94" t="n">
-        <v>4.93304</v>
+        <v>5.67611</v>
       </c>
     </row>
     <row r="95">
@@ -1461,10 +1461,10 @@
         <v>0.93001</v>
       </c>
       <c r="B95" t="n">
-        <v>0.50627</v>
+        <v>0.56723</v>
       </c>
       <c r="C95" t="n">
-        <v>4.96647</v>
+        <v>5.5645</v>
       </c>
     </row>
     <row r="96">
@@ -1472,10 +1472,10 @@
         <v>0.94001</v>
       </c>
       <c r="B96" t="n">
-        <v>0.50681</v>
+        <v>0.55489</v>
       </c>
       <c r="C96" t="n">
-        <v>4.97184</v>
+        <v>5.44351</v>
       </c>
     </row>
     <row r="97">
@@ -1483,10 +1483,10 @@
         <v>0.95001</v>
       </c>
       <c r="B97" t="n">
-        <v>0.50585</v>
+        <v>0.55393</v>
       </c>
       <c r="C97" t="n">
-        <v>4.96241</v>
+        <v>5.43408</v>
       </c>
     </row>
     <row r="98">
@@ -1494,10 +1494,10 @@
         <v>0.96001</v>
       </c>
       <c r="B98" t="n">
-        <v>0.5007200000000001</v>
+        <v>0.5488</v>
       </c>
       <c r="C98" t="n">
-        <v>4.91206</v>
+        <v>5.38372</v>
       </c>
     </row>
     <row r="99">
@@ -1505,10 +1505,10 @@
         <v>0.97001</v>
       </c>
       <c r="B99" t="n">
-        <v>0.49358</v>
+        <v>0.54166</v>
       </c>
       <c r="C99" t="n">
-        <v>4.84198</v>
+        <v>5.31364</v>
       </c>
     </row>
     <row r="100">
@@ -1516,10 +1516,10 @@
         <v>0.98001</v>
       </c>
       <c r="B100" t="n">
-        <v>0.48364</v>
+        <v>0.53172</v>
       </c>
       <c r="C100" t="n">
-        <v>4.74454</v>
+        <v>5.21621</v>
       </c>
     </row>
     <row r="101">
@@ -1527,10 +1527,10 @@
         <v>0.9900099999999999</v>
       </c>
       <c r="B101" t="n">
-        <v>0.47046</v>
+        <v>0.51854</v>
       </c>
       <c r="C101" t="n">
-        <v>4.61525</v>
+        <v>5.08691</v>
       </c>
     </row>
     <row r="102">
@@ -1538,10 +1538,10 @@
         <v>1.00001</v>
       </c>
       <c r="B102" t="n">
-        <v>0.45584</v>
+        <v>0.50392</v>
       </c>
       <c r="C102" t="n">
-        <v>4.47181</v>
+        <v>4.94347</v>
       </c>
     </row>
     <row r="103">
@@ -1549,10 +1549,10 @@
         <v>1.01001</v>
       </c>
       <c r="B103" t="n">
-        <v>0.43784</v>
+        <v>0.48592</v>
       </c>
       <c r="C103" t="n">
-        <v>4.29517</v>
+        <v>4.76684</v>
       </c>
     </row>
     <row r="104">
@@ -1560,10 +1560,10 @@
         <v>1.02001</v>
       </c>
       <c r="B104" t="n">
-        <v>0.43009</v>
+        <v>0.47701</v>
       </c>
       <c r="C104" t="n">
-        <v>4.2192</v>
+        <v>4.67948</v>
       </c>
     </row>
     <row r="105">
@@ -1571,10 +1571,10 @@
         <v>1.03001</v>
       </c>
       <c r="B105" t="n">
-        <v>0.42269</v>
+        <v>0.46961</v>
       </c>
       <c r="C105" t="n">
-        <v>4.1466</v>
+        <v>4.60689</v>
       </c>
     </row>
     <row r="106">
@@ -1582,10 +1582,10 @@
         <v>1.04001</v>
       </c>
       <c r="B106" t="n">
-        <v>0.41186</v>
+        <v>0.45878</v>
       </c>
       <c r="C106" t="n">
-        <v>4.04032</v>
+        <v>4.50061</v>
       </c>
     </row>
     <row r="107">
@@ -1593,10 +1593,10 @@
         <v>1.05001</v>
       </c>
       <c r="B107" t="n">
-        <v>0.4011</v>
+        <v>0.45681</v>
       </c>
       <c r="C107" t="n">
-        <v>3.93479</v>
+        <v>4.48132</v>
       </c>
     </row>
     <row r="108">
@@ -1604,10 +1604,10 @@
         <v>1.06001</v>
       </c>
       <c r="B108" t="n">
-        <v>0.38789</v>
+        <v>0.45524</v>
       </c>
       <c r="C108" t="n">
-        <v>3.80523</v>
+        <v>4.46587</v>
       </c>
     </row>
     <row r="109">
@@ -1615,10 +1615,10 @@
         <v>1.07001</v>
       </c>
       <c r="B109" t="n">
-        <v>0.37445</v>
+        <v>0.45338</v>
       </c>
       <c r="C109" t="n">
-        <v>3.67336</v>
+        <v>4.44761</v>
       </c>
     </row>
     <row r="110">
@@ -1626,10 +1626,10 @@
         <v>1.08001</v>
       </c>
       <c r="B110" t="n">
-        <v>0.35955</v>
+        <v>0.45124</v>
       </c>
       <c r="C110" t="n">
-        <v>3.52714</v>
+        <v>4.42662</v>
       </c>
     </row>
     <row r="111">
@@ -1637,10 +1637,10 @@
         <v>1.09001</v>
       </c>
       <c r="B111" t="n">
-        <v>0.34481</v>
+        <v>0.44883</v>
       </c>
       <c r="C111" t="n">
-        <v>3.38256</v>
+        <v>4.40297</v>
       </c>
     </row>
     <row r="112">
@@ -1648,10 +1648,10 @@
         <v>1.10001</v>
       </c>
       <c r="B112" t="n">
-        <v>0.32893</v>
+        <v>0.44615</v>
       </c>
       <c r="C112" t="n">
-        <v>3.22683</v>
+        <v>4.37676</v>
       </c>
     </row>
     <row r="113">
@@ -1659,10 +1659,10 @@
         <v>1.11001</v>
       </c>
       <c r="B113" t="n">
-        <v>0.31383</v>
+        <v>0.44323</v>
       </c>
       <c r="C113" t="n">
-        <v>3.07863</v>
+        <v>4.34807</v>
       </c>
     </row>
     <row r="114">
@@ -1670,10 +1670,10 @@
         <v>1.12001</v>
       </c>
       <c r="B114" t="n">
-        <v>0.29763</v>
+        <v>0.44006</v>
       </c>
       <c r="C114" t="n">
-        <v>2.91976</v>
+        <v>4.31704</v>
       </c>
     </row>
     <row r="115">
@@ -1681,10 +1681,10 @@
         <v>1.13001</v>
       </c>
       <c r="B115" t="n">
-        <v>0.28209</v>
+        <v>0.43667</v>
       </c>
       <c r="C115" t="n">
-        <v>2.76734</v>
+        <v>4.28377</v>
       </c>
     </row>
     <row r="116">
@@ -1692,10 +1692,10 @@
         <v>1.14001</v>
       </c>
       <c r="B116" t="n">
-        <v>0.27249</v>
+        <v>0.43307</v>
       </c>
       <c r="C116" t="n">
-        <v>2.67312</v>
+        <v>4.24839</v>
       </c>
     </row>
     <row r="117">
@@ -1703,10 +1703,10 @@
         <v>1.15001</v>
       </c>
       <c r="B117" t="n">
-        <v>0.26417</v>
+        <v>0.42926</v>
       </c>
       <c r="C117" t="n">
-        <v>2.59154</v>
+        <v>4.21104</v>
       </c>
     </row>
     <row r="118">
@@ -1714,10 +1714,10 @@
         <v>1.16001</v>
       </c>
       <c r="B118" t="n">
-        <v>0.25651</v>
+        <v>0.42527</v>
       </c>
       <c r="C118" t="n">
-        <v>2.51635</v>
+        <v>4.17187</v>
       </c>
     </row>
     <row r="119">
@@ -1725,10 +1725,10 @@
         <v>1.17001</v>
       </c>
       <c r="B119" t="n">
-        <v>0.2534</v>
+        <v>0.4211</v>
       </c>
       <c r="C119" t="n">
-        <v>2.4859</v>
+        <v>4.13102</v>
       </c>
     </row>
     <row r="120">
@@ -1736,10 +1736,10 @@
         <v>1.18001</v>
       </c>
       <c r="B120" t="n">
-        <v>0.25703</v>
+        <v>0.41678</v>
       </c>
       <c r="C120" t="n">
-        <v>2.52145</v>
+        <v>4.08864</v>
       </c>
     </row>
     <row r="121">
@@ -1747,10 +1747,10 @@
         <v>1.19001</v>
       </c>
       <c r="B121" t="n">
-        <v>0.25869</v>
+        <v>0.41232</v>
       </c>
       <c r="C121" t="n">
-        <v>2.53774</v>
+        <v>4.04488</v>
       </c>
     </row>
     <row r="122">
@@ -1758,10 +1758,10 @@
         <v>1.20001</v>
       </c>
       <c r="B122" t="n">
-        <v>0.259</v>
+        <v>0.40774</v>
       </c>
       <c r="C122" t="n">
-        <v>2.54082</v>
+        <v>3.99989</v>
       </c>
     </row>
     <row r="123">
@@ -1769,10 +1769,10 @@
         <v>1.21001</v>
       </c>
       <c r="B123" t="n">
-        <v>0.2573</v>
+        <v>0.40304</v>
       </c>
       <c r="C123" t="n">
-        <v>2.52411</v>
+        <v>3.95382</v>
       </c>
     </row>
     <row r="124">
@@ -1780,10 +1780,10 @@
         <v>1.22001</v>
       </c>
       <c r="B124" t="n">
-        <v>0.25495</v>
+        <v>0.39825</v>
       </c>
       <c r="C124" t="n">
-        <v>2.50111</v>
+        <v>3.90683</v>
       </c>
     </row>
     <row r="125">
@@ -1791,10 +1791,10 @@
         <v>1.23001</v>
       </c>
       <c r="B125" t="n">
-        <v>0.25096</v>
+        <v>0.39338</v>
       </c>
       <c r="C125" t="n">
-        <v>2.46191</v>
+        <v>3.85906</v>
       </c>
     </row>
     <row r="126">
@@ -1802,10 +1802,10 @@
         <v>1.24001</v>
       </c>
       <c r="B126" t="n">
-        <v>0.24671</v>
+        <v>0.38845</v>
       </c>
       <c r="C126" t="n">
-        <v>2.42023</v>
+        <v>3.81066</v>
       </c>
     </row>
     <row r="127">
@@ -1813,10 +1813,10 @@
         <v>1.25001</v>
       </c>
       <c r="B127" t="n">
-        <v>0.24147</v>
+        <v>0.38346</v>
       </c>
       <c r="C127" t="n">
-        <v>2.36882</v>
+        <v>3.76176</v>
       </c>
     </row>
     <row r="128">
@@ -1824,10 +1824,10 @@
         <v>1.26001</v>
       </c>
       <c r="B128" t="n">
-        <v>0.2361</v>
+        <v>0.37844</v>
       </c>
       <c r="C128" t="n">
-        <v>2.31619</v>
+        <v>3.71252</v>
       </c>
     </row>
     <row r="129">
@@ -1835,10 +1835,10 @@
         <v>1.27001</v>
       </c>
       <c r="B129" t="n">
-        <v>0.23037</v>
+        <v>0.3734</v>
       </c>
       <c r="C129" t="n">
-        <v>2.25993</v>
+        <v>3.66305</v>
       </c>
     </row>
     <row r="130">
@@ -1846,10 +1846,10 @@
         <v>1.28001</v>
       </c>
       <c r="B130" t="n">
-        <v>0.22467</v>
+        <v>0.36835</v>
       </c>
       <c r="C130" t="n">
-        <v>2.20399</v>
+        <v>3.61348</v>
       </c>
     </row>
     <row r="131">
@@ -1857,10 +1857,10 @@
         <v>1.29001</v>
       </c>
       <c r="B131" t="n">
-        <v>0.21906</v>
+        <v>0.3633</v>
       </c>
       <c r="C131" t="n">
-        <v>2.14896</v>
+        <v>3.56394</v>
       </c>
     </row>
     <row r="132">
@@ -1868,10 +1868,10 @@
         <v>1.30001</v>
       </c>
       <c r="B132" t="n">
-        <v>0.21364</v>
+        <v>0.35826</v>
       </c>
       <c r="C132" t="n">
-        <v>2.09585</v>
+        <v>3.51455</v>
       </c>
     </row>
     <row r="133">
@@ -1879,10 +1879,10 @@
         <v>1.31001</v>
       </c>
       <c r="B133" t="n">
-        <v>0.20829</v>
+        <v>0.35325</v>
       </c>
       <c r="C133" t="n">
-        <v>2.0433</v>
+        <v>3.4654</v>
       </c>
     </row>
     <row r="134">
@@ -1890,10 +1890,10 @@
         <v>1.32001</v>
       </c>
       <c r="B134" t="n">
-        <v>0.20355</v>
+        <v>0.34828</v>
       </c>
       <c r="C134" t="n">
-        <v>1.99683</v>
+        <v>3.41661</v>
       </c>
     </row>
     <row r="135">
@@ -1901,10 +1901,10 @@
         <v>1.33001</v>
       </c>
       <c r="B135" t="n">
-        <v>0.19919</v>
+        <v>0.34335</v>
       </c>
       <c r="C135" t="n">
-        <v>1.95406</v>
+        <v>3.36827</v>
       </c>
     </row>
     <row r="136">
@@ -1912,10 +1912,10 @@
         <v>1.34001</v>
       </c>
       <c r="B136" t="n">
-        <v>0.19526</v>
+        <v>0.33848</v>
       </c>
       <c r="C136" t="n">
-        <v>1.91547</v>
+        <v>3.32047</v>
       </c>
     </row>
     <row r="137">
@@ -1923,10 +1923,10 @@
         <v>1.35001</v>
       </c>
       <c r="B137" t="n">
-        <v>0.19184</v>
+        <v>0.33367</v>
       </c>
       <c r="C137" t="n">
-        <v>1.88194</v>
+        <v>3.27329</v>
       </c>
     </row>
     <row r="138">
@@ -1934,10 +1934,10 @@
         <v>1.36001</v>
       </c>
       <c r="B138" t="n">
-        <v>0.18899</v>
+        <v>0.32893</v>
       </c>
       <c r="C138" t="n">
-        <v>1.85398</v>
+        <v>3.22681</v>
       </c>
     </row>
     <row r="139">
@@ -1945,10 +1945,10 @@
         <v>1.37001</v>
       </c>
       <c r="B139" t="n">
-        <v>0.18673</v>
+        <v>0.32427</v>
       </c>
       <c r="C139" t="n">
-        <v>1.83178</v>
+        <v>3.1811</v>
       </c>
     </row>
     <row r="140">
@@ -1956,10 +1956,10 @@
         <v>1.38001</v>
       </c>
       <c r="B140" t="n">
-        <v>0.18504</v>
+        <v>0.3197</v>
       </c>
       <c r="C140" t="n">
-        <v>1.81526</v>
+        <v>3.13622</v>
       </c>
     </row>
     <row r="141">
@@ -1967,10 +1967,10 @@
         <v>1.39001</v>
       </c>
       <c r="B141" t="n">
-        <v>0.18398</v>
+        <v>0.31521</v>
       </c>
       <c r="C141" t="n">
-        <v>1.80484</v>
+        <v>3.09224</v>
       </c>
     </row>
     <row r="142">
@@ -1978,10 +1978,10 @@
         <v>1.40001</v>
       </c>
       <c r="B142" t="n">
-        <v>0.18348</v>
+        <v>0.31083</v>
       </c>
       <c r="C142" t="n">
-        <v>1.79989</v>
+        <v>3.0492</v>
       </c>
     </row>
     <row r="143">
@@ -1989,10 +1989,10 @@
         <v>1.41001</v>
       </c>
       <c r="B143" t="n">
-        <v>0.1834</v>
+        <v>0.30654</v>
       </c>
       <c r="C143" t="n">
-        <v>1.79918</v>
+        <v>3.00715</v>
       </c>
     </row>
     <row r="144">
@@ -2000,10 +2000,10 @@
         <v>1.42001</v>
       </c>
       <c r="B144" t="n">
-        <v>0.18369</v>
+        <v>0.30236</v>
       </c>
       <c r="C144" t="n">
-        <v>1.802</v>
+        <v>2.96614</v>
       </c>
     </row>
     <row r="145">
@@ -2011,10 +2011,10 @@
         <v>1.43001</v>
       </c>
       <c r="B145" t="n">
-        <v>0.18426</v>
+        <v>0.29829</v>
       </c>
       <c r="C145" t="n">
-        <v>1.80755</v>
+        <v>2.9262</v>
       </c>
     </row>
     <row r="146">
@@ -2022,10 +2022,10 @@
         <v>1.44001</v>
       </c>
       <c r="B146" t="n">
-        <v>0.18501</v>
+        <v>0.29433</v>
       </c>
       <c r="C146" t="n">
-        <v>1.81498</v>
+        <v>2.88736</v>
       </c>
     </row>
     <row r="147">
@@ -2033,10 +2033,10 @@
         <v>1.45001</v>
       </c>
       <c r="B147" t="n">
-        <v>0.18588</v>
+        <v>0.29048</v>
       </c>
       <c r="C147" t="n">
-        <v>1.82343</v>
+        <v>2.84964</v>
       </c>
     </row>
     <row r="148">
@@ -2044,10 +2044,10 @@
         <v>1.46001</v>
       </c>
       <c r="B148" t="n">
-        <v>0.18675</v>
+        <v>0.28676</v>
       </c>
       <c r="C148" t="n">
-        <v>1.83206</v>
+        <v>2.81307</v>
       </c>
     </row>
     <row r="149">
@@ -2055,10 +2055,10 @@
         <v>1.47001</v>
       </c>
       <c r="B149" t="n">
-        <v>0.18757</v>
+        <v>0.28315</v>
       </c>
       <c r="C149" t="n">
-        <v>1.84007</v>
+        <v>2.77767</v>
       </c>
     </row>
     <row r="150">
@@ -2066,10 +2066,10 @@
         <v>1.48001</v>
       </c>
       <c r="B150" t="n">
-        <v>0.18856</v>
+        <v>0.27966</v>
       </c>
       <c r="C150" t="n">
-        <v>1.84979</v>
+        <v>2.74344</v>
       </c>
     </row>
     <row r="151">
@@ -2077,10 +2077,10 @@
         <v>1.49001</v>
       </c>
       <c r="B151" t="n">
-        <v>0.1894</v>
+        <v>0.27629</v>
       </c>
       <c r="C151" t="n">
-        <v>1.858</v>
+        <v>2.71041</v>
       </c>
     </row>
     <row r="152">
@@ -2088,10 +2088,10 @@
         <v>1.50001</v>
       </c>
       <c r="B152" t="n">
-        <v>0.18999</v>
+        <v>0.27304</v>
       </c>
       <c r="C152" t="n">
-        <v>1.86382</v>
+        <v>2.67856</v>
       </c>
     </row>
     <row r="153">
@@ -2099,10 +2099,10 @@
         <v>1.51001</v>
       </c>
       <c r="B153" t="n">
-        <v>0.19029</v>
+        <v>0.26992</v>
       </c>
       <c r="C153" t="n">
-        <v>1.86674</v>
+        <v>2.64792</v>
       </c>
     </row>
     <row r="154">
@@ -2110,10 +2110,10 @@
         <v>1.52001</v>
       </c>
       <c r="B154" t="n">
-        <v>0.19052</v>
+        <v>0.26692</v>
       </c>
       <c r="C154" t="n">
-        <v>1.869</v>
+        <v>2.61847</v>
       </c>
     </row>
     <row r="155">
@@ -2121,10 +2121,10 @@
         <v>1.53001</v>
       </c>
       <c r="B155" t="n">
-        <v>0.19055</v>
+        <v>0.26404</v>
       </c>
       <c r="C155" t="n">
-        <v>1.86929</v>
+        <v>2.59021</v>
       </c>
     </row>
     <row r="156">
@@ -2132,10 +2132,10 @@
         <v>1.54001</v>
       </c>
       <c r="B156" t="n">
-        <v>0.1902</v>
+        <v>0.26128</v>
       </c>
       <c r="C156" t="n">
-        <v>1.86582</v>
+        <v>2.56314</v>
       </c>
     </row>
     <row r="157">
@@ -2143,10 +2143,10 @@
         <v>1.55001</v>
       </c>
       <c r="B157" t="n">
-        <v>0.18984</v>
+        <v>0.25864</v>
       </c>
       <c r="C157" t="n">
-        <v>1.86233</v>
+        <v>2.53724</v>
       </c>
     </row>
     <row r="158">
@@ -2154,10 +2154,10 @@
         <v>1.56001</v>
       </c>
       <c r="B158" t="n">
-        <v>0.18913</v>
+        <v>0.25612</v>
       </c>
       <c r="C158" t="n">
-        <v>1.85539</v>
+        <v>2.51252</v>
       </c>
     </row>
     <row r="159">
@@ -2165,10 +2165,10 @@
         <v>1.57001</v>
       </c>
       <c r="B159" t="n">
-        <v>0.18836</v>
+        <v>0.25683</v>
       </c>
       <c r="C159" t="n">
-        <v>1.84778</v>
+        <v>2.51946</v>
       </c>
     </row>
     <row r="160">
@@ -2176,10 +2176,10 @@
         <v>1.58001</v>
       </c>
       <c r="B160" t="n">
-        <v>0.18729</v>
+        <v>0.2589</v>
       </c>
       <c r="C160" t="n">
-        <v>1.83732</v>
+        <v>2.53978</v>
       </c>
     </row>
     <row r="161">
@@ -2187,10 +2187,10 @@
         <v>1.59001</v>
       </c>
       <c r="B161" t="n">
-        <v>0.186</v>
+        <v>0.25959</v>
       </c>
       <c r="C161" t="n">
-        <v>1.8247</v>
+        <v>2.54657</v>
       </c>
     </row>
     <row r="162">
@@ -2198,10 +2198,10 @@
         <v>1.60001</v>
       </c>
       <c r="B162" t="n">
-        <v>0.1846</v>
+        <v>0.25892</v>
       </c>
       <c r="C162" t="n">
-        <v>1.81089</v>
+        <v>2.53999</v>
       </c>
     </row>
     <row r="163">
@@ -2209,10 +2209,10 @@
         <v>1.61001</v>
       </c>
       <c r="B163" t="n">
-        <v>0.18282</v>
+        <v>0.25693</v>
       </c>
       <c r="C163" t="n">
-        <v>1.79342</v>
+        <v>2.52053</v>
       </c>
     </row>
     <row r="164">
@@ -2220,10 +2220,10 @@
         <v>1.62001</v>
       </c>
       <c r="B164" t="n">
-        <v>0.18084</v>
+        <v>0.25371</v>
       </c>
       <c r="C164" t="n">
-        <v>1.77401</v>
+        <v>2.48894</v>
       </c>
     </row>
     <row r="165">
@@ -2231,10 +2231,10 @@
         <v>1.63001</v>
       </c>
       <c r="B165" t="n">
-        <v>0.1788</v>
+        <v>0.24936</v>
       </c>
       <c r="C165" t="n">
-        <v>1.75399</v>
+        <v>2.44619</v>
       </c>
     </row>
     <row r="166">
@@ -2242,10 +2242,10 @@
         <v>1.64001</v>
       </c>
       <c r="B166" t="n">
-        <v>0.17645</v>
+        <v>0.24398</v>
       </c>
       <c r="C166" t="n">
-        <v>1.731</v>
+        <v>2.39343</v>
       </c>
     </row>
     <row r="167">
@@ -2253,10 +2253,10 @@
         <v>1.65001</v>
       </c>
       <c r="B167" t="n">
-        <v>0.17398</v>
+        <v>0.23852</v>
       </c>
       <c r="C167" t="n">
-        <v>1.7067</v>
+        <v>2.3399</v>
       </c>
     </row>
     <row r="168">
@@ -2264,10 +2264,10 @@
         <v>1.66001</v>
       </c>
       <c r="B168" t="n">
-        <v>0.17149</v>
+        <v>0.23709</v>
       </c>
       <c r="C168" t="n">
-        <v>1.68229</v>
+        <v>2.3259</v>
       </c>
     </row>
     <row r="169">
@@ -2275,10 +2275,10 @@
         <v>1.67001</v>
       </c>
       <c r="B169" t="n">
-        <v>0.16879</v>
+        <v>0.23577</v>
       </c>
       <c r="C169" t="n">
-        <v>1.65582</v>
+        <v>2.31286</v>
       </c>
     </row>
     <row r="170">
@@ -2286,10 +2286,10 @@
         <v>1.68001</v>
       </c>
       <c r="B170" t="n">
-        <v>0.16614</v>
+        <v>0.23453</v>
       </c>
       <c r="C170" t="n">
-        <v>1.62985</v>
+        <v>2.30074</v>
       </c>
     </row>
     <row r="171">
@@ -2297,10 +2297,10 @@
         <v>1.69001</v>
       </c>
       <c r="B171" t="n">
-        <v>0.16439</v>
+        <v>0.23489</v>
       </c>
       <c r="C171" t="n">
-        <v>1.61265</v>
+        <v>2.30428</v>
       </c>
     </row>
     <row r="172">
@@ -2308,10 +2308,10 @@
         <v>1.70001</v>
       </c>
       <c r="B172" t="n">
-        <v>0.16267</v>
+        <v>0.2409</v>
       </c>
       <c r="C172" t="n">
-        <v>1.59584</v>
+        <v>2.36323</v>
       </c>
     </row>
     <row r="173">
@@ -2319,10 +2319,10 @@
         <v>1.71001</v>
       </c>
       <c r="B173" t="n">
-        <v>0.16092</v>
+        <v>0.24612</v>
       </c>
       <c r="C173" t="n">
-        <v>1.57866</v>
+        <v>2.41445</v>
       </c>
     </row>
     <row r="174">
@@ -2330,10 +2330,10 @@
         <v>1.72001</v>
       </c>
       <c r="B174" t="n">
-        <v>0.15864</v>
+        <v>0.25058</v>
       </c>
       <c r="C174" t="n">
-        <v>1.55627</v>
+        <v>2.45818</v>
       </c>
     </row>
     <row r="175">
@@ -2341,10 +2341,10 @@
         <v>1.73001</v>
       </c>
       <c r="B175" t="n">
-        <v>0.15588</v>
+        <v>0.25431</v>
       </c>
       <c r="C175" t="n">
-        <v>1.52921</v>
+        <v>2.49479</v>
       </c>
     </row>
     <row r="176">
@@ -2352,10 +2352,10 @@
         <v>1.74001</v>
       </c>
       <c r="B176" t="n">
-        <v>0.153</v>
+        <v>0.25737</v>
       </c>
       <c r="C176" t="n">
-        <v>1.50093</v>
+        <v>2.52476</v>
       </c>
     </row>
     <row r="177">
@@ -2363,10 +2363,10 @@
         <v>1.75001</v>
       </c>
       <c r="B177" t="n">
-        <v>0.15038</v>
+        <v>0.2598</v>
       </c>
       <c r="C177" t="n">
-        <v>1.47521</v>
+        <v>2.54862</v>
       </c>
     </row>
     <row r="178">
@@ -2374,10 +2374,10 @@
         <v>1.76001</v>
       </c>
       <c r="B178" t="n">
-        <v>0.14991</v>
+        <v>0.26167</v>
       </c>
       <c r="C178" t="n">
-        <v>1.47066</v>
+        <v>2.56696</v>
       </c>
     </row>
     <row r="179">
@@ -2385,10 +2385,10 @@
         <v>1.77001</v>
       </c>
       <c r="B179" t="n">
-        <v>0.15107</v>
+        <v>0.26304</v>
       </c>
       <c r="C179" t="n">
-        <v>1.48197</v>
+        <v>2.58038</v>
       </c>
     </row>
     <row r="180">
@@ -2396,10 +2396,10 @@
         <v>1.78001</v>
       </c>
       <c r="B180" t="n">
-        <v>0.15206</v>
+        <v>0.26397</v>
       </c>
       <c r="C180" t="n">
-        <v>1.49169</v>
+        <v>2.5895</v>
       </c>
     </row>
     <row r="181">
@@ -2407,10 +2407,10 @@
         <v>1.79001</v>
       </c>
       <c r="B181" t="n">
-        <v>0.15265</v>
+        <v>0.26452</v>
       </c>
       <c r="C181" t="n">
-        <v>1.49746</v>
+        <v>2.59491</v>
       </c>
     </row>
     <row r="182">
@@ -2418,10 +2418,10 @@
         <v>1.80001</v>
       </c>
       <c r="B182" t="n">
-        <v>0.15297</v>
+        <v>0.26475</v>
       </c>
       <c r="C182" t="n">
-        <v>1.50065</v>
+        <v>2.59718</v>
       </c>
     </row>
     <row r="183">
@@ -2429,10 +2429,10 @@
         <v>1.81001</v>
       </c>
       <c r="B183" t="n">
-        <v>0.15486</v>
+        <v>0.26471</v>
       </c>
       <c r="C183" t="n">
-        <v>1.51917</v>
+        <v>2.59681</v>
       </c>
     </row>
     <row r="184">
@@ -2440,10 +2440,10 @@
         <v>1.82001</v>
       </c>
       <c r="B184" t="n">
-        <v>0.1563</v>
+        <v>0.26445</v>
       </c>
       <c r="C184" t="n">
-        <v>1.53329</v>
+        <v>2.59426</v>
       </c>
     </row>
     <row r="185">
@@ -2451,10 +2451,10 @@
         <v>1.83001</v>
       </c>
       <c r="B185" t="n">
-        <v>0.15726</v>
+        <v>0.26401</v>
       </c>
       <c r="C185" t="n">
-        <v>1.54269</v>
+        <v>2.58993</v>
       </c>
     </row>
     <row r="186">
@@ -2462,10 +2462,10 @@
         <v>1.84001</v>
       </c>
       <c r="B186" t="n">
-        <v>0.15763</v>
+        <v>0.26342</v>
       </c>
       <c r="C186" t="n">
-        <v>1.54631</v>
+        <v>2.58415</v>
       </c>
     </row>
     <row r="187">
@@ -2473,10 +2473,10 @@
         <v>1.85001</v>
       </c>
       <c r="B187" t="n">
-        <v>0.1578</v>
+        <v>0.26271</v>
       </c>
       <c r="C187" t="n">
-        <v>1.54806</v>
+        <v>2.57717</v>
       </c>
     </row>
     <row r="188">
@@ -2484,10 +2484,10 @@
         <v>1.86001</v>
       </c>
       <c r="B188" t="n">
-        <v>0.1574</v>
+        <v>0.26189</v>
       </c>
       <c r="C188" t="n">
-        <v>1.54412</v>
+        <v>2.56918</v>
       </c>
     </row>
     <row r="189">
@@ -2495,10 +2495,10 @@
         <v>1.87001</v>
       </c>
       <c r="B189" t="n">
-        <v>0.15691</v>
+        <v>0.26099</v>
       </c>
       <c r="C189" t="n">
-        <v>1.53926</v>
+        <v>2.56029</v>
       </c>
     </row>
     <row r="190">
@@ -2506,10 +2506,10 @@
         <v>1.88001</v>
       </c>
       <c r="B190" t="n">
-        <v>0.1559</v>
+        <v>0.25999</v>
       </c>
       <c r="C190" t="n">
-        <v>1.52935</v>
+        <v>2.55055</v>
       </c>
     </row>
     <row r="191">
@@ -2517,10 +2517,10 @@
         <v>1.89001</v>
       </c>
       <c r="B191" t="n">
-        <v>0.15479</v>
+        <v>0.25891</v>
       </c>
       <c r="C191" t="n">
-        <v>1.51846</v>
+        <v>2.53995</v>
       </c>
     </row>
     <row r="192">
@@ -2528,10 +2528,10 @@
         <v>1.90001</v>
       </c>
       <c r="B192" t="n">
-        <v>0.15329</v>
+        <v>0.25774</v>
       </c>
       <c r="C192" t="n">
-        <v>1.50373</v>
+        <v>2.52844</v>
       </c>
     </row>
     <row r="193">
@@ -2539,10 +2539,10 @@
         <v>1.91001</v>
       </c>
       <c r="B193" t="n">
-        <v>0.15158</v>
+        <v>0.2566</v>
       </c>
       <c r="C193" t="n">
-        <v>1.487</v>
+        <v>2.5172</v>
       </c>
     </row>
     <row r="194">
@@ -2550,10 +2550,10 @@
         <v>1.92001</v>
       </c>
       <c r="B194" t="n">
-        <v>0.14958</v>
+        <v>0.2555</v>
       </c>
       <c r="C194" t="n">
-        <v>1.46737</v>
+        <v>2.50647</v>
       </c>
     </row>
     <row r="195">
@@ -2561,10 +2561,10 @@
         <v>1.93001</v>
       </c>
       <c r="B195" t="n">
-        <v>0.14727</v>
+        <v>0.25427</v>
       </c>
       <c r="C195" t="n">
-        <v>1.44471</v>
+        <v>2.49438</v>
       </c>
     </row>
     <row r="196">
@@ -2572,10 +2572,10 @@
         <v>1.94001</v>
       </c>
       <c r="B196" t="n">
-        <v>0.1447</v>
+        <v>0.25288</v>
       </c>
       <c r="C196" t="n">
-        <v>1.41947</v>
+        <v>2.48075</v>
       </c>
     </row>
     <row r="197">
@@ -2583,10 +2583,10 @@
         <v>1.95001</v>
       </c>
       <c r="B197" t="n">
-        <v>0.14176</v>
+        <v>0.25131</v>
       </c>
       <c r="C197" t="n">
-        <v>1.39064</v>
+        <v>2.46539</v>
       </c>
     </row>
     <row r="198">
@@ -2594,10 +2594,10 @@
         <v>1.96001</v>
       </c>
       <c r="B198" t="n">
-        <v>0.13966</v>
+        <v>0.24955</v>
       </c>
       <c r="C198" t="n">
-        <v>1.37006</v>
+        <v>2.44809</v>
       </c>
     </row>
     <row r="199">
@@ -2605,10 +2605,10 @@
         <v>1.97001</v>
       </c>
       <c r="B199" t="n">
-        <v>0.13858</v>
+        <v>0.24757</v>
       </c>
       <c r="C199" t="n">
-        <v>1.35951</v>
+        <v>2.42865</v>
       </c>
     </row>
     <row r="200">
@@ -2616,10 +2616,10 @@
         <v>1.98001</v>
       </c>
       <c r="B200" t="n">
-        <v>0.13782</v>
+        <v>0.24535</v>
       </c>
       <c r="C200" t="n">
-        <v>1.35198</v>
+        <v>2.40687</v>
       </c>
     </row>
     <row r="201">
@@ -2627,10 +2627,10 @@
         <v>1.99001</v>
       </c>
       <c r="B201" t="n">
-        <v>0.13703</v>
+        <v>0.24287</v>
       </c>
       <c r="C201" t="n">
-        <v>1.3443</v>
+        <v>2.38258</v>
       </c>
     </row>
     <row r="202">
@@ -2638,10 +2638,10 @@
         <v>2.00001</v>
       </c>
       <c r="B202" t="n">
-        <v>0.13827</v>
+        <v>0.24013</v>
       </c>
       <c r="C202" t="n">
-        <v>1.35646</v>
+        <v>2.35563</v>
       </c>
     </row>
     <row r="203">
@@ -2649,10 +2649,10 @@
         <v>2.01001</v>
       </c>
       <c r="B203" t="n">
-        <v>0.13974</v>
+        <v>0.23709</v>
       </c>
       <c r="C203" t="n">
-        <v>1.37087</v>
+        <v>2.32588</v>
       </c>
     </row>
     <row r="204">
@@ -2660,10 +2660,10 @@
         <v>2.02001</v>
       </c>
       <c r="B204" t="n">
-        <v>0.14124</v>
+        <v>0.23376</v>
       </c>
       <c r="C204" t="n">
-        <v>1.38555</v>
+        <v>2.29323</v>
       </c>
     </row>
     <row r="205">
@@ -2671,10 +2671,10 @@
         <v>2.03001</v>
       </c>
       <c r="B205" t="n">
-        <v>0.14275</v>
+        <v>0.23212</v>
       </c>
       <c r="C205" t="n">
-        <v>1.40033</v>
+        <v>2.2771</v>
       </c>
     </row>
     <row r="206">
@@ -2682,10 +2682,10 @@
         <v>2.04001</v>
       </c>
       <c r="B206" t="n">
-        <v>0.14429</v>
+        <v>0.23283</v>
       </c>
       <c r="C206" t="n">
-        <v>1.41553</v>
+        <v>2.28402</v>
       </c>
     </row>
     <row r="207">
@@ -2693,10 +2693,10 @@
         <v>2.05001</v>
       </c>
       <c r="B207" t="n">
-        <v>0.14591</v>
+        <v>0.23355</v>
       </c>
       <c r="C207" t="n">
-        <v>1.43134</v>
+        <v>2.2911</v>
       </c>
     </row>
     <row r="208">
@@ -2704,10 +2704,10 @@
         <v>2.06001</v>
       </c>
       <c r="B208" t="n">
-        <v>0.14749</v>
+        <v>0.23428</v>
       </c>
       <c r="C208" t="n">
-        <v>1.44683</v>
+        <v>2.29831</v>
       </c>
     </row>
     <row r="209">
@@ -2715,10 +2715,10 @@
         <v>2.07001</v>
       </c>
       <c r="B209" t="n">
-        <v>0.14903</v>
+        <v>0.23503</v>
       </c>
       <c r="C209" t="n">
-        <v>1.46202</v>
+        <v>2.30564</v>
       </c>
     </row>
     <row r="210">
@@ -2726,10 +2726,10 @@
         <v>2.08001</v>
       </c>
       <c r="B210" t="n">
-        <v>0.15067</v>
+        <v>0.23579</v>
       </c>
       <c r="C210" t="n">
-        <v>1.47803</v>
+        <v>2.31309</v>
       </c>
     </row>
     <row r="211">
@@ -2737,10 +2737,10 @@
         <v>2.09001</v>
       </c>
       <c r="B211" t="n">
-        <v>0.15223</v>
+        <v>0.23656</v>
       </c>
       <c r="C211" t="n">
-        <v>1.49336</v>
+        <v>2.32065</v>
       </c>
     </row>
     <row r="212">
@@ -2748,10 +2748,10 @@
         <v>2.10001</v>
       </c>
       <c r="B212" t="n">
-        <v>0.15372</v>
+        <v>0.23734</v>
       </c>
       <c r="C212" t="n">
-        <v>1.508</v>
+        <v>2.3283</v>
       </c>
     </row>
     <row r="213">
@@ -2759,10 +2759,10 @@
         <v>2.11001</v>
       </c>
       <c r="B213" t="n">
-        <v>0.15529</v>
+        <v>0.23813</v>
       </c>
       <c r="C213" t="n">
-        <v>1.52338</v>
+        <v>2.33604</v>
       </c>
     </row>
     <row r="214">
@@ -2770,10 +2770,10 @@
         <v>2.12001</v>
       </c>
       <c r="B214" t="n">
-        <v>0.15675</v>
+        <v>0.23893</v>
       </c>
       <c r="C214" t="n">
-        <v>1.53776</v>
+        <v>2.34386</v>
       </c>
     </row>
     <row r="215">
@@ -2781,10 +2781,10 @@
         <v>2.13001</v>
       </c>
       <c r="B215" t="n">
-        <v>0.15811</v>
+        <v>0.23973</v>
       </c>
       <c r="C215" t="n">
-        <v>1.55101</v>
+        <v>2.35174</v>
       </c>
     </row>
     <row r="216">
@@ -2792,10 +2792,10 @@
         <v>2.14001</v>
       </c>
       <c r="B216" t="n">
-        <v>0.15953</v>
+        <v>0.24054</v>
       </c>
       <c r="C216" t="n">
-        <v>1.56498</v>
+        <v>2.35969</v>
       </c>
     </row>
     <row r="217">
@@ -2803,10 +2803,10 @@
         <v>2.15001</v>
       </c>
       <c r="B217" t="n">
-        <v>0.16083</v>
+        <v>0.24136</v>
       </c>
       <c r="C217" t="n">
-        <v>1.57773</v>
+        <v>2.3677</v>
       </c>
     </row>
     <row r="218">
@@ -2814,10 +2814,10 @@
         <v>2.16001</v>
       </c>
       <c r="B218" t="n">
-        <v>0.16203</v>
+        <v>0.24218</v>
       </c>
       <c r="C218" t="n">
-        <v>1.58955</v>
+        <v>2.37574</v>
       </c>
     </row>
     <row r="219">
@@ -2825,10 +2825,10 @@
         <v>2.17001</v>
       </c>
       <c r="B219" t="n">
-        <v>0.16327</v>
+        <v>0.243</v>
       </c>
       <c r="C219" t="n">
-        <v>1.60164</v>
+        <v>2.38383</v>
       </c>
     </row>
     <row r="220">
@@ -2836,10 +2836,10 @@
         <v>2.18001</v>
       </c>
       <c r="B220" t="n">
-        <v>0.16434</v>
+        <v>0.24383</v>
       </c>
       <c r="C220" t="n">
-        <v>1.61222</v>
+        <v>2.39195</v>
       </c>
     </row>
     <row r="221">
@@ -2847,10 +2847,10 @@
         <v>2.19001</v>
       </c>
       <c r="B221" t="n">
-        <v>0.16544</v>
+        <v>0.24466</v>
       </c>
       <c r="C221" t="n">
-        <v>1.62297</v>
+        <v>2.4001</v>
       </c>
     </row>
     <row r="222">
@@ -2858,10 +2858,10 @@
         <v>2.20001</v>
       </c>
       <c r="B222" t="n">
-        <v>0.16642</v>
+        <v>0.24549</v>
       </c>
       <c r="C222" t="n">
-        <v>1.63263</v>
+        <v>2.40827</v>
       </c>
     </row>
     <row r="223">
@@ -2869,10 +2869,10 @@
         <v>2.21001</v>
       </c>
       <c r="B223" t="n">
-        <v>0.16736</v>
+        <v>0.24632</v>
       </c>
       <c r="C223" t="n">
-        <v>1.64176</v>
+        <v>2.41645</v>
       </c>
     </row>
     <row r="224">
@@ -2880,10 +2880,10 @@
         <v>2.22001</v>
       </c>
       <c r="B224" t="n">
-        <v>0.16823</v>
+        <v>0.24716</v>
       </c>
       <c r="C224" t="n">
-        <v>1.65038</v>
+        <v>2.42464</v>
       </c>
     </row>
     <row r="225">
@@ -2891,10 +2891,10 @@
         <v>2.23001</v>
       </c>
       <c r="B225" t="n">
-        <v>0.16903</v>
+        <v>0.24799</v>
       </c>
       <c r="C225" t="n">
-        <v>1.65819</v>
+        <v>2.43283</v>
       </c>
     </row>
     <row r="226">
@@ -2902,10 +2902,10 @@
         <v>2.24001</v>
       </c>
       <c r="B226" t="n">
-        <v>0.16979</v>
+        <v>0.24883</v>
       </c>
       <c r="C226" t="n">
-        <v>1.66568</v>
+        <v>2.44102</v>
       </c>
     </row>
     <row r="227">
@@ -2913,10 +2913,10 @@
         <v>2.25001</v>
       </c>
       <c r="B227" t="n">
-        <v>0.17049</v>
+        <v>0.24966</v>
       </c>
       <c r="C227" t="n">
-        <v>1.67251</v>
+        <v>2.44921</v>
       </c>
     </row>
     <row r="228">
@@ -2924,10 +2924,10 @@
         <v>2.26001</v>
       </c>
       <c r="B228" t="n">
-        <v>0.17113</v>
+        <v>0.2505</v>
       </c>
       <c r="C228" t="n">
-        <v>1.67879</v>
+        <v>2.45738</v>
       </c>
     </row>
     <row r="229">
@@ -2935,10 +2935,10 @@
         <v>2.27001</v>
       </c>
       <c r="B229" t="n">
-        <v>0.17168</v>
+        <v>0.25133</v>
       </c>
       <c r="C229" t="n">
-        <v>1.68416</v>
+        <v>2.46553</v>
       </c>
     </row>
     <row r="230">
@@ -2946,10 +2946,10 @@
         <v>2.28001</v>
       </c>
       <c r="B230" t="n">
-        <v>0.17219</v>
+        <v>0.25216</v>
       </c>
       <c r="C230" t="n">
-        <v>1.68918</v>
+        <v>2.47367</v>
       </c>
     </row>
     <row r="231">
@@ -2957,10 +2957,10 @@
         <v>2.29001</v>
       </c>
       <c r="B231" t="n">
-        <v>0.17251</v>
+        <v>0.25299</v>
       </c>
       <c r="C231" t="n">
-        <v>1.69231</v>
+        <v>2.48179</v>
       </c>
     </row>
     <row r="232">
@@ -2968,10 +2968,10 @@
         <v>2.30001</v>
       </c>
       <c r="B232" t="n">
-        <v>0.17289</v>
+        <v>0.25381</v>
       </c>
       <c r="C232" t="n">
-        <v>1.69602</v>
+        <v>2.48987</v>
       </c>
     </row>
     <row r="233">
@@ -2979,10 +2979,10 @@
         <v>2.31001</v>
       </c>
       <c r="B233" t="n">
-        <v>0.17306</v>
+        <v>0.25463</v>
       </c>
       <c r="C233" t="n">
-        <v>1.69776</v>
+        <v>2.49793</v>
       </c>
     </row>
     <row r="234">
@@ -2990,10 +2990,10 @@
         <v>2.32001</v>
       </c>
       <c r="B234" t="n">
-        <v>0.17319</v>
+        <v>0.25545</v>
       </c>
       <c r="C234" t="n">
-        <v>1.69898</v>
+        <v>2.50595</v>
       </c>
     </row>
     <row r="235">
@@ -3001,10 +3001,10 @@
         <v>2.33001</v>
       </c>
       <c r="B235" t="n">
-        <v>0.17323</v>
+        <v>0.25626</v>
       </c>
       <c r="C235" t="n">
-        <v>1.69938</v>
+        <v>2.51393</v>
       </c>
     </row>
     <row r="236">
@@ -3012,10 +3012,10 @@
         <v>2.34001</v>
       </c>
       <c r="B236" t="n">
-        <v>0.17307</v>
+        <v>0.25707</v>
       </c>
       <c r="C236" t="n">
-        <v>1.69779</v>
+        <v>2.52188</v>
       </c>
     </row>
     <row r="237">
@@ -3023,10 +3023,10 @@
         <v>2.35001</v>
       </c>
       <c r="B237" t="n">
-        <v>0.17297</v>
+        <v>0.25788</v>
       </c>
       <c r="C237" t="n">
-        <v>1.69681</v>
+        <v>2.52978</v>
       </c>
     </row>
     <row r="238">
@@ -3034,10 +3034,10 @@
         <v>2.36001</v>
       </c>
       <c r="B238" t="n">
-        <v>0.17281</v>
+        <v>0.25868</v>
       </c>
       <c r="C238" t="n">
-        <v>1.69527</v>
+        <v>2.53763</v>
       </c>
     </row>
     <row r="239">
@@ -3045,10 +3045,10 @@
         <v>2.37001</v>
       </c>
       <c r="B239" t="n">
-        <v>0.17387</v>
+        <v>0.25947</v>
       </c>
       <c r="C239" t="n">
-        <v>1.70564</v>
+        <v>2.54544</v>
       </c>
     </row>
     <row r="240">
@@ -3056,10 +3056,10 @@
         <v>2.38001</v>
       </c>
       <c r="B240" t="n">
-        <v>0.17481</v>
+        <v>0.26026</v>
       </c>
       <c r="C240" t="n">
-        <v>1.71487</v>
+        <v>2.55319</v>
       </c>
     </row>
     <row r="241">
@@ -3067,10 +3067,10 @@
         <v>2.39001</v>
       </c>
       <c r="B241" t="n">
-        <v>0.17563</v>
+        <v>0.26105</v>
       </c>
       <c r="C241" t="n">
-        <v>1.72295</v>
+        <v>2.5609</v>
       </c>
     </row>
     <row r="242">
@@ -3078,10 +3078,10 @@
         <v>2.40001</v>
       </c>
       <c r="B242" t="n">
-        <v>0.1764</v>
+        <v>0.26183</v>
       </c>
       <c r="C242" t="n">
-        <v>1.73052</v>
+        <v>2.56855</v>
       </c>
     </row>
     <row r="243">
@@ -3089,10 +3089,10 @@
         <v>2.41001</v>
       </c>
       <c r="B243" t="n">
-        <v>0.17716</v>
+        <v>0.2626</v>
       </c>
       <c r="C243" t="n">
-        <v>1.73794</v>
+        <v>2.57614</v>
       </c>
     </row>
     <row r="244">
@@ -3100,10 +3100,10 @@
         <v>2.42001</v>
       </c>
       <c r="B244" t="n">
-        <v>0.1778</v>
+        <v>0.26337</v>
       </c>
       <c r="C244" t="n">
-        <v>1.74421</v>
+        <v>2.58368</v>
       </c>
     </row>
     <row r="245">
@@ -3111,10 +3111,10 @@
         <v>2.43001</v>
       </c>
       <c r="B245" t="n">
-        <v>0.17832</v>
+        <v>0.26413</v>
       </c>
       <c r="C245" t="n">
-        <v>1.74933</v>
+        <v>2.59115</v>
       </c>
     </row>
     <row r="246">
@@ -3122,10 +3122,10 @@
         <v>2.44001</v>
       </c>
       <c r="B246" t="n">
-        <v>0.17873</v>
+        <v>0.26489</v>
       </c>
       <c r="C246" t="n">
-        <v>1.75331</v>
+        <v>2.59856</v>
       </c>
     </row>
     <row r="247">
@@ -3133,10 +3133,10 @@
         <v>2.45001</v>
       </c>
       <c r="B247" t="n">
-        <v>0.17912</v>
+        <v>0.26564</v>
       </c>
       <c r="C247" t="n">
-        <v>1.75714</v>
+        <v>2.60591</v>
       </c>
     </row>
     <row r="248">
@@ -3144,10 +3144,10 @@
         <v>2.46001</v>
       </c>
       <c r="B248" t="n">
-        <v>0.17946</v>
+        <v>0.26638</v>
       </c>
       <c r="C248" t="n">
-        <v>1.76051</v>
+        <v>2.6132</v>
       </c>
     </row>
     <row r="249">
@@ -3155,10 +3155,10 @@
         <v>2.47001</v>
       </c>
       <c r="B249" t="n">
-        <v>0.17969</v>
+        <v>0.26712</v>
       </c>
       <c r="C249" t="n">
-        <v>1.76275</v>
+        <v>2.62042</v>
       </c>
     </row>
     <row r="250">
@@ -3166,10 +3166,10 @@
         <v>2.48001</v>
       </c>
       <c r="B250" t="n">
-        <v>0.1798</v>
+        <v>0.26785</v>
       </c>
       <c r="C250" t="n">
-        <v>1.76387</v>
+        <v>2.62758</v>
       </c>
     </row>
     <row r="251">
@@ -3177,10 +3177,10 @@
         <v>2.49001</v>
       </c>
       <c r="B251" t="n">
-        <v>0.1798</v>
+        <v>0.26857</v>
       </c>
       <c r="C251" t="n">
-        <v>1.76388</v>
+        <v>2.63466</v>
       </c>
     </row>
     <row r="252">
@@ -3188,10 +3188,10 @@
         <v>2.50001</v>
       </c>
       <c r="B252" t="n">
-        <v>0.17977</v>
+        <v>0.26928</v>
       </c>
       <c r="C252" t="n">
-        <v>1.76359</v>
+        <v>2.64168</v>
       </c>
     </row>
     <row r="253">
@@ -3199,10 +3199,10 @@
         <v>2.51001</v>
       </c>
       <c r="B253" t="n">
-        <v>0.17972</v>
+        <v>0.26999</v>
       </c>
       <c r="C253" t="n">
-        <v>1.76309</v>
+        <v>2.64863</v>
       </c>
     </row>
     <row r="254">
@@ -3210,10 +3210,10 @@
         <v>2.52001</v>
       </c>
       <c r="B254" t="n">
-        <v>0.17956</v>
+        <v>0.27069</v>
       </c>
       <c r="C254" t="n">
-        <v>1.76151</v>
+        <v>2.65552</v>
       </c>
     </row>
     <row r="255">
@@ -3221,10 +3221,10 @@
         <v>2.53001</v>
       </c>
       <c r="B255" t="n">
-        <v>0.17929</v>
+        <v>0.27139</v>
       </c>
       <c r="C255" t="n">
-        <v>1.75887</v>
+        <v>2.66233</v>
       </c>
     </row>
     <row r="256">
@@ -3232,10 +3232,10 @@
         <v>2.54001</v>
       </c>
       <c r="B256" t="n">
-        <v>0.17892</v>
+        <v>0.27208</v>
       </c>
       <c r="C256" t="n">
-        <v>1.75519</v>
+        <v>2.66906</v>
       </c>
     </row>
     <row r="257">
@@ -3243,10 +3243,10 @@
         <v>2.55001</v>
       </c>
       <c r="B257" t="n">
-        <v>0.17844</v>
+        <v>0.27276</v>
       </c>
       <c r="C257" t="n">
-        <v>1.75049</v>
+        <v>2.67573</v>
       </c>
     </row>
     <row r="258">
@@ -3254,10 +3254,10 @@
         <v>2.56001</v>
       </c>
       <c r="B258" t="n">
-        <v>0.17802</v>
+        <v>0.27343</v>
       </c>
       <c r="C258" t="n">
-        <v>1.74638</v>
+        <v>2.68233</v>
       </c>
     </row>
     <row r="259">
@@ -3265,10 +3265,10 @@
         <v>2.57001</v>
       </c>
       <c r="B259" t="n">
-        <v>0.1775</v>
+        <v>0.27409</v>
       </c>
       <c r="C259" t="n">
-        <v>1.7413</v>
+        <v>2.68885</v>
       </c>
     </row>
     <row r="260">
@@ -3276,10 +3276,10 @@
         <v>2.58001</v>
       </c>
       <c r="B260" t="n">
-        <v>0.17689</v>
+        <v>0.27475</v>
       </c>
       <c r="C260" t="n">
-        <v>1.73524</v>
+        <v>2.6953</v>
       </c>
     </row>
     <row r="261">
@@ -3287,10 +3287,10 @@
         <v>2.59001</v>
       </c>
       <c r="B261" t="n">
-        <v>0.17617</v>
+        <v>0.2754</v>
       </c>
       <c r="C261" t="n">
-        <v>1.72823</v>
+        <v>2.70168</v>
       </c>
     </row>
     <row r="262">
@@ -3298,10 +3298,10 @@
         <v>2.60001</v>
       </c>
       <c r="B262" t="n">
-        <v>0.17536</v>
+        <v>0.27604</v>
       </c>
       <c r="C262" t="n">
-        <v>1.72028</v>
+        <v>2.70799</v>
       </c>
     </row>
     <row r="263">
@@ -3309,10 +3309,10 @@
         <v>2.61001</v>
       </c>
       <c r="B263" t="n">
-        <v>0.17446</v>
+        <v>0.27668</v>
       </c>
       <c r="C263" t="n">
-        <v>1.71148</v>
+        <v>2.71422</v>
       </c>
     </row>
     <row r="264">
@@ -3320,10 +3320,10 @@
         <v>2.62001</v>
       </c>
       <c r="B264" t="n">
-        <v>0.17363</v>
+        <v>0.27731</v>
       </c>
       <c r="C264" t="n">
-        <v>1.70328</v>
+        <v>2.72038</v>
       </c>
     </row>
     <row r="265">
@@ -3331,10 +3331,10 @@
         <v>2.63001</v>
       </c>
       <c r="B265" t="n">
-        <v>0.1727</v>
+        <v>0.27793</v>
       </c>
       <c r="C265" t="n">
-        <v>1.6942</v>
+        <v>2.72646</v>
       </c>
     </row>
     <row r="266">
@@ -3342,10 +3342,10 @@
         <v>2.64001</v>
       </c>
       <c r="B266" t="n">
-        <v>0.17169</v>
+        <v>0.27854</v>
       </c>
       <c r="C266" t="n">
-        <v>1.68426</v>
+        <v>2.73247</v>
       </c>
     </row>
     <row r="267">
@@ -3353,10 +3353,10 @@
         <v>2.65001</v>
       </c>
       <c r="B267" t="n">
-        <v>0.17059</v>
+        <v>0.27915</v>
       </c>
       <c r="C267" t="n">
-        <v>1.67348</v>
+        <v>2.73841</v>
       </c>
     </row>
     <row r="268">
@@ -3364,10 +3364,10 @@
         <v>2.66001</v>
       </c>
       <c r="B268" t="n">
-        <v>0.16943</v>
+        <v>0.27974</v>
       </c>
       <c r="C268" t="n">
-        <v>1.66213</v>
+        <v>2.74428</v>
       </c>
     </row>
     <row r="269">
@@ -3375,10 +3375,10 @@
         <v>2.67001</v>
       </c>
       <c r="B269" t="n">
-        <v>0.16832</v>
+        <v>0.28033</v>
       </c>
       <c r="C269" t="n">
-        <v>1.65123</v>
+        <v>2.75007</v>
       </c>
     </row>
     <row r="270">
@@ -3386,10 +3386,10 @@
         <v>2.68001</v>
       </c>
       <c r="B270" t="n">
-        <v>0.16713</v>
+        <v>0.28092</v>
       </c>
       <c r="C270" t="n">
-        <v>1.63954</v>
+        <v>2.75579</v>
       </c>
     </row>
     <row r="271">
@@ -3397,10 +3397,10 @@
         <v>2.69001</v>
       </c>
       <c r="B271" t="n">
-        <v>0.16586</v>
+        <v>0.28149</v>
       </c>
       <c r="C271" t="n">
-        <v>1.62711</v>
+        <v>2.76144</v>
       </c>
     </row>
     <row r="272">
@@ -3408,10 +3408,10 @@
         <v>2.70001</v>
       </c>
       <c r="B272" t="n">
-        <v>0.16466</v>
+        <v>0.28206</v>
       </c>
       <c r="C272" t="n">
-        <v>1.61536</v>
+        <v>2.76701</v>
       </c>
     </row>
     <row r="273">
@@ -3419,10 +3419,10 @@
         <v>2.71001</v>
       </c>
       <c r="B273" t="n">
-        <v>0.16339</v>
+        <v>0.28262</v>
       </c>
       <c r="C273" t="n">
-        <v>1.60287</v>
+        <v>2.77251</v>
       </c>
     </row>
     <row r="274">
@@ -3430,10 +3430,10 @@
         <v>2.72001</v>
       </c>
       <c r="B274" t="n">
-        <v>0.16214</v>
+        <v>0.28317</v>
       </c>
       <c r="C274" t="n">
-        <v>1.59057</v>
+        <v>2.77794</v>
       </c>
     </row>
     <row r="275">
@@ -3441,10 +3441,10 @@
         <v>2.73001</v>
       </c>
       <c r="B275" t="n">
-        <v>0.16087</v>
+        <v>0.28372</v>
       </c>
       <c r="C275" t="n">
-        <v>1.57812</v>
+        <v>2.7833</v>
       </c>
     </row>
     <row r="276">
@@ -3452,10 +3452,10 @@
         <v>2.74001</v>
       </c>
       <c r="B276" t="n">
-        <v>0.15967</v>
+        <v>0.28426</v>
       </c>
       <c r="C276" t="n">
-        <v>1.56632</v>
+        <v>2.78859</v>
       </c>
     </row>
     <row r="277">
@@ -3463,10 +3463,10 @@
         <v>2.75001</v>
       </c>
       <c r="B277" t="n">
-        <v>0.15839</v>
+        <v>0.28479</v>
       </c>
       <c r="C277" t="n">
-        <v>1.55382</v>
+        <v>2.79381</v>
       </c>
     </row>
     <row r="278">
@@ -3474,10 +3474,10 @@
         <v>2.76001</v>
       </c>
       <c r="B278" t="n">
-        <v>0.15717</v>
+        <v>0.28532</v>
       </c>
       <c r="C278" t="n">
-        <v>1.54188</v>
+        <v>2.79895</v>
       </c>
     </row>
     <row r="279">
@@ -3485,10 +3485,10 @@
         <v>2.77001</v>
       </c>
       <c r="B279" t="n">
-        <v>0.15626</v>
+        <v>0.28583</v>
       </c>
       <c r="C279" t="n">
-        <v>1.53291</v>
+        <v>2.80403</v>
       </c>
     </row>
     <row r="280">
@@ -3496,10 +3496,10 @@
         <v>2.78001</v>
       </c>
       <c r="B280" t="n">
-        <v>0.1562</v>
+        <v>0.28634</v>
       </c>
       <c r="C280" t="n">
-        <v>1.53228</v>
+        <v>2.80904</v>
       </c>
     </row>
     <row r="281">
@@ -3507,10 +3507,10 @@
         <v>2.79001</v>
       </c>
       <c r="B281" t="n">
-        <v>0.15602</v>
+        <v>0.28685</v>
       </c>
       <c r="C281" t="n">
-        <v>1.53053</v>
+        <v>2.81397</v>
       </c>
     </row>
     <row r="282">
@@ -3518,10 +3518,10 @@
         <v>2.80001</v>
       </c>
       <c r="B282" t="n">
-        <v>0.15547</v>
+        <v>0.28734</v>
       </c>
       <c r="C282" t="n">
-        <v>1.52517</v>
+        <v>2.81884</v>
       </c>
     </row>
     <row r="283">
@@ -3529,10 +3529,10 @@
         <v>2.81001</v>
       </c>
       <c r="B283" t="n">
-        <v>0.1548</v>
+        <v>0.28783</v>
       </c>
       <c r="C283" t="n">
-        <v>1.51856</v>
+        <v>2.82364</v>
       </c>
     </row>
     <row r="284">
@@ -3540,10 +3540,10 @@
         <v>2.82001</v>
       </c>
       <c r="B284" t="n">
-        <v>0.15381</v>
+        <v>0.28832</v>
       </c>
       <c r="C284" t="n">
-        <v>1.50885</v>
+        <v>2.82838</v>
       </c>
     </row>
     <row r="285">
@@ -3551,10 +3551,10 @@
         <v>2.83001</v>
       </c>
       <c r="B285" t="n">
-        <v>0.15268</v>
+        <v>0.28879</v>
       </c>
       <c r="C285" t="n">
-        <v>1.49778</v>
+        <v>2.83304</v>
       </c>
     </row>
     <row r="286">
@@ -3562,10 +3562,10 @@
         <v>2.84001</v>
       </c>
       <c r="B286" t="n">
-        <v>0.15127</v>
+        <v>0.28926</v>
       </c>
       <c r="C286" t="n">
-        <v>1.48399</v>
+        <v>2.83764</v>
       </c>
     </row>
     <row r="287">
@@ -3573,10 +3573,10 @@
         <v>2.85001</v>
       </c>
       <c r="B287" t="n">
-        <v>0.14971</v>
+        <v>0.28972</v>
       </c>
       <c r="C287" t="n">
-        <v>1.46868</v>
+        <v>2.84217</v>
       </c>
     </row>
     <row r="288">
@@ -3584,10 +3584,10 @@
         <v>2.86001</v>
       </c>
       <c r="B288" t="n">
-        <v>0.14792</v>
+        <v>0.29018</v>
       </c>
       <c r="C288" t="n">
-        <v>1.45113</v>
+        <v>2.84664</v>
       </c>
     </row>
     <row r="289">
@@ -3595,10 +3595,10 @@
         <v>2.87001</v>
       </c>
       <c r="B289" t="n">
-        <v>0.14595</v>
+        <v>0.29063</v>
       </c>
       <c r="C289" t="n">
-        <v>1.4318</v>
+        <v>2.85104</v>
       </c>
     </row>
     <row r="290">
@@ -3606,10 +3606,10 @@
         <v>2.88001</v>
       </c>
       <c r="B290" t="n">
-        <v>0.14381</v>
+        <v>0.29107</v>
       </c>
       <c r="C290" t="n">
-        <v>1.4108</v>
+        <v>2.85538</v>
       </c>
     </row>
     <row r="291">
@@ -3617,10 +3617,10 @@
         <v>2.89001</v>
       </c>
       <c r="B291" t="n">
-        <v>0.14139</v>
+        <v>0.2915</v>
       </c>
       <c r="C291" t="n">
-        <v>1.38706</v>
+        <v>2.85966</v>
       </c>
     </row>
     <row r="292">
@@ -3628,10 +3628,10 @@
         <v>2.90001</v>
       </c>
       <c r="B292" t="n">
-        <v>0.1389</v>
+        <v>0.29193</v>
       </c>
       <c r="C292" t="n">
-        <v>1.36263</v>
+        <v>2.86387</v>
       </c>
     </row>
     <row r="293">
@@ -3639,10 +3639,10 @@
         <v>2.91001</v>
       </c>
       <c r="B293" t="n">
-        <v>0.13619</v>
+        <v>0.29236</v>
       </c>
       <c r="C293" t="n">
-        <v>1.33601</v>
+        <v>2.86801</v>
       </c>
     </row>
     <row r="294">
@@ -3650,10 +3650,10 @@
         <v>2.92001</v>
       </c>
       <c r="B294" t="n">
-        <v>0.13452</v>
+        <v>0.29277</v>
       </c>
       <c r="C294" t="n">
-        <v>1.31961</v>
+        <v>2.8721</v>
       </c>
     </row>
     <row r="295">
@@ -3661,10 +3661,10 @@
         <v>2.93001</v>
       </c>
       <c r="B295" t="n">
-        <v>0.13302</v>
+        <v>0.29318</v>
       </c>
       <c r="C295" t="n">
-        <v>1.30489</v>
+        <v>2.87612</v>
       </c>
     </row>
     <row r="296">
@@ -3672,10 +3672,10 @@
         <v>2.94001</v>
       </c>
       <c r="B296" t="n">
-        <v>0.13154</v>
+        <v>0.29359</v>
       </c>
       <c r="C296" t="n">
-        <v>1.29042</v>
+        <v>2.88009</v>
       </c>
     </row>
     <row r="297">
@@ -3683,10 +3683,10 @@
         <v>2.95001</v>
       </c>
       <c r="B297" t="n">
-        <v>0.13012</v>
+        <v>0.29398</v>
       </c>
       <c r="C297" t="n">
-        <v>1.27652</v>
+        <v>2.88399</v>
       </c>
     </row>
     <row r="298">
@@ -3694,10 +3694,10 @@
         <v>2.96001</v>
       </c>
       <c r="B298" t="n">
-        <v>0.12876</v>
+        <v>0.29438</v>
       </c>
       <c r="C298" t="n">
-        <v>1.2631</v>
+        <v>2.88784</v>
       </c>
     </row>
     <row r="299">
@@ -3705,10 +3705,10 @@
         <v>2.97001</v>
       </c>
       <c r="B299" t="n">
-        <v>0.12736</v>
+        <v>0.29476</v>
       </c>
       <c r="C299" t="n">
-        <v>1.24945</v>
+        <v>2.89162</v>
       </c>
     </row>
     <row r="300">
@@ -3716,10 +3716,10 @@
         <v>2.98001</v>
       </c>
       <c r="B300" t="n">
-        <v>0.12603</v>
+        <v>0.29514</v>
       </c>
       <c r="C300" t="n">
-        <v>1.23633</v>
+        <v>2.89535</v>
       </c>
     </row>
     <row r="301">
@@ -3727,10 +3727,10 @@
         <v>2.99001</v>
       </c>
       <c r="B301" t="n">
-        <v>0.12469</v>
+        <v>0.29552</v>
       </c>
       <c r="C301" t="n">
-        <v>1.22322</v>
+        <v>2.89902</v>
       </c>
     </row>
     <row r="302">
@@ -3738,10 +3738,10 @@
         <v>3.00001</v>
       </c>
       <c r="B302" t="n">
-        <v>0.12338</v>
+        <v>0.29588</v>
       </c>
       <c r="C302" t="n">
-        <v>1.21034</v>
+        <v>2.90263</v>
       </c>
     </row>
     <row r="303">
@@ -3749,10 +3749,10 @@
         <v>3.01001</v>
       </c>
       <c r="B303" t="n">
-        <v>0.12205</v>
+        <v>0.29625</v>
       </c>
       <c r="C303" t="n">
-        <v>1.19727</v>
+        <v>2.90618</v>
       </c>
     </row>
     <row r="304">
@@ -3760,10 +3760,10 @@
         <v>3.02001</v>
       </c>
       <c r="B304" t="n">
-        <v>0.12075</v>
+        <v>0.2966</v>
       </c>
       <c r="C304" t="n">
-        <v>1.18456</v>
+        <v>2.90968</v>
       </c>
     </row>
     <row r="305">
@@ -3771,10 +3771,10 @@
         <v>3.03001</v>
       </c>
       <c r="B305" t="n">
-        <v>0.11941</v>
+        <v>0.29695</v>
       </c>
       <c r="C305" t="n">
-        <v>1.17145</v>
+        <v>2.91313</v>
       </c>
     </row>
     <row r="306">
@@ -3782,10 +3782,10 @@
         <v>3.04001</v>
       </c>
       <c r="B306" t="n">
-        <v>0.11806</v>
+        <v>0.2973</v>
       </c>
       <c r="C306" t="n">
-        <v>1.15819</v>
+        <v>2.91652</v>
       </c>
     </row>
     <row r="307">
@@ -3793,10 +3793,10 @@
         <v>3.05001</v>
       </c>
       <c r="B307" t="n">
-        <v>0.11675</v>
+        <v>0.29764</v>
       </c>
       <c r="C307" t="n">
-        <v>1.14527</v>
+        <v>2.91985</v>
       </c>
     </row>
     <row r="308">
@@ -3804,10 +3804,10 @@
         <v>3.06001</v>
       </c>
       <c r="B308" t="n">
-        <v>0.11543</v>
+        <v>0.29798</v>
       </c>
       <c r="C308" t="n">
-        <v>1.1324</v>
+        <v>2.92314</v>
       </c>
     </row>
     <row r="309">
@@ -3815,10 +3815,10 @@
         <v>3.07001</v>
       </c>
       <c r="B309" t="n">
-        <v>0.11425</v>
+        <v>0.2983</v>
       </c>
       <c r="C309" t="n">
-        <v>1.12074</v>
+        <v>2.92637</v>
       </c>
     </row>
     <row r="310">
@@ -3826,10 +3826,10 @@
         <v>3.08001</v>
       </c>
       <c r="B310" t="n">
-        <v>0.11294</v>
+        <v>0.29863</v>
       </c>
       <c r="C310" t="n">
-        <v>1.10795</v>
+        <v>2.92954</v>
       </c>
     </row>
     <row r="311">
@@ -3837,10 +3837,10 @@
         <v>3.09001</v>
       </c>
       <c r="B311" t="n">
-        <v>0.11165</v>
+        <v>0.29895</v>
       </c>
       <c r="C311" t="n">
-        <v>1.0953</v>
+        <v>2.93267</v>
       </c>
     </row>
     <row r="312">
@@ -3848,10 +3848,10 @@
         <v>3.10001</v>
       </c>
       <c r="B312" t="n">
-        <v>0.1105</v>
+        <v>0.29926</v>
       </c>
       <c r="C312" t="n">
-        <v>1.08403</v>
+        <v>2.93574</v>
       </c>
     </row>
     <row r="313">
@@ -3859,10 +3859,10 @@
         <v>3.11001</v>
       </c>
       <c r="B313" t="n">
-        <v>0.11049</v>
+        <v>0.29957</v>
       </c>
       <c r="C313" t="n">
-        <v>1.08392</v>
+        <v>2.93877</v>
       </c>
     </row>
     <row r="314">
@@ -3870,10 +3870,10 @@
         <v>3.12001</v>
       </c>
       <c r="B314" t="n">
-        <v>0.11045</v>
+        <v>0.29987</v>
       </c>
       <c r="C314" t="n">
-        <v>1.0835</v>
+        <v>2.94175</v>
       </c>
     </row>
     <row r="315">
@@ -3881,10 +3881,10 @@
         <v>3.13001</v>
       </c>
       <c r="B315" t="n">
-        <v>0.11038</v>
+        <v>0.30017</v>
       </c>
       <c r="C315" t="n">
-        <v>1.08279</v>
+        <v>2.94467</v>
       </c>
     </row>
     <row r="316">
@@ -3892,10 +3892,10 @@
         <v>3.14001</v>
       </c>
       <c r="B316" t="n">
-        <v>0.11028</v>
+        <v>0.30046</v>
       </c>
       <c r="C316" t="n">
-        <v>1.08181</v>
+        <v>2.94755</v>
       </c>
     </row>
     <row r="317">
@@ -3903,10 +3903,10 @@
         <v>3.15001</v>
       </c>
       <c r="B317" t="n">
-        <v>0.11021</v>
+        <v>0.30075</v>
       </c>
       <c r="C317" t="n">
-        <v>1.08112</v>
+        <v>2.95038</v>
       </c>
     </row>
     <row r="318">
@@ -3914,10 +3914,10 @@
         <v>3.16001</v>
       </c>
       <c r="B318" t="n">
-        <v>0.11011</v>
+        <v>0.30104</v>
       </c>
       <c r="C318" t="n">
-        <v>1.08016</v>
+        <v>2.95316</v>
       </c>
     </row>
     <row r="319">
@@ -3925,10 +3925,10 @@
         <v>3.17001</v>
       </c>
       <c r="B319" t="n">
-        <v>0.10998</v>
+        <v>0.30132</v>
       </c>
       <c r="C319" t="n">
-        <v>1.07892</v>
+        <v>2.9559</v>
       </c>
     </row>
     <row r="320">
@@ -3936,10 +3936,10 @@
         <v>3.18001</v>
       </c>
       <c r="B320" t="n">
-        <v>0.10983</v>
+        <v>0.30159</v>
       </c>
       <c r="C320" t="n">
-        <v>1.07742</v>
+        <v>2.95859</v>
       </c>
     </row>
     <row r="321">
@@ -3947,10 +3947,10 @@
         <v>3.19001</v>
       </c>
       <c r="B321" t="n">
-        <v>0.10965</v>
+        <v>0.30186</v>
       </c>
       <c r="C321" t="n">
-        <v>1.07566</v>
+        <v>2.96124</v>
       </c>
     </row>
     <row r="322">
@@ -3958,10 +3958,10 @@
         <v>3.20001</v>
       </c>
       <c r="B322" t="n">
-        <v>0.10944</v>
+        <v>0.30212</v>
       </c>
       <c r="C322" t="n">
-        <v>1.07365</v>
+        <v>2.96384</v>
       </c>
     </row>
     <row r="323">
@@ -3969,10 +3969,10 @@
         <v>3.21001</v>
       </c>
       <c r="B323" t="n">
-        <v>0.10921</v>
+        <v>0.30238</v>
       </c>
       <c r="C323" t="n">
-        <v>1.07139</v>
+        <v>2.9664</v>
       </c>
     </row>
     <row r="324">
@@ -3980,10 +3980,10 @@
         <v>3.22001</v>
       </c>
       <c r="B324" t="n">
-        <v>0.10896</v>
+        <v>0.30264</v>
       </c>
       <c r="C324" t="n">
-        <v>1.0689</v>
+        <v>2.96891</v>
       </c>
     </row>
     <row r="325">
@@ -3991,10 +3991,10 @@
         <v>3.23001</v>
       </c>
       <c r="B325" t="n">
-        <v>0.10868</v>
+        <v>0.30289</v>
       </c>
       <c r="C325" t="n">
-        <v>1.06617</v>
+        <v>2.97138</v>
       </c>
     </row>
     <row r="326">
@@ -4002,10 +4002,10 @@
         <v>3.24001</v>
       </c>
       <c r="B326" t="n">
-        <v>0.10838</v>
+        <v>0.30314</v>
       </c>
       <c r="C326" t="n">
-        <v>1.06322</v>
+        <v>2.97381</v>
       </c>
     </row>
     <row r="327">
@@ -4013,10 +4013,10 @@
         <v>3.25001</v>
       </c>
       <c r="B327" t="n">
-        <v>0.10806</v>
+        <v>0.30338</v>
       </c>
       <c r="C327" t="n">
-        <v>1.06005</v>
+        <v>2.97619</v>
       </c>
     </row>
     <row r="328">
@@ -4024,10 +4024,10 @@
         <v>3.26001</v>
       </c>
       <c r="B328" t="n">
-        <v>0.10771</v>
+        <v>0.30362</v>
       </c>
       <c r="C328" t="n">
-        <v>1.05668</v>
+        <v>2.97854</v>
       </c>
     </row>
     <row r="329">
@@ -4035,10 +4035,10 @@
         <v>3.27001</v>
       </c>
       <c r="B329" t="n">
-        <v>0.10736</v>
+        <v>0.30386</v>
       </c>
       <c r="C329" t="n">
-        <v>1.05322</v>
+        <v>2.98084</v>
       </c>
     </row>
     <row r="330">
@@ -4046,10 +4046,10 @@
         <v>3.28001</v>
       </c>
       <c r="B330" t="n">
-        <v>0.10703</v>
+        <v>0.30409</v>
       </c>
       <c r="C330" t="n">
-        <v>1.04994</v>
+        <v>2.9831</v>
       </c>
     </row>
     <row r="331">
@@ -4057,10 +4057,10 @@
         <v>3.29001</v>
       </c>
       <c r="B331" t="n">
-        <v>0.10667</v>
+        <v>0.30431</v>
       </c>
       <c r="C331" t="n">
-        <v>1.04646</v>
+        <v>2.98533</v>
       </c>
     </row>
     <row r="332">
@@ -4068,10 +4068,10 @@
         <v>3.30001</v>
       </c>
       <c r="B332" t="n">
-        <v>0.1063</v>
+        <v>0.30454</v>
       </c>
       <c r="C332" t="n">
-        <v>1.04278</v>
+        <v>2.98751</v>
       </c>
     </row>
     <row r="333">
@@ -4079,10 +4079,10 @@
         <v>3.31001</v>
       </c>
       <c r="B333" t="n">
-        <v>0.1059</v>
+        <v>0.30476</v>
       </c>
       <c r="C333" t="n">
-        <v>1.03892</v>
+        <v>2.98966</v>
       </c>
     </row>
     <row r="334">
@@ -4090,10 +4090,10 @@
         <v>3.32001</v>
       </c>
       <c r="B334" t="n">
-        <v>0.10549</v>
+        <v>0.30497</v>
       </c>
       <c r="C334" t="n">
-        <v>1.03487</v>
+        <v>2.99176</v>
       </c>
     </row>
     <row r="335">
@@ -4101,10 +4101,10 @@
         <v>3.33001</v>
       </c>
       <c r="B335" t="n">
-        <v>0.10506</v>
+        <v>0.30518</v>
       </c>
       <c r="C335" t="n">
-        <v>1.03064</v>
+        <v>2.99383</v>
       </c>
     </row>
     <row r="336">
@@ -4112,10 +4112,10 @@
         <v>3.34001</v>
       </c>
       <c r="B336" t="n">
-        <v>0.10461</v>
+        <v>0.30539</v>
       </c>
       <c r="C336" t="n">
-        <v>1.02625</v>
+        <v>2.99587</v>
       </c>
     </row>
     <row r="337">
@@ -4123,10 +4123,10 @@
         <v>3.35001</v>
       </c>
       <c r="B337" t="n">
-        <v>0.10415</v>
+        <v>0.30559</v>
       </c>
       <c r="C337" t="n">
-        <v>1.02169</v>
+        <v>2.99786</v>
       </c>
     </row>
     <row r="338">
@@ -4134,10 +4134,10 @@
         <v>3.36001</v>
       </c>
       <c r="B338" t="n">
-        <v>0.10367</v>
+        <v>0.30579</v>
       </c>
       <c r="C338" t="n">
-        <v>1.01697</v>
+        <v>2.99982</v>
       </c>
     </row>
     <row r="339">
@@ -4145,10 +4145,10 @@
         <v>3.37001</v>
       </c>
       <c r="B339" t="n">
-        <v>0.10317</v>
+        <v>0.30599</v>
       </c>
       <c r="C339" t="n">
-        <v>1.01209</v>
+        <v>3.00175</v>
       </c>
     </row>
     <row r="340">
@@ -4156,10 +4156,10 @@
         <v>3.38001</v>
       </c>
       <c r="B340" t="n">
-        <v>0.1027</v>
+        <v>0.30618</v>
       </c>
       <c r="C340" t="n">
-        <v>1.00744</v>
+        <v>3.00364</v>
       </c>
     </row>
     <row r="341">
@@ -4167,10 +4167,10 @@
         <v>3.39001</v>
       </c>
       <c r="B341" t="n">
-        <v>0.10221</v>
+        <v>0.30637</v>
       </c>
       <c r="C341" t="n">
-        <v>1.0027</v>
+        <v>3.0055</v>
       </c>
     </row>
     <row r="342">
@@ -4178,10 +4178,10 @@
         <v>3.40001</v>
       </c>
       <c r="B342" t="n">
-        <v>0.10171</v>
+        <v>0.30656</v>
       </c>
       <c r="C342" t="n">
-        <v>0.99782</v>
+        <v>3.00732</v>
       </c>
     </row>
     <row r="343">
@@ -4189,10 +4189,10 @@
         <v>3.41001</v>
       </c>
       <c r="B343" t="n">
-        <v>0.1012</v>
+        <v>0.30674</v>
       </c>
       <c r="C343" t="n">
-        <v>0.9928</v>
+        <v>3.00911</v>
       </c>
     </row>
     <row r="344">
@@ -4200,10 +4200,10 @@
         <v>3.42001</v>
       </c>
       <c r="B344" t="n">
-        <v>0.10069</v>
+        <v>0.30692</v>
       </c>
       <c r="C344" t="n">
-        <v>0.98773</v>
+        <v>3.01086</v>
       </c>
     </row>
     <row r="345">
@@ -4211,10 +4211,10 @@
         <v>3.43001</v>
       </c>
       <c r="B345" t="n">
-        <v>0.10019</v>
+        <v>0.30709</v>
       </c>
       <c r="C345" t="n">
-        <v>0.98286</v>
+        <v>3.01258</v>
       </c>
     </row>
     <row r="346">
@@ -4222,10 +4222,10 @@
         <v>3.44001</v>
       </c>
       <c r="B346" t="n">
-        <v>0.09968</v>
+        <v>0.30727</v>
       </c>
       <c r="C346" t="n">
-        <v>0.97785</v>
+        <v>3.01427</v>
       </c>
     </row>
     <row r="347">
@@ -4233,10 +4233,10 @@
         <v>3.45001</v>
       </c>
       <c r="B347" t="n">
-        <v>0.09916</v>
+        <v>0.30743</v>
       </c>
       <c r="C347" t="n">
-        <v>0.97271</v>
+        <v>3.01593</v>
       </c>
     </row>
     <row r="348">
@@ -4244,10 +4244,10 @@
         <v>3.46001</v>
       </c>
       <c r="B348" t="n">
-        <v>0.09865</v>
+        <v>0.3076</v>
       </c>
       <c r="C348" t="n">
-        <v>0.96777</v>
+        <v>3.01756</v>
       </c>
     </row>
     <row r="349">
@@ -4255,10 +4255,10 @@
         <v>3.47001</v>
       </c>
       <c r="B349" t="n">
-        <v>0.09814000000000001</v>
+        <v>0.30776</v>
       </c>
       <c r="C349" t="n">
-        <v>0.96278</v>
+        <v>3.01916</v>
       </c>
     </row>
     <row r="350">
@@ -4266,10 +4266,10 @@
         <v>3.48001</v>
       </c>
       <c r="B350" t="n">
-        <v>0.09765</v>
+        <v>0.30792</v>
       </c>
       <c r="C350" t="n">
-        <v>0.9579</v>
+        <v>3.02072</v>
       </c>
     </row>
     <row r="351">
@@ -4277,10 +4277,10 @@
         <v>3.49001</v>
       </c>
       <c r="B351" t="n">
-        <v>0.09715</v>
+        <v>0.30808</v>
       </c>
       <c r="C351" t="n">
-        <v>0.95307</v>
+        <v>3.02226</v>
       </c>
     </row>
     <row r="352">
@@ -4288,10 +4288,10 @@
         <v>3.50001</v>
       </c>
       <c r="B352" t="n">
-        <v>0.09665</v>
+        <v>0.30823</v>
       </c>
       <c r="C352" t="n">
-        <v>0.94812</v>
+        <v>3.02377</v>
       </c>
     </row>
     <row r="353">
@@ -4299,10 +4299,10 @@
         <v>3.51001</v>
       </c>
       <c r="B353" t="n">
-        <v>0.09612999999999999</v>
+        <v>0.30838</v>
       </c>
       <c r="C353" t="n">
-        <v>0.9430500000000001</v>
+        <v>3.02525</v>
       </c>
     </row>
     <row r="354">
@@ -4310,10 +4310,10 @@
         <v>3.52001</v>
       </c>
       <c r="B354" t="n">
-        <v>0.0956</v>
+        <v>0.30853</v>
       </c>
       <c r="C354" t="n">
-        <v>0.93787</v>
+        <v>3.0267</v>
       </c>
     </row>
     <row r="355">
@@ -4321,10 +4321,10 @@
         <v>3.53001</v>
       </c>
       <c r="B355" t="n">
-        <v>0.09506000000000001</v>
+        <v>0.30868</v>
       </c>
       <c r="C355" t="n">
-        <v>0.93258</v>
+        <v>3.02812</v>
       </c>
     </row>
     <row r="356">
@@ -4332,10 +4332,10 @@
         <v>3.54001</v>
       </c>
       <c r="B356" t="n">
-        <v>0.09453</v>
+        <v>0.30882</v>
       </c>
       <c r="C356" t="n">
-        <v>0.9273</v>
+        <v>3.02951</v>
       </c>
     </row>
     <row r="357">
@@ -4343,10 +4343,10 @@
         <v>3.55001</v>
       </c>
       <c r="B357" t="n">
-        <v>0.094</v>
+        <v>0.30896</v>
       </c>
       <c r="C357" t="n">
-        <v>0.92217</v>
+        <v>3.03088</v>
       </c>
     </row>
     <row r="358">
@@ -4354,10 +4354,10 @@
         <v>3.56001</v>
       </c>
       <c r="B358" t="n">
-        <v>0.09347</v>
+        <v>0.30909</v>
       </c>
       <c r="C358" t="n">
-        <v>0.91694</v>
+        <v>3.03222</v>
       </c>
     </row>
     <row r="359">
@@ -4365,10 +4365,10 @@
         <v>3.57001</v>
       </c>
       <c r="B359" t="n">
-        <v>0.09293</v>
+        <v>0.30923</v>
       </c>
       <c r="C359" t="n">
-        <v>0.91161</v>
+        <v>3.03353</v>
       </c>
     </row>
     <row r="360">
@@ -4376,10 +4376,10 @@
         <v>3.58001</v>
       </c>
       <c r="B360" t="n">
-        <v>0.09236999999999999</v>
+        <v>0.30936</v>
       </c>
       <c r="C360" t="n">
-        <v>0.9061900000000001</v>
+        <v>3.03482</v>
       </c>
     </row>
     <row r="361">
@@ -4387,10 +4387,10 @@
         <v>3.59001</v>
       </c>
       <c r="B361" t="n">
-        <v>0.09181</v>
+        <v>0.30949</v>
       </c>
       <c r="C361" t="n">
-        <v>0.90067</v>
+        <v>3.03608</v>
       </c>
     </row>
     <row r="362">
@@ -4398,10 +4398,10 @@
         <v>3.60001</v>
       </c>
       <c r="B362" t="n">
-        <v>0.09124</v>
+        <v>0.30961</v>
       </c>
       <c r="C362" t="n">
-        <v>0.89507</v>
+        <v>3.03731</v>
       </c>
     </row>
     <row r="363">
@@ -4409,10 +4409,10 @@
         <v>3.61001</v>
       </c>
       <c r="B363" t="n">
-        <v>0.09066</v>
+        <v>0.30974</v>
       </c>
       <c r="C363" t="n">
-        <v>0.88939</v>
+        <v>3.03853</v>
       </c>
     </row>
     <row r="364">
@@ -4420,10 +4420,10 @@
         <v>3.62001</v>
       </c>
       <c r="B364" t="n">
-        <v>0.09007</v>
+        <v>0.30986</v>
       </c>
       <c r="C364" t="n">
-        <v>0.88363</v>
+        <v>3.03971</v>
       </c>
     </row>
     <row r="365">
@@ -4431,10 +4431,10 @@
         <v>3.63001</v>
       </c>
       <c r="B365" t="n">
-        <v>0.08948</v>
+        <v>0.30998</v>
       </c>
       <c r="C365" t="n">
-        <v>0.8778</v>
+        <v>3.04087</v>
       </c>
     </row>
     <row r="366">
@@ -4442,10 +4442,10 @@
         <v>3.64001</v>
       </c>
       <c r="B366" t="n">
-        <v>0.08888</v>
+        <v>0.31009</v>
       </c>
       <c r="C366" t="n">
-        <v>0.8718900000000001</v>
+        <v>3.04201</v>
       </c>
     </row>
     <row r="367">
@@ -4453,10 +4453,10 @@
         <v>3.65001</v>
       </c>
       <c r="B367" t="n">
-        <v>0.08827</v>
+        <v>0.31021</v>
       </c>
       <c r="C367" t="n">
-        <v>0.86592</v>
+        <v>3.04313</v>
       </c>
     </row>
     <row r="368">
@@ -4464,10 +4464,10 @@
         <v>3.66001</v>
       </c>
       <c r="B368" t="n">
-        <v>0.08765000000000001</v>
+        <v>0.31032</v>
       </c>
       <c r="C368" t="n">
-        <v>0.85988</v>
+        <v>3.04422</v>
       </c>
     </row>
     <row r="369">
@@ -4475,10 +4475,10 @@
         <v>3.67001</v>
       </c>
       <c r="B369" t="n">
-        <v>0.08704000000000001</v>
+        <v>0.31043</v>
       </c>
       <c r="C369" t="n">
-        <v>0.85382</v>
+        <v>3.04529</v>
       </c>
     </row>
     <row r="370">
@@ -4486,10 +4486,10 @@
         <v>3.68001</v>
       </c>
       <c r="B370" t="n">
-        <v>0.08644</v>
+        <v>0.31053</v>
       </c>
       <c r="C370" t="n">
-        <v>0.84795</v>
+        <v>3.04633</v>
       </c>
     </row>
     <row r="371">
@@ -4497,10 +4497,10 @@
         <v>3.69001</v>
       </c>
       <c r="B371" t="n">
-        <v>0.08583</v>
+        <v>0.31064</v>
       </c>
       <c r="C371" t="n">
-        <v>0.8420299999999999</v>
+        <v>3.04736</v>
       </c>
     </row>
     <row r="372">
@@ -4508,10 +4508,10 @@
         <v>3.70001</v>
       </c>
       <c r="B372" t="n">
-        <v>0.08522</v>
+        <v>0.31074</v>
       </c>
       <c r="C372" t="n">
-        <v>0.83605</v>
+        <v>3.04836</v>
       </c>
     </row>
     <row r="373">
@@ -4519,10 +4519,10 @@
         <v>3.71001</v>
       </c>
       <c r="B373" t="n">
-        <v>0.08461</v>
+        <v>0.31084</v>
       </c>
       <c r="C373" t="n">
-        <v>0.83001</v>
+        <v>3.04934</v>
       </c>
     </row>
     <row r="374">
@@ -4530,10 +4530,10 @@
         <v>3.72001</v>
       </c>
       <c r="B374" t="n">
-        <v>0.08399</v>
+        <v>0.31094</v>
       </c>
       <c r="C374" t="n">
-        <v>0.82392</v>
+        <v>3.0503</v>
       </c>
     </row>
     <row r="375">
@@ -4541,10 +4541,10 @@
         <v>3.73001</v>
       </c>
       <c r="B375" t="n">
-        <v>0.08336</v>
+        <v>0.31103</v>
       </c>
       <c r="C375" t="n">
-        <v>0.81779</v>
+        <v>3.05124</v>
       </c>
     </row>
     <row r="376">
@@ -4552,10 +4552,10 @@
         <v>3.74001</v>
       </c>
       <c r="B376" t="n">
-        <v>0.08273</v>
+        <v>0.31113</v>
       </c>
       <c r="C376" t="n">
-        <v>0.8116100000000001</v>
+        <v>3.05215</v>
       </c>
     </row>
     <row r="377">
@@ -4563,10 +4563,10 @@
         <v>3.75001</v>
       </c>
       <c r="B377" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.31122</v>
       </c>
       <c r="C377" t="n">
-        <v>0.8053900000000001</v>
+        <v>3.05305</v>
       </c>
     </row>
     <row r="378">
@@ -4574,10 +4574,10 @@
         <v>3.76001</v>
       </c>
       <c r="B378" t="n">
-        <v>0.08146</v>
+        <v>0.31131</v>
       </c>
       <c r="C378" t="n">
-        <v>0.7991200000000001</v>
+        <v>3.05393</v>
       </c>
     </row>
     <row r="379">
@@ -4585,10 +4585,10 @@
         <v>3.77001</v>
       </c>
       <c r="B379" t="n">
-        <v>0.08082</v>
+        <v>0.3114</v>
       </c>
       <c r="C379" t="n">
-        <v>0.79283</v>
+        <v>3.05479</v>
       </c>
     </row>
     <row r="380">
@@ -4596,10 +4596,10 @@
         <v>3.78001</v>
       </c>
       <c r="B380" t="n">
-        <v>0.08017000000000001</v>
+        <v>0.31148</v>
       </c>
       <c r="C380" t="n">
-        <v>0.78649</v>
+        <v>3.05563</v>
       </c>
     </row>
     <row r="381">
@@ -4607,10 +4607,10 @@
         <v>3.79001</v>
       </c>
       <c r="B381" t="n">
-        <v>0.07951999999999999</v>
+        <v>0.31156</v>
       </c>
       <c r="C381" t="n">
-        <v>0.78013</v>
+        <v>3.05645</v>
       </c>
     </row>
     <row r="382">
@@ -4618,10 +4618,10 @@
         <v>3.80001</v>
       </c>
       <c r="B382" t="n">
-        <v>0.07887</v>
+        <v>0.31165</v>
       </c>
       <c r="C382" t="n">
-        <v>0.77374</v>
+        <v>3.05725</v>
       </c>
     </row>
     <row r="383">
@@ -4629,10 +4629,10 @@
         <v>3.81001</v>
       </c>
       <c r="B383" t="n">
-        <v>0.07822</v>
+        <v>0.31173</v>
       </c>
       <c r="C383" t="n">
-        <v>0.76732</v>
+        <v>3.05803</v>
       </c>
     </row>
     <row r="384">
@@ -4640,10 +4640,10 @@
         <v>3.82001</v>
       </c>
       <c r="B384" t="n">
-        <v>0.07756</v>
+        <v>0.3118</v>
       </c>
       <c r="C384" t="n">
-        <v>0.76088</v>
+        <v>3.0588</v>
       </c>
     </row>
     <row r="385">
@@ -4651,10 +4651,10 @@
         <v>3.83001</v>
       </c>
       <c r="B385" t="n">
-        <v>0.0769</v>
+        <v>0.31188</v>
       </c>
       <c r="C385" t="n">
-        <v>0.75442</v>
+        <v>3.05954</v>
       </c>
     </row>
     <row r="386">
@@ -4662,10 +4662,10 @@
         <v>3.84001</v>
       </c>
       <c r="B386" t="n">
-        <v>0.07624</v>
+        <v>0.31195</v>
       </c>
       <c r="C386" t="n">
-        <v>0.74794</v>
+        <v>3.06027</v>
       </c>
     </row>
     <row r="387">
@@ -4673,10 +4673,10 @@
         <v>3.85001</v>
       </c>
       <c r="B387" t="n">
-        <v>0.07557999999999999</v>
+        <v>0.31203</v>
       </c>
       <c r="C387" t="n">
-        <v>0.74144</v>
+        <v>3.06099</v>
       </c>
     </row>
     <row r="388">
@@ -4684,10 +4684,10 @@
         <v>3.86001</v>
       </c>
       <c r="B388" t="n">
-        <v>0.07492</v>
+        <v>0.3121</v>
       </c>
       <c r="C388" t="n">
-        <v>0.73498</v>
+        <v>3.06168</v>
       </c>
     </row>
     <row r="389">
@@ -4695,10 +4695,10 @@
         <v>3.87001</v>
       </c>
       <c r="B389" t="n">
-        <v>0.07428</v>
+        <v>0.31217</v>
       </c>
       <c r="C389" t="n">
-        <v>0.72865</v>
+        <v>3.06236</v>
       </c>
     </row>
     <row r="390">
@@ -4706,10 +4706,10 @@
         <v>3.88001</v>
       </c>
       <c r="B390" t="n">
-        <v>0.07363</v>
+        <v>0.31223</v>
       </c>
       <c r="C390" t="n">
-        <v>0.72231</v>
+        <v>3.06302</v>
       </c>
     </row>
     <row r="391">
@@ -4717,10 +4717,10 @@
         <v>3.89001</v>
       </c>
       <c r="B391" t="n">
-        <v>0.07298</v>
+        <v>0.3123</v>
       </c>
       <c r="C391" t="n">
-        <v>0.71596</v>
+        <v>3.06367</v>
       </c>
     </row>
     <row r="392">
@@ -4728,10 +4728,10 @@
         <v>3.90001</v>
       </c>
       <c r="B392" t="n">
-        <v>0.07233000000000001</v>
+        <v>0.31236</v>
       </c>
       <c r="C392" t="n">
-        <v>0.7095900000000001</v>
+        <v>3.0643</v>
       </c>
     </row>
     <row r="393">
@@ -4739,10 +4739,10 @@
         <v>3.91001</v>
       </c>
       <c r="B393" t="n">
-        <v>0.07167999999999999</v>
+        <v>0.31243</v>
       </c>
       <c r="C393" t="n">
-        <v>0.70322</v>
+        <v>3.06491</v>
       </c>
     </row>
     <row r="394">
@@ -4750,10 +4750,10 @@
         <v>3.92001</v>
       </c>
       <c r="B394" t="n">
-        <v>0.07103</v>
+        <v>0.31249</v>
       </c>
       <c r="C394" t="n">
-        <v>0.6968299999999999</v>
+        <v>3.06551</v>
       </c>
     </row>
     <row r="395">
@@ -4761,10 +4761,10 @@
         <v>3.93001</v>
       </c>
       <c r="B395" t="n">
-        <v>0.07038</v>
+        <v>0.31255</v>
       </c>
       <c r="C395" t="n">
-        <v>0.6904400000000001</v>
+        <v>3.06609</v>
       </c>
     </row>
     <row r="396">
@@ -4772,10 +4772,10 @@
         <v>3.94001</v>
       </c>
       <c r="B396" t="n">
-        <v>0.06973</v>
+        <v>0.31261</v>
       </c>
       <c r="C396" t="n">
-        <v>0.68405</v>
+        <v>3.06666</v>
       </c>
     </row>
     <row r="397">
@@ -4783,10 +4783,10 @@
         <v>3.95001</v>
       </c>
       <c r="B397" t="n">
-        <v>0.06908</v>
+        <v>0.31266</v>
       </c>
       <c r="C397" t="n">
-        <v>0.67766</v>
+        <v>3.06721</v>
       </c>
     </row>
     <row r="398">
@@ -4794,10 +4794,10 @@
         <v>3.96001</v>
       </c>
       <c r="B398" t="n">
-        <v>0.06843</v>
+        <v>0.31272</v>
       </c>
       <c r="C398" t="n">
-        <v>0.67126</v>
+        <v>3.06775</v>
       </c>
     </row>
     <row r="399">
@@ -4805,10 +4805,10 @@
         <v>3.97001</v>
       </c>
       <c r="B399" t="n">
-        <v>0.06777</v>
+        <v>0.31277</v>
       </c>
       <c r="C399" t="n">
-        <v>0.66487</v>
+        <v>3.06828</v>
       </c>
     </row>
     <row r="400">
@@ -4816,10 +4816,10 @@
         <v>3.98001</v>
       </c>
       <c r="B400" t="n">
-        <v>0.06712</v>
+        <v>0.31282</v>
       </c>
       <c r="C400" t="n">
-        <v>0.65847</v>
+        <v>3.06879</v>
       </c>
     </row>
     <row r="401">
@@ -4827,10 +4827,10 @@
         <v>3.99001</v>
       </c>
       <c r="B401" t="n">
-        <v>0.06647</v>
+        <v>0.31287</v>
       </c>
       <c r="C401" t="n">
-        <v>0.6520899999999999</v>
+        <v>3.06928</v>
       </c>
     </row>
   </sheetData>
